--- a/python_imp/samples_export.xlsx
+++ b/python_imp/samples_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,4122 +462,3958 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-4.163379355687049e-08</v>
+        <v>-4.733727810650888e-08</v>
       </c>
       <c r="B2" t="n">
-        <v>1.777141614437343e-11</v>
+        <v>1.266416554909418e-14</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.163379355687049e-08</v>
+        <v>-4.733727810650888e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.777141614437343e-11</v>
+        <v>1.266416554909418e-14</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.163379355687049e-08</v>
+        <v>-4.733727810650888e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.777141614437343e-11</v>
+        <v>1.266416554909418e-14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-3.547994740302433e-08</v>
+        <v>-4.092702169625247e-08</v>
       </c>
       <c r="B3" t="n">
-        <v>1.558940642955917e-08</v>
+        <v>4.088986476321812e-11</v>
       </c>
       <c r="C3" t="n">
-        <v>-4.101840894148587e-08</v>
+        <v>-4.669625246548323e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.574934917485853e-09</v>
+        <v>4.100384225316018e-12</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.101840894148587e-08</v>
+        <v>-4.669625246548323e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.122682327176099e-05</v>
+        <v>-1.540124775660534e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-2.932610124917818e-08</v>
+        <v>-3.451676528599606e-08</v>
       </c>
       <c r="B4" t="n">
-        <v>4.636648898333438e-06</v>
+        <v>4.082836041142489e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.040302432610125e-08</v>
+        <v>-4.60552268244576e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.132098418827333e-09</v>
+        <v>8.1881042850829e-12</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.040302432610125e-08</v>
+        <v>-4.60552268244576e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.576935114591077e-05</v>
+        <v>-2.593911387248159e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.317225509533202e-08</v>
+        <v>-2.810650887573965e-08</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0004675692381140412</v>
+        <v>1.260710517704852e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.978763971071664e-08</v>
+        <v>-4.541420118343195e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.689261920168812e-09</v>
+        <v>1.227582434484982e-11</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.978763971071664e-08</v>
+        <v>-4.541420118343195e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.436515010552858e-05</v>
+        <v>-3.21539288002381e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-2.169625246548324e-08</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.001203859994828202</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.917225509533202e-08</v>
+        <v>-4.477317554240632e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.246425421510292e-09</v>
+        <v>1.636354440461671e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.917225509533202e-08</v>
+        <v>-4.477317554240632e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.775180440510982e-05</v>
+        <v>-3.458602300514806e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.03555034011478109</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.855687047994741e-08</v>
+        <v>-4.413214990138067e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.803588922851772e-09</v>
+        <v>2.045126446438363e-11</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.855687047994741e-08</v>
+        <v>-4.413214990138067e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.666689829914985e-05</v>
+        <v>-3.377572695248478e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.3246524673583495</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.794148586456279e-08</v>
+        <v>-4.349112426035503e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.360752424193252e-09</v>
+        <v>2.453898452415051e-11</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.794148586456279e-08</v>
+        <v>-4.349112426035503e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.184801604214406e-05</v>
+        <v>-3.026337110752159e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.443129520052593e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9706970133569975</v>
+        <v>0.9168553557320287</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.732610124917818e-08</v>
+        <v>-4.285009861932939e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.091791592553473e-08</v>
+        <v>2.862670458391743e-11</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.732610124917818e-08</v>
+        <v>-4.285009861932939e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.403274188858784e-05</v>
+        <v>-2.458928593553169e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.8007374029168086</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.671071663379356e-08</v>
+        <v>-4.220907297830375e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>1.247507942687621e-08</v>
+        <v>3.271442464368432e-11</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.671071663379356e-08</v>
+        <v>-4.220907297830375e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.395866009297659e-05</v>
+        <v>-1.729380190178853e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.5580351457700473</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.609533201840894e-08</v>
+        <v>-4.156804733727811e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>1.403224292821769e-08</v>
+        <v>3.680214470345124e-11</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.609533201840894e-08</v>
+        <v>-4.156804733727811e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.236335490980562e-05</v>
+        <v>-8.917249471565255e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.388895563989223</v>
       </c>
       <c r="C12" t="n">
-        <v>-3.547994740302433e-08</v>
+        <v>-4.092702169625247e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>1.558940642955917e-08</v>
+        <v>4.088986476321812e-11</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.547994740302433e-08</v>
+        <v>-4.092702169625247e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.558940642955917e-08</v>
+        <v>4.088986476321812e-11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.2710219254771064</v>
       </c>
       <c r="C13" t="n">
-        <v>-3.486456278763971e-08</v>
+        <v>-4.028599605522683e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>4.776953556199475e-07</v>
+        <v>4.119636919429406e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.486456278763971e-08</v>
+        <v>-4.028599605522683e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>1.244058860123368e-05</v>
+        <v>8.91773871722828e-06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1888756028375619</v>
       </c>
       <c r="C14" t="n">
-        <v>-3.42491781722551e-08</v>
+        <v>-3.964497041420119e-08</v>
       </c>
       <c r="D14" t="n">
-        <v>9.398013048103358e-07</v>
+        <v>8.19838397409555e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.42491781722551e-08</v>
+        <v>-3.964497041420119e-08</v>
       </c>
       <c r="F14" t="n">
-        <v>2.417405842011132e-05</v>
+        <v>1.729551354525188e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>3.599605522682445e-08</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.1316277023877387</v>
       </c>
       <c r="C15" t="n">
-        <v>-3.363379355687048e-08</v>
+        <v>-3.900394477317554e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>1.401907254000724e-06</v>
+        <v>1.227713102876174e-08</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.363379355687048e-08</v>
+        <v>-3.900394477317554e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>3.447841460856709e-05</v>
+        <v>2.459303490866241e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.452005259697567e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0814339543807958</v>
+        <v>0.09173155121985659</v>
       </c>
       <c r="C16" t="n">
-        <v>-3.301840894148587e-08</v>
+        <v>-3.836291913214991e-08</v>
       </c>
       <c r="D16" t="n">
-        <v>1.864013203191108e-06</v>
+        <v>1.635587808342788e-08</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.301840894148587e-08</v>
+        <v>-3.836291913214991e-08</v>
       </c>
       <c r="F16" t="n">
-        <v>4.261607291210555e-05</v>
+        <v>3.026997234218646e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>4.881656804733726e-08</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.06392786120670763</v>
       </c>
       <c r="C17" t="n">
-        <v>-3.240302432610126e-08</v>
+        <v>-3.772189349112426e-08</v>
       </c>
       <c r="D17" t="n">
-        <v>2.326119152381496e-06</v>
+        <v>2.043462513809407e-08</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.240302432610126e-08</v>
+        <v>-3.772189349112426e-08</v>
       </c>
       <c r="F17" t="n">
-        <v>4.784944907623148e-05</v>
+        <v>3.378599538055083e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="B18" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.04455142624448971</v>
       </c>
       <c r="C18" t="n">
-        <v>-3.178763971071664e-08</v>
+        <v>-3.708086785009862e-08</v>
       </c>
       <c r="D18" t="n">
-        <v>2.788225101571884e-06</v>
+        <v>2.451337219276022e-08</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.178763971071664e-08</v>
+        <v>-3.708086785009862e-08</v>
       </c>
       <c r="F18" t="n">
-        <v>4.94409588464494e-05</v>
+        <v>3.460077355848216e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.03104795847932967</v>
       </c>
       <c r="C19" t="n">
-        <v>-3.117225509533202e-08</v>
+        <v>-3.643984220907298e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>3.250331050762272e-06</v>
+        <v>2.85921192474264e-08</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.117225509533202e-08</v>
+        <v>-3.643984220907298e-08</v>
       </c>
       <c r="F19" t="n">
-        <v>4.665301796826396e-05</v>
+        <v>3.217397641070716e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.02163737071949312</v>
       </c>
       <c r="C20" t="n">
-        <v>-3.055687047994741e-08</v>
+        <v>-3.579881656804734e-08</v>
       </c>
       <c r="D20" t="n">
-        <v>3.712436999952661e-06</v>
+        <v>3.267086630209255e-08</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.055687047994741e-08</v>
+        <v>-3.579881656804734e-08</v>
       </c>
       <c r="F20" t="n">
-        <v>3.874804218717971e-05</v>
+        <v>2.59652734719526e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7.528928336620645e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01438892743508268</v>
+        <v>0.0150791174229529</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.994148586456279e-08</v>
+        <v>-3.51577909270217e-08</v>
       </c>
       <c r="D21" t="n">
-        <v>4.17454294914305e-06</v>
+        <v>3.674961335675874e-08</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.994148586456279e-08</v>
+        <v>-3.51577909270217e-08</v>
       </c>
       <c r="F21" t="n">
-        <v>2.498844724870134e-05</v>
+        <v>1.543433427694503e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>8.144312952005262e-08</v>
+        <v>8.086785009861932e-08</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01017356120096248</v>
+        <v>0.01050866046540279</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.932610124917818e-08</v>
+        <v>-3.451676528599606e-08</v>
       </c>
       <c r="D22" t="n">
-        <v>4.636648898333438e-06</v>
+        <v>4.082836041142489e-08</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.932610124917818e-08</v>
+        <v>-3.451676528599606e-08</v>
       </c>
       <c r="F22" t="n">
-        <v>4.636648898333438e-06</v>
+        <v>4.082836041142489e-08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8.759697567389875e-08</v>
+        <v>8.727810650887573e-08</v>
       </c>
       <c r="B23" t="n">
-        <v>0.007193124572813908</v>
+        <v>0.007323501878765411</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.871071663379356e-08</v>
+        <v>-3.387573964497042e-08</v>
       </c>
       <c r="D23" t="n">
-        <v>5.092990781990424e-05</v>
+        <v>1.297456042075141e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.871071663379356e-08</v>
+        <v>-3.387573964497042e-08</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.18536468220571e-05</v>
+        <v>-2.020275953489583e-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9.375082182774491e-08</v>
+        <v>9.368836291913213e-08</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00508583377029512</v>
+        <v>0.005103759888794233</v>
       </c>
       <c r="C24" t="n">
-        <v>-2.809533201840895e-08</v>
+        <v>-3.323471400394478e-08</v>
       </c>
       <c r="D24" t="n">
-        <v>9.722316674147504e-05</v>
+        <v>2.554083723738843e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.809533201840895e-08</v>
+        <v>-3.323471400394478e-08</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.926357268515415e-05</v>
+        <v>-4.307268383411941e-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9.990466798159107e-08</v>
+        <v>1.000986193293885e-07</v>
       </c>
       <c r="B25" t="n">
-        <v>0.003595892838674382</v>
+        <v>0.003556818231724975</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.747994740302433e-08</v>
+        <v>-3.259368836291913e-08</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001435164256630459</v>
+        <v>3.810711405402559e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.747994740302433e-08</v>
+        <v>-3.259368836291913e-08</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.118297116727932e-05</v>
+        <v>-6.579238375437684e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.060585141354372e-07</v>
+        <v>1.06508875739645e-07</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002542443558173824</v>
+        <v>0.002478752176666358</v>
       </c>
       <c r="C26" t="n">
-        <v>-2.686456278763971e-08</v>
+        <v>-3.195266272189349e-08</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001898096845846167</v>
+        <v>5.067339087066275e-06</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.686456278763971e-08</v>
+        <v>-3.195266272189349e-08</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.120168474475419e-05</v>
+        <v>-8.558529851278489e-05</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>1.122123602892834e-07</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.001797611757774885</v>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-2.62491781722551e-08</v>
+        <v>-3.131163708086785e-08</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002361029435061875</v>
+        <v>6.323966768729978e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.62491781722551e-08</v>
+        <v>-3.131163708086785e-08</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.290955589390045e-05</v>
+        <v>-9.967486732646046e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-2.563379355687048e-08</v>
+        <v>-3.067061143984222e-08</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002823962024277582</v>
+        <v>7.58059445039368e-06</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.563379355687048e-08</v>
+        <v>-3.067061143984222e-08</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.989642709103952e-05</v>
+        <v>-0.0001052845294125209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-2.501840894148587e-08</v>
+        <v>-3.002958579881657e-08</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0003286894613493288</v>
+        <v>8.837222132057396e-06</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.501840894148587e-08</v>
+        <v>-3.002958579881657e-08</v>
       </c>
       <c r="F29" t="n">
-        <v>2.424785918750632e-05</v>
+        <v>-9.963772398808316e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-2.440302432610125e-08</v>
+        <v>-2.938856015779093e-08</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0003749827202708996</v>
+        <v>1.00938498137211e-05</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.440302432610125e-08</v>
+        <v>-2.938856015779093e-08</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0001259334604654163</v>
+        <v>-7.995789027026435e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-2.378763971071664e-08</v>
+        <v>-2.874753451676529e-08</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004212759791924704</v>
+        <v>1.135047749538481e-05</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.378763971071664e-08</v>
+        <v>-2.874753451676529e-08</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0002715705342663685</v>
+        <v>-4.346846747618137e-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-2.317225509533202e-08</v>
+        <v>-2.810650887573965e-08</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004675692381140412</v>
+        <v>1.260710517704852e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.317225509533202e-08</v>
+        <v>-2.810650887573965e-08</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0004675692381140412</v>
+        <v>1.260710517704852e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-2.255687047994741e-08</v>
+        <v>-2.746548323471401e-08</v>
       </c>
       <c r="D33" t="n">
-        <v>0.002019467271997894</v>
+        <v>0.0001317323941421639</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.255687047994741e-08</v>
+        <v>-2.746548323471401e-08</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0007297185985246959</v>
+        <v>8.99878040209399e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>-2.194148586456279e-08</v>
+        <v>-2.682445759368837e-08</v>
       </c>
       <c r="D34" t="n">
-        <v>0.003571365305881748</v>
+        <v>0.0002508576831072792</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.194148586456279e-08</v>
+        <v>-2.682445759368837e-08</v>
       </c>
       <c r="F34" t="n">
-        <v>0.001111323117984926</v>
+        <v>0.0001861622675815333</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-2.132610124917817e-08</v>
+        <v>-2.618343195266273e-08</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0051232633397656</v>
+        <v>0.0003699829720723945</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.132610124917817e-08</v>
+        <v>-2.618343195266273e-08</v>
       </c>
       <c r="F35" t="n">
-        <v>0.001675066167973907</v>
+        <v>0.0002975615499335008</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-2.071071663379356e-08</v>
+        <v>-2.554240631163708e-08</v>
       </c>
       <c r="D36" t="n">
-        <v>0.006675161373649454</v>
+        <v>0.0004891082610375098</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.071071663379356e-08</v>
+        <v>-2.554240631163708e-08</v>
       </c>
       <c r="F36" t="n">
-        <v>0.002483631119970815</v>
+        <v>0.0004206167051515144</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-2.009533201840894e-08</v>
+        <v>-2.490138067061144e-08</v>
       </c>
       <c r="D37" t="n">
-        <v>0.008227059407533308</v>
+        <v>0.0006082335500026252</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.009533201840894e-08</v>
+        <v>-2.490138067061144e-08</v>
       </c>
       <c r="F37" t="n">
-        <v>0.003599701345454825</v>
+        <v>0.0005517587873102465</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-1.947994740302433e-08</v>
+        <v>-2.42603550295858e-08</v>
       </c>
       <c r="D38" t="n">
-        <v>0.009778957441417161</v>
+        <v>0.0007273588389677404</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.947994740302433e-08</v>
+        <v>-2.42603550295858e-08</v>
       </c>
       <c r="F38" t="n">
-        <v>0.005085960215905115</v>
+        <v>0.0006874188504843687</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>-1.886456278763971e-08</v>
+        <v>-2.361932938856016e-08</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01133085547530101</v>
+        <v>0.0008464841279328558</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.886456278763971e-08</v>
+        <v>-2.361932938856016e-08</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00700509110280086</v>
+        <v>0.0008240279487485532</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-1.82491781722551e-08</v>
+        <v>-2.297830374753452e-08</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01288275350918486</v>
+        <v>0.0009656094168979711</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.82491781722551e-08</v>
+        <v>-2.297830374753452e-08</v>
       </c>
       <c r="F40" t="n">
-        <v>0.009419777377621223</v>
+        <v>0.000958017136177472</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-1.763379355687048e-08</v>
+        <v>-2.233727810650888e-08</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01443465154306871</v>
+        <v>0.001084734705863086</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.763379355687048e-08</v>
+        <v>-2.233727810650888e-08</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0123927024118454</v>
+        <v>0.001085817466845797</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-2.169625246548324e-08</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.001203859994828202</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-2.169625246548324e-08</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.001203859994828202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-1.640302432610125e-08</v>
+        <v>-2.10552268244576e-08</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0329202506642956</v>
+        <v>0.004638508006823489</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.640302432610125e-08</v>
+        <v>-2.10552268244576e-08</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02034945972472026</v>
+        <v>0.001343063676290783</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>-1.578763971071664e-08</v>
+        <v>-2.041420118343196e-08</v>
       </c>
       <c r="D44" t="n">
-        <v>0.04985395175163863</v>
+        <v>0.008073156018818778</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.578763971071664e-08</v>
+        <v>-2.041420118343196e-08</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02597140362811955</v>
+        <v>0.001672299075765347</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-1.517225509533202e-08</v>
+        <v>-1.977317554240632e-08</v>
       </c>
       <c r="D45" t="n">
-        <v>0.06678765283898166</v>
+        <v>0.01150780403081407</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.517225509533202e-08</v>
+        <v>-1.977317554240632e-08</v>
       </c>
       <c r="F45" t="n">
-        <v>0.03342780954041986</v>
+        <v>0.002394924659875125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-1.45568704799474e-08</v>
+        <v>-1.913214990138068e-08</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08372135392632468</v>
+        <v>0.01494245204280935</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.45568704799474e-08</v>
+        <v>-1.913214990138068e-08</v>
       </c>
       <c r="F46" t="n">
-        <v>0.04329410571489062</v>
+        <v>0.003714298895243349</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-1.394148586456279e-08</v>
+        <v>-1.849112426035503e-08</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1006550550136677</v>
+        <v>0.01837710005480464</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.394148586456279e-08</v>
+        <v>-1.849112426035503e-08</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05614572040480127</v>
+        <v>0.00583378024849325</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-1.332610124917817e-08</v>
+        <v>-1.785009861932939e-08</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1175887561010107</v>
+        <v>0.02181174806679993</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.332610124917817e-08</v>
+        <v>-1.785009861932939e-08</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07255808186342123</v>
+        <v>0.008956727186248062</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-1.271071663379356e-08</v>
+        <v>-1.720907297830375e-08</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1345224571883538</v>
+        <v>0.02524639607879521</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.271071663379356e-08</v>
+        <v>-1.720907297830375e-08</v>
       </c>
       <c r="F49" t="n">
-        <v>0.09310661834401994</v>
+        <v>0.01328649817513101</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-1.209533201840894e-08</v>
+        <v>-1.656804733727811e-08</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1514561582756968</v>
+        <v>0.02868104409079052</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.209533201840894e-08</v>
+        <v>-1.656804733727811e-08</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1183667580998668</v>
+        <v>0.01902645168176538</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-1.147994740302433e-08</v>
+        <v>-1.592702169625247e-08</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1683898593630398</v>
+        <v>0.0321156921027858</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.147994740302433e-08</v>
+        <v>-1.592702169625247e-08</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1489139293842313</v>
+        <v>0.02637994617277428</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.03555034011478109</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.03555034011478109</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>-1.024917817225509e-08</v>
+        <v>-1.464497041420119e-08</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2396318221284143</v>
+        <v>0.06446055283913779</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.024917817225509e-08</v>
+        <v>-1.464497041420119e-08</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2279010363539921</v>
+        <v>0.04679372182977039</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-9.633793556870478e-09</v>
+        <v>-1.400394477317555e-08</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2939400838064458</v>
+        <v>0.09337076556349479</v>
       </c>
       <c r="E54" t="n">
-        <v>-9.633793556870478e-09</v>
+        <v>-1.400394477317555e-08</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2758715693603346</v>
+        <v>0.06057709906117316</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-9.018408941485862e-09</v>
+        <v>-1.336291913214991e-08</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3482483454844773</v>
+        <v>0.1222809782878515</v>
       </c>
       <c r="E55" t="n">
-        <v>-9.018408941485862e-09</v>
+        <v>-1.336291913214991e-08</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3281903285370875</v>
+        <v>0.07742020940778141</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-8.403024326101253e-09</v>
+        <v>-1.272189349112426e-08</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4025566071625081</v>
+        <v>0.1511911910122085</v>
       </c>
       <c r="E56" t="n">
-        <v>-8.403024326101253e-09</v>
+        <v>-1.272189349112426e-08</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3838124829519267</v>
+        <v>0.09784279046838777</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-7.787639710716637e-09</v>
+        <v>-1.208086785009863e-08</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4568648688405396</v>
+        <v>0.1801014037365652</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.787639710716637e-09</v>
+        <v>-1.208086785009863e-08</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4416932016725303</v>
+        <v>0.1223645798417841</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-7.172255095332021e-09</v>
+        <v>-1.143984220907298e-08</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5111731305185711</v>
+        <v>0.2090116164609221</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.172255095332021e-09</v>
+        <v>-1.143984220907298e-08</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5007876537665746</v>
+        <v>0.1515053151267632</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-6.556870479947405e-09</v>
+        <v>-1.079881656804734e-08</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5654813921966024</v>
+        <v>0.2379218291852788</v>
       </c>
       <c r="E59" t="n">
-        <v>-6.556870479947405e-09</v>
+        <v>-1.079881656804734e-08</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5600510083017367</v>
+        <v>0.1857847339221168</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-5.94148586456279e-09</v>
+        <v>-1.01577909270217e-08</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6197896538746339</v>
+        <v>0.2668320419096359</v>
       </c>
       <c r="E60" t="n">
-        <v>-5.94148586456279e-09</v>
+        <v>-1.01577909270217e-08</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6184384343456931</v>
+        <v>0.2257225738266377</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-5.326101249178174e-09</v>
+        <v>-9.516765285996062e-09</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6740979155526654</v>
+        <v>0.2957422546339926</v>
       </c>
       <c r="E61" t="n">
-        <v>-5.326101249178174e-09</v>
+        <v>-9.516765285996062e-09</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6749051009661208</v>
+        <v>0.2718385724391176</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="D62" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.3246524673583495</v>
       </c>
       <c r="E62" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.3246524673583495</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-4.095332018408942e-09</v>
+        <v>-8.23471400394478e-09</v>
       </c>
       <c r="D63" t="n">
-        <v>0.752635260843327</v>
+        <v>0.3838727561957171</v>
       </c>
       <c r="E63" t="n">
-        <v>-4.095332018408942e-09</v>
+        <v>-8.23471400394478e-09</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7779970825552612</v>
+        <v>0.3842653335537005</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-3.479947403024326e-09</v>
+        <v>-7.593688362919136e-09</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7768643444559571</v>
+        <v>0.4430930450330853</v>
       </c>
       <c r="E64" t="n">
-        <v>-3.479947403024326e-09</v>
+        <v>-7.593688362919136e-09</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8231342377483085</v>
+        <v>0.4491035954768428</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-2.864562787639711e-09</v>
+        <v>-6.952662721893498e-09</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8010934280685872</v>
+        <v>0.502313333870453</v>
       </c>
       <c r="E65" t="n">
-        <v>-2.864562787639711e-09</v>
+        <v>-6.952662721893498e-09</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8633743139664963</v>
+        <v>0.5171750149500214</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-2.249178172255095e-09</v>
+        <v>-6.311637080867854e-09</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8253225116812173</v>
+        <v>0.5615336227078211</v>
       </c>
       <c r="E66" t="n">
-        <v>-2.249178172255095e-09</v>
+        <v>-6.311637080867854e-09</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8982739823664824</v>
+        <v>0.5864873537954844</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-1.633793556870479e-09</v>
+        <v>-5.67061143984221e-09</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8495515952938474</v>
+        <v>0.6207539115451894</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.633793556870479e-09</v>
+        <v>-5.67061143984221e-09</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9273899141049244</v>
+        <v>0.6550483738354778</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>-1.018408941485863e-09</v>
+        <v>-5.029585798816572e-09</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8737806789064775</v>
+        <v>0.6799742003825571</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.018408941485863e-09</v>
+        <v>-5.029585798816572e-09</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9502787803384803</v>
+        <v>0.7208658368922475</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-4.030243261012473e-10</v>
+        <v>-4.388560157790928e-09</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8980097625191075</v>
+        <v>0.7391944892199253</v>
       </c>
       <c r="E69" t="n">
-        <v>-4.030243261012473e-10</v>
+        <v>-4.388560157790928e-09</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9664972522238078</v>
+        <v>0.7819475047880411</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>2.123602892833685e-10</v>
+        <v>-3.74753451676529e-09</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9222388461317377</v>
+        <v>0.7984147780572928</v>
       </c>
       <c r="E70" t="n">
-        <v>2.123602892833685e-10</v>
+        <v>-3.74753451676529e-09</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9756020009175648</v>
+        <v>0.8363011393451045</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>8.277449046679843e-10</v>
+        <v>-3.106508875739646e-09</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9464679297443677</v>
+        <v>0.8576350668946611</v>
       </c>
       <c r="E71" t="n">
-        <v>8.277449046679843e-10</v>
+        <v>-3.106508875739646e-09</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9771496975764087</v>
+        <v>0.8819345023856852</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.4431295200526e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9706970133569972</v>
+        <v>0.9168553557320287</v>
       </c>
       <c r="E72" t="n">
-        <v>1.4431295200526e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9706970133569974</v>
+        <v>0.9168553557320287</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>2.058514135437216e-09</v>
+        <v>-1.824457593688364e-09</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9388108676622282</v>
+        <v>0.9052435604505066</v>
       </c>
       <c r="E73" t="n">
-        <v>2.058514135437216e-09</v>
+        <v>-1.824457593688364e-09</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9560838380950746</v>
+        <v>0.9396336151523926</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>2.673898750821832e-09</v>
+        <v>-1.183431952662727e-09</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9069247219674591</v>
+        <v>0.8936317651689847</v>
       </c>
       <c r="E74" t="n">
-        <v>2.673898750821832e-09</v>
+        <v>-1.183431952662727e-09</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9342829363427267</v>
+        <v>0.9510878121990735</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>3.289283366206448e-09</v>
+        <v>-5.424063116370826e-10</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8750385762726901</v>
+        <v>0.8820199698874627</v>
       </c>
       <c r="E75" t="n">
-        <v>3.289283366206448e-09</v>
+        <v>-5.424063116370826e-10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9065502913311259</v>
+        <v>0.9525986323703789</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>3.904667981591063e-09</v>
+        <v>9.861932938855505e-11</v>
       </c>
       <c r="D76" t="n">
-        <v>0.843152430577921</v>
+        <v>0.8704081746059407</v>
       </c>
       <c r="E76" t="n">
-        <v>3.904667981591063e-09</v>
+        <v>9.861932938855505e-11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8741418862914443</v>
+        <v>0.945546761164616</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>4.520052596975673e-09</v>
+        <v>7.396449704141993e-10</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8112662848831523</v>
+        <v>0.8587963793244187</v>
       </c>
       <c r="E77" t="n">
-        <v>4.520052596975673e-09</v>
+        <v>7.396449704141993e-10</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8383137044548549</v>
+        <v>0.9313128840800919</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>5.135437212360288e-09</v>
+        <v>1.380670611439837e-09</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7793801391883832</v>
+        <v>0.8471845840428966</v>
       </c>
       <c r="E78" t="n">
-        <v>5.135437212360288e-09</v>
+        <v>1.380670611439837e-09</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8003217290525287</v>
+        <v>0.9112776866151142</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>5.750821827744904e-09</v>
+        <v>2.021696252465481e-09</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7474939934936142</v>
+        <v>0.8355727887613746</v>
       </c>
       <c r="E79" t="n">
-        <v>5.750821827744904e-09</v>
+        <v>2.021696252465481e-09</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7614219433156388</v>
+        <v>0.8868218542679894</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>6.36620644312952e-09</v>
+        <v>2.662721893491119e-09</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7156078477988452</v>
+        <v>0.8239609934798526</v>
       </c>
       <c r="E80" t="n">
-        <v>6.36620644312952e-09</v>
+        <v>2.662721893491119e-09</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7228703304753569</v>
+        <v>0.8593260725370258</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>6.981591058514136e-09</v>
+        <v>3.303747534516763e-09</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6837217021040762</v>
+        <v>0.8123491981983306</v>
       </c>
       <c r="E81" t="n">
-        <v>6.981591058514136e-09</v>
+        <v>3.303747534516763e-09</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6859228737628557</v>
+        <v>0.8301710269205296</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.8007374029168086</v>
       </c>
       <c r="E82" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.8007374029168086</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>8.212360289283367e-09</v>
+        <v>4.585798816568045e-09</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6327394451314969</v>
+        <v>0.7764671772021323</v>
       </c>
       <c r="E83" t="n">
-        <v>8.212360289283367e-09</v>
+        <v>4.585798816568045e-09</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6215806497310407</v>
+        <v>0.7721690910087301</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>8.827744904667983e-09</v>
+        <v>5.226824457593682e-09</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6136433338536869</v>
+        <v>0.7521969514874564</v>
       </c>
       <c r="E84" t="n">
-        <v>8.827744904667983e-09</v>
+        <v>5.226824457593682e-09</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5949955773850139</v>
+        <v>0.7446628016174026</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>9.443129520052599e-09</v>
+        <v>5.867850098619327e-09</v>
       </c>
       <c r="D85" t="n">
-        <v>0.5945472225758767</v>
+        <v>0.7279267257727801</v>
       </c>
       <c r="E85" t="n">
-        <v>9.443129520052599e-09</v>
+        <v>5.867850098619327e-09</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5716340511133418</v>
+        <v>0.7181784501484944</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1.005851413543721e-08</v>
+        <v>6.508875739644964e-09</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5754511112980665</v>
+        <v>0.7036565000581041</v>
       </c>
       <c r="E86" t="n">
-        <v>1.005851413543721e-08</v>
+        <v>6.508875739644964e-09</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5510497826581388</v>
+        <v>0.6926759520076745</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.067389875082183e-08</v>
+        <v>7.149901380670608e-09</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5563550000202564</v>
+        <v>0.6793862743434278</v>
       </c>
       <c r="E87" t="n">
-        <v>1.067389875082183e-08</v>
+        <v>7.149901380670608e-09</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5327964837615201</v>
+        <v>0.6681152226006112</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1.128928336620645e-08</v>
+        <v>7.790927021696246e-09</v>
       </c>
       <c r="D88" t="n">
-        <v>0.5372588887424462</v>
+        <v>0.6551160486287518</v>
       </c>
       <c r="E88" t="n">
-        <v>1.128928336620645e-08</v>
+        <v>7.790927021696246e-09</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5164278661656001</v>
+        <v>0.6444561773329734</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.190466798159106e-08</v>
+        <v>8.43195266272189e-09</v>
       </c>
       <c r="D89" t="n">
-        <v>0.518162777464636</v>
+        <v>0.6308458229140755</v>
       </c>
       <c r="E89" t="n">
-        <v>1.190466798159106e-08</v>
+        <v>8.43195266272189e-09</v>
       </c>
       <c r="F89" t="n">
-        <v>0.501497641612494</v>
+        <v>0.6216587316104294</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1.252005259697568e-08</v>
+        <v>9.072978303747528e-09</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4990666661868259</v>
+        <v>0.6065755971993996</v>
       </c>
       <c r="E90" t="n">
-        <v>1.252005259697568e-08</v>
+        <v>9.072978303747528e-09</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4875595218443164</v>
+        <v>0.599682800838648</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.313543721236029e-08</v>
+        <v>9.714003944773172e-09</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4799705549090157</v>
+        <v>0.5823053714847233</v>
       </c>
       <c r="E91" t="n">
-        <v>1.313543721236029e-08</v>
+        <v>9.714003944773172e-09</v>
       </c>
       <c r="F91" t="n">
-        <v>0.474167218603182</v>
+        <v>0.5784883004232978</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.5580351457700473</v>
       </c>
       <c r="E92" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="F92" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.5580351457700473</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.436620644312953e-08</v>
+        <v>1.099605522682445e-08</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4473727106033835</v>
+        <v>0.5411211875919648</v>
       </c>
       <c r="E93" t="n">
-        <v>1.436620644312953e-08</v>
+        <v>1.099605522682445e-08</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4473255284518747</v>
+        <v>0.5382866888431541</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1.498159105851414e-08</v>
+        <v>1.163708086785009e-08</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4338709775755614</v>
+        <v>0.5242072294138824</v>
       </c>
       <c r="E94" t="n">
-        <v>1.498159105851414e-08</v>
+        <v>1.163708086785009e-08</v>
       </c>
       <c r="F94" t="n">
-        <v>0.433527283714167</v>
+        <v>0.5192200278412328</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.559697567389876e-08</v>
+        <v>1.227810650887574e-08</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4203692445477393</v>
+        <v>0.5072932712358</v>
       </c>
       <c r="E95" t="n">
-        <v>1.559697567389876e-08</v>
+        <v>1.227810650887574e-08</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4195771398484329</v>
+        <v>0.5008156975214859</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1.621236028928337e-08</v>
+        <v>1.291913214990137e-08</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4068675115199172</v>
+        <v>0.4903793130577176</v>
       </c>
       <c r="E96" t="n">
-        <v>1.621236028928337e-08</v>
+        <v>1.291913214990137e-08</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4055725272850227</v>
+        <v>0.4830542326411174</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.682774490466799e-08</v>
+        <v>1.356015779092701e-08</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3933657784920951</v>
+        <v>0.4734653548796353</v>
       </c>
       <c r="E97" t="n">
-        <v>1.682774490466799e-08</v>
+        <v>1.356015779092701e-08</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3916108764542869</v>
+        <v>0.46591616795733</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1.74431295200526e-08</v>
+        <v>1.420118343195266e-08</v>
       </c>
       <c r="D98" t="n">
-        <v>0.379864045464273</v>
+        <v>0.4565513967015526</v>
       </c>
       <c r="E98" t="n">
-        <v>1.74431295200526e-08</v>
+        <v>1.420118343195266e-08</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3777896177865757</v>
+        <v>0.4493820382273268</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.805851413543722e-08</v>
+        <v>1.48422090729783e-08</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3663623124364509</v>
+        <v>0.4396374385234703</v>
       </c>
       <c r="E99" t="n">
-        <v>1.805851413543722e-08</v>
+        <v>1.48422090729783e-08</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3642061817122395</v>
+        <v>0.4334323782083114</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1.867389875082184e-08</v>
+        <v>1.548323471400394e-08</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3528605794086288</v>
+        <v>0.422723480345388</v>
       </c>
       <c r="E100" t="n">
-        <v>1.867389875082184e-08</v>
+        <v>1.548323471400394e-08</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3509579986616286</v>
+        <v>0.4180477226574869</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.928928336620645e-08</v>
+        <v>1.612426035502959e-08</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3393588463808067</v>
+        <v>0.4058095221673053</v>
       </c>
       <c r="E101" t="n">
-        <v>1.928928336620645e-08</v>
+        <v>1.612426035502959e-08</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3381424990650935</v>
+        <v>0.4032086063320561</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.388895563989223</v>
       </c>
       <c r="E102" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.388895563989223</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>2.052005259697568e-08</v>
+        <v>1.740631163708086e-08</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3163108349456937</v>
+        <v>0.3771082001380114</v>
       </c>
       <c r="E103" t="n">
-        <v>2.052005259697568e-08</v>
+        <v>1.740631163708086e-08</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3141760720703797</v>
+        <v>0.375089735455479</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>2.11354372123603e-08</v>
+        <v>1.80473372781065e-08</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3067645565384028</v>
+        <v>0.3653208362867997</v>
       </c>
       <c r="E104" t="n">
-        <v>2.11354372123603e-08</v>
+        <v>1.80473372781065e-08</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3030808062212677</v>
+        <v>0.3617746808344706</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>2.175082182774492e-08</v>
+        <v>1.868836291913215e-08</v>
       </c>
       <c r="D105" t="n">
-        <v>0.297218278131112</v>
+        <v>0.3535334724355879</v>
       </c>
       <c r="E105" t="n">
-        <v>2.175082182774492e-08</v>
+        <v>1.868836291913215e-08</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2925295469243648</v>
+        <v>0.3489345652991328</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>2.236620644312953e-08</v>
+        <v>1.932938856015779e-08</v>
       </c>
       <c r="D106" t="n">
-        <v>0.2876719997238211</v>
+        <v>0.3417461085843763</v>
       </c>
       <c r="E106" t="n">
-        <v>2.236620644312953e-08</v>
+        <v>1.932938856015779e-08</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2824805252983875</v>
+        <v>0.3365535540224012</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>2.298159105851415e-08</v>
+        <v>1.997041420118343e-08</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2781257213165302</v>
+        <v>0.3299587447331647</v>
       </c>
       <c r="E107" t="n">
-        <v>2.298159105851415e-08</v>
+        <v>1.997041420118343e-08</v>
       </c>
       <c r="F107" t="n">
-        <v>0.272891972462052</v>
+        <v>0.3246158121772108</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>2.359697567389876e-08</v>
+        <v>2.061143984220906e-08</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2685794429092394</v>
+        <v>0.3181713808819531</v>
       </c>
       <c r="E108" t="n">
-        <v>2.359697567389876e-08</v>
+        <v>2.061143984220906e-08</v>
       </c>
       <c r="F108" t="n">
-        <v>0.2637221195340749</v>
+        <v>0.3131055049364967</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2.421236028928337e-08</v>
+        <v>2.125246548323472e-08</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2590331645019487</v>
+        <v>0.3063840170307412</v>
       </c>
       <c r="E109" t="n">
-        <v>2.421236028928337e-08</v>
+        <v>2.125246548323472e-08</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2549291976331725</v>
+        <v>0.3020067974731938</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2.482774490466798e-08</v>
+        <v>2.189349112426035e-08</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2494868860946579</v>
+        <v>0.2945966531795296</v>
       </c>
       <c r="E110" t="n">
-        <v>2.482774490466798e-08</v>
+        <v>2.189349112426035e-08</v>
       </c>
       <c r="F110" t="n">
-        <v>0.246471437878061</v>
+        <v>0.2913038549602379</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>2.54431295200526e-08</v>
+        <v>2.253451676528599e-08</v>
       </c>
       <c r="D111" t="n">
-        <v>0.239940607687367</v>
+        <v>0.2828092893283179</v>
       </c>
       <c r="E111" t="n">
-        <v>2.54431295200526e-08</v>
+        <v>2.253451676528599e-08</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2383070713874567</v>
+        <v>0.2809808425705635</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.2710219254771064</v>
       </c>
       <c r="E112" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.2710219254771064</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>2.667389875082183e-08</v>
+        <v>2.381656804733728e-08</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2236447193417283</v>
+        <v>0.2628072932131518</v>
       </c>
       <c r="E113" t="n">
-        <v>2.667389875082183e-08</v>
+        <v>2.381656804733728e-08</v>
       </c>
       <c r="F113" t="n">
-        <v>0.222698423809131</v>
+        <v>0.2614121701217584</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>2.728928336620644e-08</v>
+        <v>2.445759368836292e-08</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2168951094033804</v>
+        <v>0.2545926609491974</v>
       </c>
       <c r="E114" t="n">
-        <v>2.728928336620644e-08</v>
+        <v>2.445759368836292e-08</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2152124917658149</v>
+        <v>0.2521402480222421</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>2.790466798159106e-08</v>
+        <v>2.509861932938855e-08</v>
       </c>
       <c r="D115" t="n">
-        <v>0.2101454994650326</v>
+        <v>0.246378028685243</v>
       </c>
       <c r="E115" t="n">
-        <v>2.790466798159106e-08</v>
+        <v>2.509861932938855e-08</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2079366510758167</v>
+        <v>0.2431957319652366</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>2.852005259697568e-08</v>
+        <v>2.573964497041419e-08</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2033958895266847</v>
+        <v>0.2381633964212886</v>
       </c>
       <c r="E116" t="n">
-        <v>2.852005259697568e-08</v>
+        <v>2.573964497041419e-08</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2008710196648252</v>
+        <v>0.2345681947374211</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>2.913543721236029e-08</v>
+        <v>2.638067061143984e-08</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1966462795883368</v>
+        <v>0.229948764157334</v>
       </c>
       <c r="E117" t="n">
-        <v>2.913543721236029e-08</v>
+        <v>2.638067061143984e-08</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1940157154585294</v>
+        <v>0.2262472091254749</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>2.975082182774491e-08</v>
+        <v>2.702169625246548e-08</v>
       </c>
       <c r="D118" t="n">
-        <v>0.189896669649989</v>
+        <v>0.2217341318933796</v>
       </c>
       <c r="E118" t="n">
-        <v>2.975082182774491e-08</v>
+        <v>2.702169625246548e-08</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1873708563826182</v>
+        <v>0.2182223479160776</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>3.036620644312952e-08</v>
+        <v>2.766272189349112e-08</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1831470597116411</v>
+        <v>0.2135194996294252</v>
       </c>
       <c r="E119" t="n">
-        <v>3.036620644312952e-08</v>
+        <v>2.766272189349112e-08</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1809365603627805</v>
+        <v>0.2104831838959083</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>3.098159105851414e-08</v>
+        <v>2.830374753451676e-08</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1763974497732932</v>
+        <v>0.2053048673654708</v>
       </c>
       <c r="E120" t="n">
-        <v>3.098159105851414e-08</v>
+        <v>2.830374753451676e-08</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1747129453247052</v>
+        <v>0.2030192898516464</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>3.159697567389875e-08</v>
+        <v>2.894477317554241e-08</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1696478398349454</v>
+        <v>0.1970902351015162</v>
       </c>
       <c r="E121" t="n">
-        <v>3.159697567389875e-08</v>
+        <v>2.894477317554241e-08</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1687001291940813</v>
+        <v>0.1958202385699711</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1888756028375619</v>
       </c>
       <c r="E122" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="F122" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1888756028375619</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>3.282774490466799e-08</v>
+        <v>3.022682445759368e-08</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1581259791433563</v>
+        <v>0.1831508127925796</v>
       </c>
       <c r="E123" t="n">
-        <v>3.282774490466799e-08</v>
+        <v>3.022682445759368e-08</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1573060354739111</v>
+        <v>0.1821754550296932</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>3.34431295200526e-08</v>
+        <v>3.086785009861932e-08</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1533537283901151</v>
+        <v>0.1774260227475973</v>
       </c>
       <c r="E124" t="n">
-        <v>3.34431295200526e-08</v>
+        <v>3.086785009861932e-08</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1519170144315516</v>
+        <v>0.1757118658760202</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>3.405851413543722e-08</v>
+        <v>3.150887573964497e-08</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1485814776368738</v>
+        <v>0.1717012327026148</v>
       </c>
       <c r="E125" t="n">
-        <v>3.405851413543722e-08</v>
+        <v>3.150887573964497e-08</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1467233053910169</v>
+        <v>0.1694774056947934</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>3.467389875082183e-08</v>
+        <v>3.214990138067061e-08</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1438092268836326</v>
+        <v>0.1659764426576326</v>
       </c>
       <c r="E126" t="n">
-        <v>3.467389875082183e-08</v>
+        <v>3.214990138067061e-08</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1417170469738047</v>
+        <v>0.1634646448042634</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>3.528928336620645e-08</v>
+        <v>3.279092702169624e-08</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1390369761303914</v>
+        <v>0.1602516526126503</v>
       </c>
       <c r="E127" t="n">
-        <v>3.528928336620645e-08</v>
+        <v>3.279092702169624e-08</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1368903778014131</v>
+        <v>0.1576661535226805</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>3.590466798159107e-08</v>
+        <v>3.343195266272188e-08</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1342647253771502</v>
+        <v>0.154526862567668</v>
       </c>
       <c r="E128" t="n">
-        <v>3.590466798159107e-08</v>
+        <v>3.343195266272188e-08</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1322354364953397</v>
+        <v>0.1520745021682952</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>3.652005259697568e-08</v>
+        <v>3.407297830374753e-08</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1294924746239089</v>
+        <v>0.1488020725226855</v>
       </c>
       <c r="E129" t="n">
-        <v>3.652005259697568e-08</v>
+        <v>3.407297830374753e-08</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1277443616770824</v>
+        <v>0.1466822610593578</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>3.71354372123603e-08</v>
+        <v>3.471400394477317e-08</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1247202238706677</v>
+        <v>0.1430772824777032</v>
       </c>
       <c r="E130" t="n">
-        <v>3.71354372123603e-08</v>
+        <v>3.471400394477317e-08</v>
       </c>
       <c r="F130" t="n">
-        <v>0.123409291968139</v>
+        <v>0.141482000514119</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>3.775082182774491e-08</v>
+        <v>3.535502958579881e-08</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1199479731174265</v>
+        <v>0.137352492432721</v>
       </c>
       <c r="E131" t="n">
-        <v>3.775082182774491e-08</v>
+        <v>3.535502958579881e-08</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1192223659900074</v>
+        <v>0.1364662908508291</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>3.599605522682446e-08</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.1316277023877386</v>
       </c>
       <c r="E132" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>3.599605522682446e-08</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.1316277023877385</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>3.898159105851414e-08</v>
+        <v>3.66370808678501e-08</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1118015455658463</v>
+        <v>0.1276380872709504</v>
       </c>
       <c r="E133" t="n">
-        <v>3.898159105851414e-08</v>
+        <v>3.66370808678501e-08</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1112622383543389</v>
+        <v>0.1269591880405349</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>3.959697567389876e-08</v>
+        <v>3.727810650887573e-08</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1084273687675074</v>
+        <v>0.1236484721541622</v>
       </c>
       <c r="E134" t="n">
-        <v>3.959697567389876e-08</v>
+        <v>3.727810650887573e-08</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1074777457928074</v>
+        <v>0.1224552311146533</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>4.021236028928338e-08</v>
+        <v>3.791913214990137e-08</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1050531919691684</v>
+        <v>0.119658857037374</v>
       </c>
       <c r="E135" t="n">
-        <v>4.021236028928338e-08</v>
+        <v>3.791913214990137e-08</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1038188151540984</v>
+        <v>0.1181106975129659</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>4.082774490466799e-08</v>
+        <v>3.856015779092702e-08</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1016790151708295</v>
+        <v>0.1156692419205858</v>
       </c>
       <c r="E136" t="n">
-        <v>4.082774490466799e-08</v>
+        <v>3.856015779092702e-08</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1002820169127193</v>
+        <v>0.1139204531383448</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>4.144312952005261e-08</v>
+        <v>3.920118343195266e-08</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0983048383724905</v>
+        <v>0.1116796268037976</v>
       </c>
       <c r="E137" t="n">
-        <v>4.144312952005261e-08</v>
+        <v>3.920118343195266e-08</v>
       </c>
       <c r="F137" t="n">
-        <v>0.09686392154317779</v>
+        <v>0.1098793638936624</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>4.205851413543722e-08</v>
+        <v>3.98422090729783e-08</v>
       </c>
       <c r="D138" t="n">
-        <v>0.09493066157415156</v>
+        <v>0.1076900116870094</v>
       </c>
       <c r="E138" t="n">
-        <v>4.205851413543722e-08</v>
+        <v>3.98422090729783e-08</v>
       </c>
       <c r="F138" t="n">
-        <v>0.09356109951998122</v>
+        <v>0.1059822956817909</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>4.267389875082184e-08</v>
+        <v>4.048323471400394e-08</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0915564847758126</v>
+        <v>0.1037003965702212</v>
       </c>
       <c r="E139" t="n">
-        <v>4.267389875082184e-08</v>
+        <v>4.048323471400394e-08</v>
       </c>
       <c r="F139" t="n">
-        <v>0.09037012131763722</v>
+        <v>0.1022241144056023</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>4.328928336620645e-08</v>
+        <v>4.112426035502959e-08</v>
       </c>
       <c r="D140" t="n">
-        <v>0.08818230797747365</v>
+        <v>0.09971078145343296</v>
       </c>
       <c r="E140" t="n">
-        <v>4.328928336620645e-08</v>
+        <v>4.112426035502959e-08</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0872875574106533</v>
+        <v>0.09859968596796891</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>4.390466798159107e-08</v>
+        <v>4.176528599605522e-08</v>
       </c>
       <c r="D141" t="n">
-        <v>0.08480813117913469</v>
+        <v>0.09572116633664476</v>
       </c>
       <c r="E141" t="n">
-        <v>4.390466798159107e-08</v>
+        <v>4.176528599605522e-08</v>
       </c>
       <c r="F141" t="n">
-        <v>0.08430997827353696</v>
+        <v>0.09510387627176296</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>4.452005259697569e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="D142" t="n">
-        <v>0.08143395438079574</v>
+        <v>0.09173155121985659</v>
       </c>
       <c r="E142" t="n">
-        <v>4.452005259697569e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="F142" t="n">
-        <v>0.08143395438079574</v>
+        <v>0.09173155121985659</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>4.51354372123603e-08</v>
+        <v>4.30473372781065e-08</v>
       </c>
       <c r="D143" t="n">
-        <v>0.07904827314669119</v>
+        <v>0.0889511822185417</v>
       </c>
       <c r="E143" t="n">
-        <v>4.51354372123603e-08</v>
+        <v>4.30473372781065e-08</v>
       </c>
       <c r="F143" t="n">
-        <v>0.07865612859069125</v>
+        <v>0.08847783412155956</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>4.575082182774492e-08</v>
+        <v>4.368836291913215e-08</v>
       </c>
       <c r="D144" t="n">
-        <v>0.07666259191258662</v>
+        <v>0.08617081321722676</v>
       </c>
       <c r="E144" t="n">
-        <v>4.575082182774492e-08</v>
+        <v>4.368836291913215e-08</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0759734332965014</v>
+        <v>0.08533887791193177</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>4.636620644312953e-08</v>
+        <v>4.432938856015779e-08</v>
       </c>
       <c r="D145" t="n">
-        <v>0.07427691067848205</v>
+        <v>0.08339044421591188</v>
       </c>
       <c r="E145" t="n">
-        <v>4.636620644312953e-08</v>
+        <v>4.432938856015779e-08</v>
       </c>
       <c r="F145" t="n">
-        <v>0.07338287327525818</v>
+        <v>0.08231109293247088</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>4.698159105851415e-08</v>
+        <v>4.497041420118343e-08</v>
       </c>
       <c r="D146" t="n">
-        <v>0.07189122944437748</v>
+        <v>0.08061007521459698</v>
       </c>
       <c r="E146" t="n">
-        <v>4.698159105851415e-08</v>
+        <v>4.497041420118343e-08</v>
       </c>
       <c r="F146" t="n">
-        <v>0.07088145330399363</v>
+        <v>0.07939088952467434</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>4.759697567389877e-08</v>
+        <v>4.561143984220906e-08</v>
       </c>
       <c r="D147" t="n">
-        <v>0.06950554821027291</v>
+        <v>0.07782970621328211</v>
       </c>
       <c r="E147" t="n">
-        <v>4.759697567389877e-08</v>
+        <v>4.561143984220906e-08</v>
       </c>
       <c r="F147" t="n">
-        <v>0.06846617815973972</v>
+        <v>0.07657467803003967</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>4.821236028928338e-08</v>
+        <v>4.625246548323471e-08</v>
       </c>
       <c r="D148" t="n">
-        <v>0.06711986697616834</v>
+        <v>0.07504933721196716</v>
       </c>
       <c r="E148" t="n">
-        <v>4.821236028928338e-08</v>
+        <v>4.625246548323471e-08</v>
       </c>
       <c r="F148" t="n">
-        <v>0.06613405261952848</v>
+        <v>0.07385886879006434</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>4.8827744904668e-08</v>
+        <v>4.689349112426035e-08</v>
       </c>
       <c r="D149" t="n">
-        <v>0.06473418574206379</v>
+        <v>0.07226896821065228</v>
       </c>
       <c r="E149" t="n">
-        <v>4.8827744904668e-08</v>
+        <v>4.689349112426035e-08</v>
       </c>
       <c r="F149" t="n">
-        <v>0.06388208146039188</v>
+        <v>0.07123987214624598</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>4.944312952005261e-08</v>
+        <v>4.753451676528599e-08</v>
       </c>
       <c r="D150" t="n">
-        <v>0.06234850450795922</v>
+        <v>0.06948859920933739</v>
       </c>
       <c r="E150" t="n">
-        <v>4.944312952005261e-08</v>
+        <v>4.753451676528599e-08</v>
       </c>
       <c r="F150" t="n">
-        <v>0.06170726945936196</v>
+        <v>0.06871409844008207</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>5.005851413543723e-08</v>
+        <v>4.817554240631163e-08</v>
       </c>
       <c r="D151" t="n">
-        <v>0.05996282327385465</v>
+        <v>0.06670823020802251</v>
       </c>
       <c r="E151" t="n">
-        <v>5.005851413543723e-08</v>
+        <v>4.817554240631163e-08</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0596066213934707</v>
+        <v>0.0662779580130701</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>4.881656804733728e-08</v>
       </c>
       <c r="D152" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.06392786120670758</v>
       </c>
       <c r="E152" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>4.881656804733728e-08</v>
       </c>
       <c r="F152" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.06392786120670758</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>5.128928336620645e-08</v>
+        <v>4.945759368836292e-08</v>
       </c>
       <c r="D153" t="n">
-        <v>0.05589036766753571</v>
+        <v>0.06199021771048581</v>
       </c>
       <c r="E153" t="n">
-        <v>5.128928336620645e-08</v>
+        <v>4.945759368836292e-08</v>
       </c>
       <c r="F153" t="n">
-        <v>0.05561600789493083</v>
+        <v>0.06166040022132834</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>5.190466798159106e-08</v>
+        <v>5.009861932938855e-08</v>
       </c>
       <c r="D154" t="n">
-        <v>0.05420359329532128</v>
+        <v>0.06005257421426403</v>
       </c>
       <c r="E154" t="n">
-        <v>5.190466798159106e-08</v>
+        <v>5.009861932938855e-08</v>
       </c>
       <c r="F154" t="n">
-        <v>0.05372108233453801</v>
+        <v>0.05947289469261102</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>5.252005259697568e-08</v>
+        <v>5.073964497041419e-08</v>
       </c>
       <c r="D155" t="n">
-        <v>0.05251681892310686</v>
+        <v>0.05811493071804225</v>
       </c>
       <c r="E155" t="n">
-        <v>5.252005259697568e-08</v>
+        <v>5.073964497041419e-08</v>
       </c>
       <c r="F155" t="n">
-        <v>0.05189040045379547</v>
+        <v>0.0573628461150705</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>5.313543721236029e-08</v>
+        <v>5.138067061143984e-08</v>
       </c>
       <c r="D156" t="n">
-        <v>0.05083004455089243</v>
+        <v>0.05617728722182043</v>
       </c>
       <c r="E156" t="n">
-        <v>5.313543721236029e-08</v>
+        <v>5.138067061143984e-08</v>
       </c>
       <c r="F156" t="n">
-        <v>0.05012199734792704</v>
+        <v>0.05532775598322167</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>5.375082182774491e-08</v>
+        <v>5.202169625246548e-08</v>
       </c>
       <c r="D157" t="n">
-        <v>0.04914327017867801</v>
+        <v>0.05423964372559865</v>
       </c>
       <c r="E157" t="n">
-        <v>5.375082182774491e-08</v>
+        <v>5.202169625246548e-08</v>
       </c>
       <c r="F157" t="n">
-        <v>0.04841390811215651</v>
+        <v>0.0533651257915795</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>5.436620644312953e-08</v>
+        <v>5.266272189349112e-08</v>
       </c>
       <c r="D158" t="n">
-        <v>0.04745649580646359</v>
+        <v>0.05230200022937687</v>
       </c>
       <c r="E158" t="n">
-        <v>5.436620644312953e-08</v>
+        <v>5.266272189349112e-08</v>
       </c>
       <c r="F158" t="n">
-        <v>0.04676416784170771</v>
+        <v>0.05147245703465887</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>5.498159105851414e-08</v>
+        <v>5.330374753451675e-08</v>
       </c>
       <c r="D159" t="n">
-        <v>0.04576972143424916</v>
+        <v>0.05036435673315509</v>
       </c>
       <c r="E159" t="n">
-        <v>5.498159105851414e-08</v>
+        <v>5.330374753451675e-08</v>
       </c>
       <c r="F159" t="n">
-        <v>0.04517081163180443</v>
+        <v>0.04964725120697468</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5.559697567389876e-08</v>
+        <v>5.39447731755424e-08</v>
       </c>
       <c r="D160" t="n">
-        <v>0.04408294706203474</v>
+        <v>0.04842671323693327</v>
       </c>
       <c r="E160" t="n">
-        <v>5.559697567389876e-08</v>
+        <v>5.39447731755424e-08</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0436318745776705</v>
+        <v>0.04788700980304178</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>5.621236028928337e-08</v>
+        <v>5.458579881656804e-08</v>
       </c>
       <c r="D161" t="n">
-        <v>0.04239617268982032</v>
+        <v>0.04648906974071149</v>
       </c>
       <c r="E161" t="n">
-        <v>5.621236028928337e-08</v>
+        <v>5.458579881656804e-08</v>
       </c>
       <c r="F161" t="n">
-        <v>0.04214539177452972</v>
+        <v>0.04618923431737517</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="D162" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.04455142624448971</v>
       </c>
       <c r="E162" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="F162" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.04455142624448971</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>5.744312952005261e-08</v>
+        <v>5.586785009861933e-08</v>
       </c>
       <c r="D163" t="n">
-        <v>0.0395167797304763</v>
+        <v>0.04320107946797368</v>
       </c>
       <c r="E163" t="n">
-        <v>5.744312952005261e-08</v>
+        <v>5.586785009861933e-08</v>
       </c>
       <c r="F163" t="n">
-        <v>0.03932201841582961</v>
+        <v>0.04297121315536773</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>5.805851413543722e-08</v>
+        <v>5.650887573964497e-08</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0383241611433467</v>
+        <v>0.04185073269145769</v>
       </c>
       <c r="E164" t="n">
-        <v>5.805851413543722e-08</v>
+        <v>5.650887573964497e-08</v>
       </c>
       <c r="F164" t="n">
-        <v>0.03798173273295855</v>
+        <v>0.04144672692686144</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>5.867389875082184e-08</v>
+        <v>5.714990138067061e-08</v>
       </c>
       <c r="D165" t="n">
-        <v>0.03713154255621712</v>
+        <v>0.04050038591494169</v>
       </c>
       <c r="E165" t="n">
-        <v>5.867389875082184e-08</v>
+        <v>5.714990138067061e-08</v>
       </c>
       <c r="F165" t="n">
-        <v>0.03668711104645713</v>
+        <v>0.03997622551229046</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>5.928928336620645e-08</v>
+        <v>5.779092702169624e-08</v>
       </c>
       <c r="D166" t="n">
-        <v>0.03593892396908752</v>
+        <v>0.03915003913842569</v>
       </c>
       <c r="E166" t="n">
-        <v>5.928928336620645e-08</v>
+        <v>5.779092702169624e-08</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0354367231337898</v>
+        <v>0.03855796686497438</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>5.990466798159107e-08</v>
+        <v>5.843195266272189e-08</v>
       </c>
       <c r="D167" t="n">
-        <v>0.03474630538195793</v>
+        <v>0.03779969236190966</v>
       </c>
       <c r="E167" t="n">
-        <v>5.990466798159107e-08</v>
+        <v>5.843195266272189e-08</v>
       </c>
       <c r="F167" t="n">
-        <v>0.03422913877242099</v>
+        <v>0.03719020893823282</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>6.052005259697568e-08</v>
+        <v>5.907297830374753e-08</v>
       </c>
       <c r="D168" t="n">
-        <v>0.03355368679482833</v>
+        <v>0.03644934558539367</v>
       </c>
       <c r="E168" t="n">
-        <v>6.052005259697568e-08</v>
+        <v>5.907297830374753e-08</v>
       </c>
       <c r="F168" t="n">
-        <v>0.03306292773981512</v>
+        <v>0.03587120968538542</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>6.11354372123603e-08</v>
+        <v>5.971400394477318e-08</v>
       </c>
       <c r="D169" t="n">
-        <v>0.03236106820769874</v>
+        <v>0.03509899880887766</v>
       </c>
       <c r="E169" t="n">
-        <v>6.11354372123603e-08</v>
+        <v>5.971400394477318e-08</v>
       </c>
       <c r="F169" t="n">
-        <v>0.03193665981343666</v>
+        <v>0.03459922705975178</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>6.175082182774492e-08</v>
+        <v>6.035502958579881e-08</v>
       </c>
       <c r="D170" t="n">
-        <v>0.03116844962056915</v>
+        <v>0.03374865203236166</v>
       </c>
       <c r="E170" t="n">
-        <v>6.175082182774492e-08</v>
+        <v>6.035502958579881e-08</v>
       </c>
       <c r="F170" t="n">
-        <v>0.03084890477075001</v>
+        <v>0.03337251901465153</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>6.236620644312953e-08</v>
+        <v>6.099605522682445e-08</v>
       </c>
       <c r="D171" t="n">
-        <v>0.02997583103343956</v>
+        <v>0.03239830525584567</v>
       </c>
       <c r="E171" t="n">
-        <v>6.236620644312953e-08</v>
+        <v>6.099605522682445e-08</v>
       </c>
       <c r="F171" t="n">
-        <v>0.02979823238921964</v>
+        <v>0.03218934350340429</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="D172" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.03104795847932967</v>
       </c>
       <c r="E172" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="F172" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.03104795847932967</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>6.359697567389876e-08</v>
+        <v>6.227810650887573e-08</v>
       </c>
       <c r="D173" t="n">
-        <v>0.02793998224445451</v>
+        <v>0.03010689970334602</v>
       </c>
       <c r="E173" t="n">
-        <v>6.359697567389876e-08</v>
+        <v>6.227810650887573e-08</v>
       </c>
       <c r="F173" t="n">
-        <v>0.02780248638172966</v>
+        <v>0.02994670993170339</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
-        <v>6.421236028928338e-08</v>
+        <v>6.291913214990136e-08</v>
       </c>
       <c r="D174" t="n">
-        <v>0.02709675204259905</v>
+        <v>0.02916584092736237</v>
       </c>
       <c r="E174" t="n">
-        <v>6.421236028928338e-08</v>
+        <v>6.291913214990136e-08</v>
       </c>
       <c r="F174" t="n">
-        <v>0.02685498228416429</v>
+        <v>0.02888429599362555</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
-        <v>6.482774490466799e-08</v>
+        <v>6.356015779092703e-08</v>
       </c>
       <c r="D175" t="n">
-        <v>0.02625352184074359</v>
+        <v>0.02822478215137867</v>
       </c>
       <c r="E175" t="n">
-        <v>6.482774490466799e-08</v>
+        <v>6.356015779092703e-08</v>
       </c>
       <c r="F175" t="n">
-        <v>0.02593969990454367</v>
+        <v>0.02785950283415236</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
-        <v>6.544312952005261e-08</v>
+        <v>6.420118343195267e-08</v>
       </c>
       <c r="D176" t="n">
-        <v>0.02541029163888813</v>
+        <v>0.02728372337539502</v>
       </c>
       <c r="E176" t="n">
-        <v>6.544312952005261e-08</v>
+        <v>6.420118343195267e-08</v>
       </c>
       <c r="F176" t="n">
-        <v>0.02505563899379758</v>
+        <v>0.02687111662234009</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
-        <v>6.605851413543723e-08</v>
+        <v>6.48422090729783e-08</v>
       </c>
       <c r="D177" t="n">
-        <v>0.02456706143703268</v>
+        <v>0.02634266459941137</v>
       </c>
       <c r="E177" t="n">
-        <v>6.605851413543723e-08</v>
+        <v>6.48422090729783e-08</v>
       </c>
       <c r="F177" t="n">
-        <v>0.02420179930285585</v>
+        <v>0.02591792352724492</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>6.667389875082184e-08</v>
+        <v>6.548323471400394e-08</v>
       </c>
       <c r="D178" t="n">
-        <v>0.02372383123517722</v>
+        <v>0.02540160582342772</v>
       </c>
       <c r="E178" t="n">
-        <v>6.667389875082184e-08</v>
+        <v>6.548323471400394e-08</v>
       </c>
       <c r="F178" t="n">
-        <v>0.02337718058264825</v>
+        <v>0.02499870971792307</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>6.728928336620646e-08</v>
+        <v>6.612426035502958e-08</v>
       </c>
       <c r="D179" t="n">
-        <v>0.02288060103332176</v>
+        <v>0.02446054704744407</v>
       </c>
       <c r="E179" t="n">
-        <v>6.728928336620646e-08</v>
+        <v>6.612426035502958e-08</v>
       </c>
       <c r="F179" t="n">
-        <v>0.02258078258410461</v>
+        <v>0.02411226136343074</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
-        <v>6.790466798159107e-08</v>
+        <v>6.676528599605522e-08</v>
       </c>
       <c r="D180" t="n">
-        <v>0.0220373708314663</v>
+        <v>0.02351948827146042</v>
       </c>
       <c r="E180" t="n">
-        <v>6.790466798159107e-08</v>
+        <v>6.676528599605522e-08</v>
       </c>
       <c r="F180" t="n">
-        <v>0.02181160505815471</v>
+        <v>0.02325736463282416</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>6.852005259697569e-08</v>
+        <v>6.740631163708085e-08</v>
       </c>
       <c r="D181" t="n">
-        <v>0.02119414062961084</v>
+        <v>0.02257842949547677</v>
       </c>
       <c r="E181" t="n">
-        <v>6.852005259697569e-08</v>
+        <v>6.740631163708085e-08</v>
       </c>
       <c r="F181" t="n">
-        <v>0.02106864775572838</v>
+        <v>0.02243280569515956</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="D182" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.02163737071949312</v>
       </c>
       <c r="E182" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="F182" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.02163737071949312</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>6.975082182774492e-08</v>
+        <v>6.868836291913216e-08</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01975471212848811</v>
+        <v>0.02098154538983907</v>
       </c>
       <c r="E183" t="n">
-        <v>6.975082182774492e-08</v>
+        <v>6.868836291913216e-08</v>
       </c>
       <c r="F183" t="n">
-        <v>0.01965744117165312</v>
+        <v>0.0208699071962389</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>7.036620644312954e-08</v>
+        <v>6.932938856015779e-08</v>
       </c>
       <c r="D184" t="n">
-        <v>0.01915851382922084</v>
+        <v>0.02032572006018505</v>
       </c>
       <c r="E184" t="n">
-        <v>7.036620644312954e-08</v>
+        <v>6.932938856015779e-08</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0189874814707892</v>
+        <v>0.02012950790124247</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
-        <v>7.098159105851415e-08</v>
+        <v>6.997041420118343e-08</v>
       </c>
       <c r="D185" t="n">
-        <v>0.01856231552995357</v>
+        <v>0.01966989473053103</v>
       </c>
       <c r="E185" t="n">
-        <v>7.098159105851415e-08</v>
+        <v>6.997041420118343e-08</v>
       </c>
       <c r="F185" t="n">
-        <v>0.01834032115501884</v>
+        <v>0.01941532693170714</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="n">
-        <v>7.159697567389877e-08</v>
+        <v>7.061143984220907e-08</v>
       </c>
       <c r="D186" t="n">
-        <v>0.0179661172306863</v>
+        <v>0.01901406940087701</v>
       </c>
       <c r="E186" t="n">
-        <v>7.159697567389877e-08</v>
+        <v>7.061143984220907e-08</v>
       </c>
       <c r="F186" t="n">
-        <v>0.01771525005419724</v>
+        <v>0.01872651838483628</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>7.221236028928338e-08</v>
+        <v>7.125246548323471e-08</v>
       </c>
       <c r="D187" t="n">
-        <v>0.01736991893141903</v>
+        <v>0.018358244071223</v>
       </c>
       <c r="E187" t="n">
-        <v>7.221236028928338e-08</v>
+        <v>7.125246548323471e-08</v>
       </c>
       <c r="F187" t="n">
-        <v>0.01711155799817958</v>
+        <v>0.01806223635783324</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>7.2827744904668e-08</v>
+        <v>7.189349112426034e-08</v>
       </c>
       <c r="D188" t="n">
-        <v>0.01677372063215175</v>
+        <v>0.01770241874156897</v>
       </c>
       <c r="E188" t="n">
-        <v>7.2827744904668e-08</v>
+        <v>7.189349112426034e-08</v>
       </c>
       <c r="F188" t="n">
-        <v>0.01652853481682109</v>
+        <v>0.01742163494790138</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
-        <v>7.344312952005262e-08</v>
+        <v>7.253451676528598e-08</v>
       </c>
       <c r="D189" t="n">
-        <v>0.01617752233288448</v>
+        <v>0.01704659341191496</v>
       </c>
       <c r="E189" t="n">
-        <v>7.344312952005262e-08</v>
+        <v>7.253451676528598e-08</v>
       </c>
       <c r="F189" t="n">
-        <v>0.01596547033997695</v>
+        <v>0.01680386825224406</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>7.405851413543723e-08</v>
+        <v>7.317554240631162e-08</v>
       </c>
       <c r="D190" t="n">
-        <v>0.01558132403361721</v>
+        <v>0.01639076808226093</v>
       </c>
       <c r="E190" t="n">
-        <v>7.405851413543723e-08</v>
+        <v>7.317554240631162e-08</v>
       </c>
       <c r="F190" t="n">
-        <v>0.01542165439750237</v>
+        <v>0.01620809036806463</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>7.467389875082185e-08</v>
+        <v>7.381656804733726e-08</v>
       </c>
       <c r="D191" t="n">
-        <v>0.01498512573434994</v>
+        <v>0.01573494275260692</v>
       </c>
       <c r="E191" t="n">
-        <v>7.467389875082185e-08</v>
+        <v>7.381656804733726e-08</v>
       </c>
       <c r="F191" t="n">
-        <v>0.01489637681925254</v>
+        <v>0.01563345539256646</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>7.528928336620646e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="D192" t="n">
-        <v>0.01438892743508267</v>
+        <v>0.0150791174229529</v>
       </c>
       <c r="E192" t="n">
-        <v>7.528928336620646e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="F192" t="n">
-        <v>0.01438892743508267</v>
+        <v>0.0150791174229529</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>7.590466798159108e-08</v>
+        <v>7.509861932938856e-08</v>
       </c>
       <c r="D193" t="n">
-        <v>0.01396739081167065</v>
+        <v>0.01462207172719787</v>
       </c>
       <c r="E193" t="n">
-        <v>7.590466798159108e-08</v>
+        <v>7.509861932938856e-08</v>
       </c>
       <c r="F193" t="n">
-        <v>0.013898630889213</v>
+        <v>0.01454427324245747</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
-        <v>7.65200525969757e-08</v>
+        <v>7.57396449704142e-08</v>
       </c>
       <c r="D194" t="n">
-        <v>0.01354585418825864</v>
+        <v>0.01416502603144286</v>
       </c>
       <c r="E194" t="n">
-        <v>7.65200525969757e-08</v>
+        <v>7.57396449704142e-08</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0134249510833239</v>
+        <v>0.01402829037843456</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>7.71354372123603e-08</v>
+        <v>7.638067061143983e-08</v>
       </c>
       <c r="D195" t="n">
-        <v>0.01312431756484662</v>
+        <v>0.01370798033568786</v>
       </c>
       <c r="E195" t="n">
-        <v>7.71354372123603e-08</v>
+        <v>7.638067061143983e-08</v>
       </c>
       <c r="F195" t="n">
-        <v>0.01296738673346081</v>
+        <v>0.01353057904426864</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>7.775082182774493e-08</v>
+        <v>7.702169625246547e-08</v>
       </c>
       <c r="D196" t="n">
-        <v>0.0127027809414346</v>
+        <v>0.01325093463993285</v>
       </c>
       <c r="E196" t="n">
-        <v>7.775082182774493e-08</v>
+        <v>7.702169625246547e-08</v>
       </c>
       <c r="F196" t="n">
-        <v>0.01252543655566912</v>
+        <v>0.01305054945334425</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>7.836620644312953e-08</v>
+        <v>7.766272189349111e-08</v>
       </c>
       <c r="D197" t="n">
-        <v>0.01228124431802259</v>
+        <v>0.01279388894417784</v>
       </c>
       <c r="E197" t="n">
-        <v>7.836620644312953e-08</v>
+        <v>7.766272189349111e-08</v>
       </c>
       <c r="F197" t="n">
-        <v>0.01209859926599429</v>
+        <v>0.0125876118190459</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="n">
-        <v>7.898159105851416e-08</v>
+        <v>7.830374753451675e-08</v>
       </c>
       <c r="D198" t="n">
-        <v>0.01185970769461056</v>
+        <v>0.01233684324842284</v>
       </c>
       <c r="E198" t="n">
-        <v>7.898159105851416e-08</v>
+        <v>7.830374753451675e-08</v>
       </c>
       <c r="F198" t="n">
-        <v>0.01168637358048171</v>
+        <v>0.0121411763547581</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="n">
-        <v>7.959697567389876e-08</v>
+        <v>7.894477317554238e-08</v>
       </c>
       <c r="D199" t="n">
-        <v>0.01143817107119855</v>
+        <v>0.01187979755266783</v>
       </c>
       <c r="E199" t="n">
-        <v>7.959697567389876e-08</v>
+        <v>7.894477317554238e-08</v>
       </c>
       <c r="F199" t="n">
-        <v>0.01128825821517683</v>
+        <v>0.01171065327386537</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
-        <v>8.021236028928339e-08</v>
+        <v>7.958579881656805e-08</v>
       </c>
       <c r="D200" t="n">
-        <v>0.01101663444778652</v>
+        <v>0.0114227518569128</v>
       </c>
       <c r="E200" t="n">
-        <v>8.021236028928339e-08</v>
+        <v>7.958579881656805e-08</v>
       </c>
       <c r="F200" t="n">
-        <v>0.01090375188612504</v>
+        <v>0.01129545278975222</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
-        <v>8.082774490466799e-08</v>
+        <v>8.022682445759369e-08</v>
       </c>
       <c r="D201" t="n">
-        <v>0.01059509782437451</v>
+        <v>0.0109657061611578</v>
       </c>
       <c r="E201" t="n">
-        <v>8.082774490466799e-08</v>
+        <v>8.022682445759369e-08</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0105323533093718</v>
+        <v>0.01089498511580319</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>8.144312952005262e-08</v>
+        <v>8.086785009861932e-08</v>
       </c>
       <c r="D202" t="n">
-        <v>0.01017356120096248</v>
+        <v>0.01050866046540279</v>
       </c>
       <c r="E202" t="n">
-        <v>8.144312952005262e-08</v>
+        <v>8.086785009861932e-08</v>
       </c>
       <c r="F202" t="n">
-        <v>0.01017356120096248</v>
+        <v>0.01050866046540279</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>8.205851413543722e-08</v>
+        <v>8.150887573964496e-08</v>
       </c>
       <c r="D203" t="n">
-        <v>0.009875517538147627</v>
+        <v>0.01019014460673905</v>
       </c>
       <c r="E203" t="n">
-        <v>8.205851413543722e-08</v>
+        <v>8.150887573964496e-08</v>
       </c>
       <c r="F203" t="n">
-        <v>0.009826898688109587</v>
+        <v>0.01013591902661313</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>8.267389875082185e-08</v>
+        <v>8.21499013806706e-08</v>
       </c>
       <c r="D204" t="n">
-        <v>0.009577473875332764</v>
+        <v>0.009871628748075317</v>
       </c>
       <c r="E204" t="n">
-        <v>8.267389875082185e-08</v>
+        <v>8.21499013806706e-08</v>
       </c>
       <c r="F204" t="n">
-        <v>0.009491986542693677</v>
+        <v>0.009776320886206724</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>8.328928336620646e-08</v>
+        <v>8.279092702169624e-08</v>
       </c>
       <c r="D205" t="n">
-        <v>0.009279430212517911</v>
+        <v>0.00955311288941158</v>
       </c>
       <c r="E205" t="n">
-        <v>8.328928336620646e-08</v>
+        <v>8.279092702169624e-08</v>
       </c>
       <c r="F205" t="n">
-        <v>0.00916846994776241</v>
+        <v>0.009429456105633675</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>8.390466798159108e-08</v>
+        <v>8.343195266272187e-08</v>
       </c>
       <c r="D206" t="n">
-        <v>0.008981386549703046</v>
+        <v>0.009234597030747844</v>
       </c>
       <c r="E206" t="n">
-        <v>8.390466798159108e-08</v>
+        <v>8.343195266272187e-08</v>
       </c>
       <c r="F206" t="n">
-        <v>0.008855994086363386</v>
+        <v>0.00909491474634409</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>8.452005259697569e-08</v>
+        <v>8.407297830374751e-08</v>
       </c>
       <c r="D207" t="n">
-        <v>0.008683342886888195</v>
+        <v>0.008916081172084107</v>
       </c>
       <c r="E207" t="n">
-        <v>8.452005259697569e-08</v>
+        <v>8.407297830374751e-08</v>
       </c>
       <c r="F207" t="n">
-        <v>0.00855420414154426</v>
+        <v>0.008772286869788081</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>8.513543721236032e-08</v>
+        <v>8.471400394477318e-08</v>
       </c>
       <c r="D208" t="n">
-        <v>0.00838529922407333</v>
+        <v>0.008597565313420357</v>
       </c>
       <c r="E208" t="n">
-        <v>8.513543721236032e-08</v>
+        <v>8.471400394477318e-08</v>
       </c>
       <c r="F208" t="n">
-        <v>0.008262745296352637</v>
+        <v>0.008461162537415742</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>8.575082182774492e-08</v>
+        <v>8.535502958579881e-08</v>
       </c>
       <c r="D209" t="n">
-        <v>0.008087255561258477</v>
+        <v>0.008279049454756621</v>
       </c>
       <c r="E209" t="n">
-        <v>8.575082182774492e-08</v>
+        <v>8.535502958579881e-08</v>
       </c>
       <c r="F209" t="n">
-        <v>0.00798126273383617</v>
+        <v>0.008161131810677206</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>8.636620644312955e-08</v>
+        <v>8.599605522682445e-08</v>
       </c>
       <c r="D210" t="n">
-        <v>0.007789211898443612</v>
+        <v>0.007960533596092884</v>
       </c>
       <c r="E210" t="n">
-        <v>8.636620644312955e-08</v>
+        <v>8.599605522682445e-08</v>
       </c>
       <c r="F210" t="n">
-        <v>0.007709401637042464</v>
+        <v>0.007871784751022567</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>8.698159105851415e-08</v>
+        <v>8.663708086785009e-08</v>
       </c>
       <c r="D211" t="n">
-        <v>0.00749116823562876</v>
+        <v>0.007642017737429147</v>
       </c>
       <c r="E211" t="n">
-        <v>8.698159105851415e-08</v>
+        <v>8.663708086785009e-08</v>
       </c>
       <c r="F211" t="n">
-        <v>0.007446807189019171</v>
+        <v>0.007592711419901934</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>8.759697567389878e-08</v>
+        <v>8.727810650887573e-08</v>
       </c>
       <c r="D212" t="n">
-        <v>0.007193124572813899</v>
+        <v>0.007323501878765411</v>
       </c>
       <c r="E212" t="n">
-        <v>8.759697567389878e-08</v>
+        <v>8.727810650887573e-08</v>
       </c>
       <c r="F212" t="n">
-        <v>0.007193124572813897</v>
+        <v>0.007323501878765411</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>8.821236028928338e-08</v>
+        <v>8.791913214990136e-08</v>
       </c>
       <c r="D213" t="n">
-        <v>0.006982395492562025</v>
+        <v>0.007101527679768294</v>
       </c>
       <c r="E213" t="n">
-        <v>8.821236028928338e-08</v>
+        <v>8.791913214990136e-08</v>
       </c>
       <c r="F213" t="n">
-        <v>0.006948016415813357</v>
+        <v>0.007063766220516353</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
-        <v>8.882774490466801e-08</v>
+        <v>8.8560157790927e-08</v>
       </c>
       <c r="D214" t="n">
-        <v>0.006771666412310141</v>
+        <v>0.006879553480771177</v>
       </c>
       <c r="E214" t="n">
-        <v>8.882774490466801e-08</v>
+        <v>8.8560157790927e-08</v>
       </c>
       <c r="F214" t="n">
-        <v>0.006711215122760478</v>
+        <v>0.00681319466387109</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
-        <v>8.944312952005261e-08</v>
+        <v>8.920118343195264e-08</v>
       </c>
       <c r="D215" t="n">
-        <v>0.006560937332058266</v>
+        <v>0.00665757928177406</v>
       </c>
       <c r="E215" t="n">
-        <v>8.944312952005261e-08</v>
+        <v>8.920118343195264e-08</v>
       </c>
       <c r="F215" t="n">
-        <v>0.006482470542737293</v>
+        <v>0.00657149745899919</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>9.005851413543722e-08</v>
+        <v>8.98422090729783e-08</v>
       </c>
       <c r="D216" t="n">
-        <v>0.006350208251806393</v>
+        <v>0.006435605082776934</v>
       </c>
       <c r="E216" t="n">
-        <v>9.005851413543722e-08</v>
+        <v>8.98422090729783e-08</v>
       </c>
       <c r="F216" t="n">
-        <v>0.006261532524825804</v>
+        <v>0.006338384856070219</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>9.067389875082185e-08</v>
+        <v>9.048323471400394e-08</v>
       </c>
       <c r="D217" t="n">
-        <v>0.006139479171554509</v>
+        <v>0.006213630883779817</v>
       </c>
       <c r="E217" t="n">
-        <v>9.067389875082185e-08</v>
+        <v>9.048323471400394e-08</v>
       </c>
       <c r="F217" t="n">
-        <v>0.006048150918108013</v>
+        <v>0.00611356710525377</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>9.128928336620645e-08</v>
+        <v>9.112426035502958e-08</v>
       </c>
       <c r="D218" t="n">
-        <v>0.005928750091302635</v>
+        <v>0.005991656684782701</v>
       </c>
       <c r="E218" t="n">
-        <v>9.128928336620645e-08</v>
+        <v>9.112426035502958e-08</v>
       </c>
       <c r="F218" t="n">
-        <v>0.00584207557166595</v>
+        <v>0.005896754456719405</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>9.190466798159108e-08</v>
+        <v>9.176528599605522e-08</v>
       </c>
       <c r="D219" t="n">
-        <v>0.005718021011050752</v>
+        <v>0.005769682485785584</v>
       </c>
       <c r="E219" t="n">
-        <v>9.190466798159108e-08</v>
+        <v>9.176528599605522e-08</v>
       </c>
       <c r="F219" t="n">
-        <v>0.005643056334581611</v>
+        <v>0.005687657160636696</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>9.252005259697568e-08</v>
+        <v>9.240631163708085e-08</v>
       </c>
       <c r="D220" t="n">
-        <v>0.005507291930798877</v>
+        <v>0.005547708286788466</v>
       </c>
       <c r="E220" t="n">
-        <v>9.252005259697568e-08</v>
+        <v>9.240631163708085e-08</v>
       </c>
       <c r="F220" t="n">
-        <v>0.005450843055937024</v>
+        <v>0.005485985467175216</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>9.313543721236031e-08</v>
+        <v>9.304733727810649e-08</v>
       </c>
       <c r="D221" t="n">
-        <v>0.005296562850546994</v>
+        <v>0.005325734087791349</v>
       </c>
       <c r="E221" t="n">
-        <v>9.313543721236031e-08</v>
+        <v>9.304733727810649e-08</v>
       </c>
       <c r="F221" t="n">
-        <v>0.005265185584814184</v>
+        <v>0.005291449626504537</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>9.375082182774491e-08</v>
+        <v>9.368836291913213e-08</v>
       </c>
       <c r="D222" t="n">
-        <v>0.00508583377029512</v>
+        <v>0.005103759888794233</v>
       </c>
       <c r="E222" t="n">
-        <v>9.375082182774491e-08</v>
+        <v>9.368836291913213e-08</v>
       </c>
       <c r="F222" t="n">
-        <v>0.00508583377029512</v>
+        <v>0.005103759888794233</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>9.436620644312954e-08</v>
+        <v>9.432938856015777e-08</v>
       </c>
       <c r="D223" t="n">
-        <v>0.004936839677133043</v>
+        <v>0.004949065723087308</v>
       </c>
       <c r="E223" t="n">
-        <v>9.436620644312954e-08</v>
+        <v>9.432938856015777e-08</v>
       </c>
       <c r="F223" t="n">
-        <v>0.004912549260764149</v>
+        <v>0.004922643669233783</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="n">
-        <v>9.498159105851414e-08</v>
+        <v>9.497041420118343e-08</v>
       </c>
       <c r="D224" t="n">
-        <v>0.004787845583970972</v>
+        <v>0.004794371557380377</v>
       </c>
       <c r="E224" t="n">
-        <v>9.498159105851414e-08</v>
+        <v>9.497041420118343e-08</v>
       </c>
       <c r="F224" t="n">
-        <v>0.004745140901814898</v>
+        <v>0.004747897043092288</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="n">
-        <v>9.559697567389877e-08</v>
+        <v>9.561143984220907e-08</v>
       </c>
       <c r="D225" t="n">
-        <v>0.004638851490808896</v>
+        <v>0.004639677391673451</v>
       </c>
       <c r="E225" t="n">
-        <v>9.559697567389877e-08</v>
+        <v>9.561143984220907e-08</v>
       </c>
       <c r="F225" t="n">
-        <v>0.004583429338343283</v>
+        <v>0.004579333250658781</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>9.621236028928337e-08</v>
+        <v>9.625246548323471e-08</v>
       </c>
       <c r="D226" t="n">
-        <v>0.004489857397646825</v>
+        <v>0.004484983225966526</v>
       </c>
       <c r="E226" t="n">
-        <v>9.621236028928337e-08</v>
+        <v>9.625246548323471e-08</v>
       </c>
       <c r="F226" t="n">
-        <v>0.004427235215245253</v>
+        <v>0.004416765532222268</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>9.6827744904668e-08</v>
+        <v>9.689349112426034e-08</v>
       </c>
       <c r="D227" t="n">
-        <v>0.004340863304484748</v>
+        <v>0.0043302890602596</v>
       </c>
       <c r="E227" t="n">
-        <v>9.6827744904668e-08</v>
+        <v>9.689349112426034e-08</v>
       </c>
       <c r="F227" t="n">
-        <v>0.004276379177416725</v>
+        <v>0.004260007128071766</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>9.744312952005261e-08</v>
+        <v>9.753451676528598e-08</v>
       </c>
       <c r="D228" t="n">
-        <v>0.004191869211322677</v>
+        <v>0.004175594894552675</v>
       </c>
       <c r="E228" t="n">
-        <v>9.744312952005261e-08</v>
+        <v>9.753451676528598e-08</v>
       </c>
       <c r="F228" t="n">
-        <v>0.004130681869753646</v>
+        <v>0.00410887127849629</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>9.805851413543724e-08</v>
+        <v>9.817554240631162e-08</v>
       </c>
       <c r="D229" t="n">
-        <v>0.004042875118160601</v>
+        <v>0.00402090072884575</v>
       </c>
       <c r="E229" t="n">
-        <v>9.805851413543724e-08</v>
+        <v>9.817554240631162e-08</v>
       </c>
       <c r="F229" t="n">
-        <v>0.003989963937151936</v>
+        <v>0.003963171223784858</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>9.867389875082184e-08</v>
+        <v>9.881656804733726e-08</v>
       </c>
       <c r="D230" t="n">
-        <v>0.00389388102499853</v>
+        <v>0.003866206563138825</v>
       </c>
       <c r="E230" t="n">
-        <v>9.867389875082184e-08</v>
+        <v>9.881656804733726e-08</v>
       </c>
       <c r="F230" t="n">
-        <v>0.003854046024507536</v>
+        <v>0.003822720204226483</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>9.928928336620647e-08</v>
+        <v>9.945759368836292e-08</v>
       </c>
       <c r="D231" t="n">
-        <v>0.003744886931836453</v>
+        <v>0.003711512397431894</v>
       </c>
       <c r="E231" t="n">
-        <v>9.928928336620647e-08</v>
+        <v>9.945759368836292e-08</v>
       </c>
       <c r="F231" t="n">
-        <v>0.003722748776716371</v>
+        <v>0.003687331460110179</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>9.990466798159107e-08</v>
+        <v>1.000986193293886e-07</v>
       </c>
       <c r="D232" t="n">
-        <v>0.003595892838674382</v>
+        <v>0.003556818231724971</v>
       </c>
       <c r="E232" t="n">
-        <v>9.990466798159107e-08</v>
+        <v>1.000986193293886e-07</v>
       </c>
       <c r="F232" t="n">
-        <v>0.003595892838674382</v>
+        <v>0.00355681823172497</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>1.005200525969757e-07</v>
+        <v>1.007396449704142e-07</v>
       </c>
       <c r="D233" t="n">
-        <v>0.003490547910624324</v>
+        <v>0.00344901162621911</v>
       </c>
       <c r="E233" t="n">
-        <v>1.005200525969757e-07</v>
+        <v>1.007396449704142e-07</v>
       </c>
       <c r="F233" t="n">
-        <v>0.003473309151464102</v>
+        <v>0.003430993759359867</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>1.011354372123603e-07</v>
+        <v>1.013806706114398e-07</v>
       </c>
       <c r="D234" t="n">
-        <v>0.003385202982574271</v>
+        <v>0.00334120502071325</v>
       </c>
       <c r="E234" t="n">
-        <v>1.011354372123603e-07</v>
+        <v>1.013806706114398e-07</v>
       </c>
       <c r="F234" t="n">
-        <v>0.003354869840914522</v>
+        <v>0.003309671283303887</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>1.017508218277449e-07</v>
+        <v>1.020216962524655e-07</v>
       </c>
       <c r="D235" t="n">
-        <v>0.003279858054524212</v>
+        <v>0.003233398415207389</v>
       </c>
       <c r="E235" t="n">
-        <v>1.017508218277449e-07</v>
+        <v>1.020216962524655e-07</v>
       </c>
       <c r="F235" t="n">
-        <v>0.003240457329041222</v>
+        <v>0.003192664043846045</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>1.023662064431295e-07</v>
+        <v>1.026627218934911e-07</v>
       </c>
       <c r="D236" t="n">
-        <v>0.003174513126474159</v>
+        <v>0.003125591809701529</v>
       </c>
       <c r="E236" t="n">
-        <v>1.023662064431295e-07</v>
+        <v>1.026627218934911e-07</v>
       </c>
       <c r="F236" t="n">
-        <v>0.003129954037859805</v>
+        <v>0.003079785281275357</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
-        <v>1.029815910585142e-07</v>
+        <v>1.033037475345167e-07</v>
       </c>
       <c r="D237" t="n">
-        <v>0.003069168198424101</v>
+        <v>0.003017785204195668</v>
       </c>
       <c r="E237" t="n">
-        <v>1.029815910585142e-07</v>
+        <v>1.033037475345167e-07</v>
       </c>
       <c r="F237" t="n">
-        <v>0.003023242389385852</v>
+        <v>0.00297084823588084</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>1.035969756738988e-07</v>
+        <v>1.039447731755424e-07</v>
       </c>
       <c r="D238" t="n">
-        <v>0.002963823270374047</v>
+        <v>0.002909978598689807</v>
       </c>
       <c r="E238" t="n">
-        <v>1.035969756738988e-07</v>
+        <v>1.039447731755424e-07</v>
       </c>
       <c r="F238" t="n">
-        <v>0.002920204805634963</v>
+        <v>0.002865666147951509</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>1.042123602892834e-07</v>
+        <v>1.04585798816568e-07</v>
       </c>
       <c r="D239" t="n">
-        <v>0.002858478342323989</v>
+        <v>0.002802171993183942</v>
       </c>
       <c r="E239" t="n">
-        <v>1.042123602892834e-07</v>
+        <v>1.04585798816568e-07</v>
       </c>
       <c r="F239" t="n">
-        <v>0.002820723708622722</v>
+        <v>0.002764052257776376</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>1.04827744904668e-07</v>
+        <v>1.052268244575937e-07</v>
       </c>
       <c r="D240" t="n">
-        <v>0.002753133414273936</v>
+        <v>0.002694365387678082</v>
       </c>
       <c r="E240" t="n">
-        <v>1.04827744904668e-07</v>
+        <v>1.052268244575937e-07</v>
       </c>
       <c r="F240" t="n">
-        <v>0.002724681520364726</v>
+        <v>0.002665819805644465</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>1.054431295200526e-07</v>
+        <v>1.058678500986193e-07</v>
       </c>
       <c r="D241" t="n">
-        <v>0.002647788486223877</v>
+        <v>0.002586558782172221</v>
       </c>
       <c r="E241" t="n">
-        <v>1.054431295200526e-07</v>
+        <v>1.058678500986193e-07</v>
       </c>
       <c r="F241" t="n">
-        <v>0.002631960662876561</v>
+        <v>0.002570782031844787</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>1.060585141354372e-07</v>
+        <v>1.06508875739645e-07</v>
       </c>
       <c r="D242" t="n">
-        <v>0.002542443558173824</v>
+        <v>0.002478752176666358</v>
       </c>
       <c r="E242" t="n">
-        <v>1.060585141354372e-07</v>
+        <v>1.06508875739645e-07</v>
       </c>
       <c r="F242" t="n">
-        <v>0.002542443558173824</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr"/>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="n">
-        <v>1.066738987508219e-07</v>
-      </c>
-      <c r="D243" t="n">
-        <v>0.002467960378133928</v>
-      </c>
-      <c r="E243" t="n">
-        <v>1.066738987508219e-07</v>
-      </c>
-      <c r="F243" t="n">
-        <v>0.002456012628272099</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr"/>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="n">
-        <v>1.072892833662065e-07</v>
-      </c>
-      <c r="D244" t="n">
-        <v>0.002393477198094036</v>
-      </c>
-      <c r="E244" t="n">
-        <v>1.072892833662065e-07</v>
-      </c>
-      <c r="F244" t="n">
-        <v>0.002372550295186986</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr"/>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="n">
-        <v>1.079046679815911e-07</v>
-      </c>
-      <c r="D245" t="n">
-        <v>0.00231899401805414</v>
-      </c>
-      <c r="E245" t="n">
-        <v>1.079046679815911e-07</v>
-      </c>
-      <c r="F245" t="n">
-        <v>0.002291938980934068</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="n">
-        <v>1.085200525969757e-07</v>
-      </c>
-      <c r="D246" t="n">
-        <v>0.002244510838014248</v>
-      </c>
-      <c r="E246" t="n">
-        <v>1.085200525969757e-07</v>
-      </c>
-      <c r="F246" t="n">
-        <v>0.002214061107528943</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="n">
-        <v>1.091354372123603e-07</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.002170027657974352</v>
-      </c>
-      <c r="E247" t="n">
-        <v>1.091354372123603e-07</v>
-      </c>
-      <c r="F247" t="n">
-        <v>0.002138799096987196</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr"/>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="n">
-        <v>1.097508218277449e-07</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.00209554447793446</v>
-      </c>
-      <c r="E248" t="n">
-        <v>1.097508218277449e-07</v>
-      </c>
-      <c r="F248" t="n">
-        <v>0.002066035371324425</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr"/>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="n">
-        <v>1.103662064431296e-07</v>
-      </c>
-      <c r="D249" t="n">
-        <v>0.002021061297894564</v>
-      </c>
-      <c r="E249" t="n">
-        <v>1.103662064431296e-07</v>
-      </c>
-      <c r="F249" t="n">
-        <v>0.001995652352556214</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr"/>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="n">
-        <v>1.109815910585142e-07</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.001946578117854672</v>
-      </c>
-      <c r="E250" t="n">
-        <v>1.109815910585142e-07</v>
-      </c>
-      <c r="F250" t="n">
-        <v>0.001927532462698162</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="n">
-        <v>1.115969756738988e-07</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.001872094937814776</v>
-      </c>
-      <c r="E251" t="n">
-        <v>1.115969756738988e-07</v>
-      </c>
-      <c r="F251" t="n">
-        <v>0.001861558123765853</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr"/>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="n">
-        <v>1.122123602892834e-07</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.001797611757774885</v>
-      </c>
-      <c r="E252" t="n">
-        <v>1.122123602892834e-07</v>
-      </c>
-      <c r="F252" t="n">
-        <v>0.001797611757774885</v>
+        <v>0.002478752176666359</v>
       </c>
     </row>
   </sheetData>

--- a/python_imp/samples_export.xlsx
+++ b/python_imp/samples_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,3958 +462,2658 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-4.733727810650888e-08</v>
+        <v>-1.701840894148587e-08</v>
       </c>
       <c r="B2" t="n">
-        <v>1.266416554909418e-14</v>
+        <v>0.01598654957695256</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.733727810650888e-08</v>
+        <v>-1.947994740302433e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.266416554909418e-14</v>
+        <v>0.009778957441417161</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.733727810650888e-08</v>
+        <v>-1.947994740302433e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.266416554909418e-14</v>
+        <v>0.005085960215905115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-4.092702169625247e-08</v>
+        <v>-1.086456278763971e-08</v>
       </c>
       <c r="B3" t="n">
-        <v>4.088986476321812e-11</v>
+        <v>0.1853235604503829</v>
       </c>
       <c r="C3" t="n">
-        <v>-4.669625246548323e-08</v>
+        <v>-1.886456278763971e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.100384225316018e-12</v>
+        <v>0.01133085547530101</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.669625246548323e-08</v>
+        <v>-1.886456278763971e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.540124775660534e-05</v>
+        <v>0.00700509110280086</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-3.451676528599606e-08</v>
+        <v>-4.710716633793558e-09</v>
       </c>
       <c r="B4" t="n">
-        <v>4.082836041142489e-08</v>
+        <v>0.7284061772306969</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.60552268244576e-08</v>
+        <v>-1.82491781722551e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.1881042850829e-12</v>
+        <v>0.01288275350918486</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.60552268244576e-08</v>
+        <v>-1.82491781722551e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.593911387248159e-05</v>
+        <v>0.009419777377621223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-2.810650887573965e-08</v>
+        <v>1.443129520052593e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>1.260710517704852e-05</v>
+        <v>0.9706970133569975</v>
       </c>
       <c r="C5" t="n">
-        <v>-4.541420118343195e-08</v>
+        <v>-1.763379355687048e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.227582434484982e-11</v>
+        <v>0.01443465154306871</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.541420118343195e-08</v>
+        <v>-1.763379355687048e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.21539288002381e-05</v>
+        <v>0.0123927024118454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-2.169625246548324e-08</v>
+        <v>7.596975673898752e-09</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001203859994828202</v>
+        <v>0.6518355564093071</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.477317554240632e-08</v>
+        <v>-1.701840894148587e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.636354440461671e-11</v>
+        <v>0.01598654957695256</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.477317554240632e-08</v>
+        <v>-1.701840894148587e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.458602300514806e-05</v>
+        <v>0.01598654957695256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.528599605522683e-08</v>
+        <v>1.375082182774491e-08</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03555034011478109</v>
+        <v>0.4608744436312056</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.413214990138067e-08</v>
+        <v>-1.640302432610125e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.045126446438363e-11</v>
+        <v>0.0329202506642956</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.413214990138067e-08</v>
+        <v>-1.640302432610125e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.377572695248478e-05</v>
+        <v>0.02034945972472026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-8.875739644970418e-09</v>
+        <v>1.990466798159107e-08</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3246524673583495</v>
+        <v>0.3258571133529846</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.349112426035503e-08</v>
+        <v>-1.578763971071664e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.453898452415051e-11</v>
+        <v>0.04985395175163863</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.349112426035503e-08</v>
+        <v>-1.578763971071664e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.026337110752159e-05</v>
+        <v>0.02597140362811955</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-2.465483234714009e-09</v>
+        <v>2.605851413543721e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9168553557320287</v>
+        <v>0.2303943292800761</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.285009861932939e-08</v>
+        <v>-1.517225509533202e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.862670458391743e-11</v>
+        <v>0.06678765283898166</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.285009861932939e-08</v>
+        <v>-1.517225509533202e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.458928593553169e-05</v>
+        <v>0.03342780954041986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.944773175542401e-09</v>
+        <v>3.221236028928337e-08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8007374029168086</v>
+        <v>0.1628982298965975</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.220907297830375e-08</v>
+        <v>-1.45568704799474e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>3.271442464368432e-11</v>
+        <v>0.08372135392632468</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.220907297830375e-08</v>
+        <v>-1.45568704799474e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.729380190178853e-05</v>
+        <v>0.04329410571489062</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.035502958579881e-08</v>
+        <v>3.836620644312953e-08</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5580351457700473</v>
+        <v>0.1151757223641853</v>
       </c>
       <c r="C11" t="n">
-        <v>-4.156804733727811e-08</v>
+        <v>-1.394148586456279e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>3.680214470345124e-11</v>
+        <v>0.1006550550136677</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.156804733727811e-08</v>
+        <v>-1.394148586456279e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.917249471565255e-06</v>
+        <v>0.05614572040480127</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.676528599605523e-08</v>
+        <v>4.452005259697567e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>0.388895563989223</v>
+        <v>0.0814339543807958</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.092702169625247e-08</v>
+        <v>-1.332610124917817e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>4.088986476321812e-11</v>
+        <v>0.1175887561010107</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.092702169625247e-08</v>
+        <v>-1.332610124917817e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>4.088986476321812e-11</v>
+        <v>0.07255808186342123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.317554240631163e-08</v>
+        <v>5.067389875082183e-08</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2710219254771064</v>
+        <v>0.05757714203975013</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.028599605522683e-08</v>
+        <v>-1.271071663379356e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>4.119636919429406e-09</v>
+        <v>0.1345224571883538</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.028599605522683e-08</v>
+        <v>-1.271071663379356e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>8.91773871722828e-06</v>
+        <v>0.09310661834401994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2.958579881656804e-08</v>
+        <v>5.682774490466799e-08</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1888756028375619</v>
+        <v>0.04070939831760589</v>
       </c>
       <c r="C14" t="n">
-        <v>-3.964497041420119e-08</v>
+        <v>-1.209533201840894e-08</v>
       </c>
       <c r="D14" t="n">
-        <v>8.19838397409555e-09</v>
+        <v>0.1514561582756968</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.964497041420119e-08</v>
+        <v>-1.209533201840894e-08</v>
       </c>
       <c r="F14" t="n">
-        <v>1.729551354525188e-05</v>
+        <v>0.1183667580998668</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.599605522682445e-08</v>
+        <v>6.298159105851415e-08</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1316277023877387</v>
+        <v>0.02878321244630996</v>
       </c>
       <c r="C15" t="n">
-        <v>-3.900394477317554e-08</v>
+        <v>-1.147994740302433e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>1.227713102876174e-08</v>
+        <v>0.1683898593630398</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.900394477317554e-08</v>
+        <v>-1.147994740302433e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>2.459303490866241e-05</v>
+        <v>0.1489139293842313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.240631163708086e-08</v>
+        <v>6.913543721236031e-08</v>
       </c>
       <c r="B16" t="n">
-        <v>0.09173155121985659</v>
+        <v>0.02035091042775538</v>
       </c>
       <c r="C16" t="n">
-        <v>-3.836291913214991e-08</v>
+        <v>-1.086456278763971e-08</v>
       </c>
       <c r="D16" t="n">
-        <v>1.635587808342788e-08</v>
+        <v>0.1853235604503829</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.836291913214991e-08</v>
+        <v>-1.086456278763971e-08</v>
       </c>
       <c r="F16" t="n">
-        <v>3.026997234218646e-05</v>
+        <v>0.1853235604503829</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4.881656804733726e-08</v>
+        <v>7.528928336620645e-08</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06392786120670763</v>
+        <v>0.01438892743508268</v>
       </c>
       <c r="C17" t="n">
-        <v>-3.772189349112426e-08</v>
+        <v>-1.024917817225509e-08</v>
       </c>
       <c r="D17" t="n">
-        <v>2.043462513809407e-08</v>
+        <v>0.2396318221284143</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.772189349112426e-08</v>
+        <v>-1.024917817225509e-08</v>
       </c>
       <c r="F17" t="n">
-        <v>3.378599538055083e-05</v>
+        <v>0.2279010363539921</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5.522682445759368e-08</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.04455142624448971</v>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-3.708086785009862e-08</v>
+        <v>-9.633793556870478e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>2.451337219276022e-08</v>
+        <v>0.2939400838064458</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.708086785009862e-08</v>
+        <v>-9.633793556870478e-09</v>
       </c>
       <c r="F18" t="n">
-        <v>3.460077355848216e-05</v>
+        <v>0.2758715693603346</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>6.163708086785009e-08</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.03104795847932967</v>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-3.643984220907298e-08</v>
+        <v>-9.018408941485862e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85921192474264e-08</v>
+        <v>0.3482483454844773</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.643984220907298e-08</v>
+        <v>-9.018408941485862e-09</v>
       </c>
       <c r="F19" t="n">
-        <v>3.217397641070716e-05</v>
+        <v>0.3281903285370875</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>6.804733727810649e-08</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.02163737071949312</v>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-3.579881656804734e-08</v>
+        <v>-8.403024326101253e-09</v>
       </c>
       <c r="D20" t="n">
-        <v>3.267086630209255e-08</v>
+        <v>0.4025566071625081</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.579881656804734e-08</v>
+        <v>-8.403024326101253e-09</v>
       </c>
       <c r="F20" t="n">
-        <v>2.59652734719526e-05</v>
+        <v>0.3838124829519267</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>7.445759368836289e-08</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.0150791174229529</v>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-3.51577909270217e-08</v>
+        <v>-7.787639710716637e-09</v>
       </c>
       <c r="D21" t="n">
-        <v>3.674961335675874e-08</v>
+        <v>0.4568648688405396</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.51577909270217e-08</v>
+        <v>-7.787639710716637e-09</v>
       </c>
       <c r="F21" t="n">
-        <v>1.543433427694503e-05</v>
+        <v>0.4416932016725303</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>8.086785009861932e-08</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.01050866046540279</v>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-3.451676528599606e-08</v>
+        <v>-7.172255095332021e-09</v>
       </c>
       <c r="D22" t="n">
-        <v>4.082836041142489e-08</v>
+        <v>0.5111731305185711</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.451676528599606e-08</v>
+        <v>-7.172255095332021e-09</v>
       </c>
       <c r="F22" t="n">
-        <v>4.082836041142489e-08</v>
+        <v>0.5007876537665746</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>8.727810650887573e-08</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.007323501878765411</v>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>-3.387573964497042e-08</v>
+        <v>-6.556870479947405e-09</v>
       </c>
       <c r="D23" t="n">
-        <v>1.297456042075141e-06</v>
+        <v>0.5654813921966024</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.387573964497042e-08</v>
+        <v>-6.556870479947405e-09</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.020275953489583e-05</v>
+        <v>0.5600510083017367</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>9.368836291913213e-08</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.005103759888794233</v>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-3.323471400394478e-08</v>
+        <v>-5.94148586456279e-09</v>
       </c>
       <c r="D24" t="n">
-        <v>2.554083723738843e-06</v>
+        <v>0.6197896538746339</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.323471400394478e-08</v>
+        <v>-5.94148586456279e-09</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.307268383411941e-05</v>
+        <v>0.6184384343456931</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>1.000986193293885e-07</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.003556818231724975</v>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-3.259368836291913e-08</v>
+        <v>-5.326101249178174e-09</v>
       </c>
       <c r="D25" t="n">
-        <v>3.810711405402559e-06</v>
+        <v>0.6740979155526654</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.259368836291913e-08</v>
+        <v>-5.326101249178174e-09</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.579238375437684e-05</v>
+        <v>0.6749051009661208</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>1.06508875739645e-07</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.002478752176666358</v>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-3.195266272189349e-08</v>
+        <v>-4.710716633793558e-09</v>
       </c>
       <c r="D26" t="n">
-        <v>5.067339087066275e-06</v>
+        <v>0.7284061772306969</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.195266272189349e-08</v>
+        <v>-4.710716633793558e-09</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.558529851278489e-05</v>
+        <v>0.7284061772306969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-3.131163708086785e-08</v>
+        <v>-4.095332018408942e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>6.323966768729978e-06</v>
+        <v>0.752635260843327</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.131163708086785e-08</v>
+        <v>-4.095332018408942e-09</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.967486732646046e-05</v>
+        <v>0.7779970825552612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-3.067061143984222e-08</v>
+        <v>-3.479947403024326e-09</v>
       </c>
       <c r="D28" t="n">
-        <v>7.58059445039368e-06</v>
+        <v>0.7768643444559571</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.067061143984222e-08</v>
+        <v>-3.479947403024326e-09</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0001052845294125209</v>
+        <v>0.8231342377483085</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-3.002958579881657e-08</v>
+        <v>-2.864562787639711e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>8.837222132057396e-06</v>
+        <v>0.8010934280685872</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.002958579881657e-08</v>
+        <v>-2.864562787639711e-09</v>
       </c>
       <c r="F29" t="n">
-        <v>-9.963772398808316e-05</v>
+        <v>0.8633743139664963</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-2.938856015779093e-08</v>
+        <v>-2.249178172255095e-09</v>
       </c>
       <c r="D30" t="n">
-        <v>1.00938498137211e-05</v>
+        <v>0.8253225116812173</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.938856015779093e-08</v>
+        <v>-2.249178172255095e-09</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.995789027026435e-05</v>
+        <v>0.8982739823664824</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-2.874753451676529e-08</v>
+        <v>-1.633793556870479e-09</v>
       </c>
       <c r="D31" t="n">
-        <v>1.135047749538481e-05</v>
+        <v>0.8495515952938474</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.874753451676529e-08</v>
+        <v>-1.633793556870479e-09</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.346846747618137e-05</v>
+        <v>0.9273899141049244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-2.810650887573965e-08</v>
+        <v>-1.018408941485863e-09</v>
       </c>
       <c r="D32" t="n">
-        <v>1.260710517704852e-05</v>
+        <v>0.8737806789064775</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.810650887573965e-08</v>
+        <v>-1.018408941485863e-09</v>
       </c>
       <c r="F32" t="n">
-        <v>1.260710517704852e-05</v>
+        <v>0.9502787803384803</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-2.746548323471401e-08</v>
+        <v>-4.030243261012473e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001317323941421639</v>
+        <v>0.8980097625191075</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.746548323471401e-08</v>
+        <v>-4.030243261012473e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>8.99878040209399e-05</v>
+        <v>0.9664972522238078</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>-2.682445759368837e-08</v>
+        <v>2.123602892833685e-10</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0002508576831072792</v>
+        <v>0.9222388461317377</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.682445759368837e-08</v>
+        <v>2.123602892833685e-10</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0001861622675815333</v>
+        <v>0.9756020009175648</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-2.618343195266273e-08</v>
+        <v>8.277449046679843e-10</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003699829720723945</v>
+        <v>0.9464679297443677</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.618343195266273e-08</v>
+        <v>8.277449046679843e-10</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0002975615499335008</v>
+        <v>0.9771496975764087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-2.554240631163708e-08</v>
+        <v>1.4431295200526e-09</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0004891082610375098</v>
+        <v>0.9706970133569972</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.554240631163708e-08</v>
+        <v>1.4431295200526e-09</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0004206167051515144</v>
+        <v>0.9706970133569974</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-2.490138067061144e-08</v>
+        <v>2.058514135437216e-09</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0006082335500026252</v>
+        <v>0.9388108676622282</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.490138067061144e-08</v>
+        <v>2.058514135437216e-09</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0005517587873102465</v>
+        <v>0.9560838380950746</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-2.42603550295858e-08</v>
+        <v>2.673898750821832e-09</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0007273588389677404</v>
+        <v>0.9069247219674591</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.42603550295858e-08</v>
+        <v>2.673898750821832e-09</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0006874188504843687</v>
+        <v>0.9342829363427267</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>-2.361932938856016e-08</v>
+        <v>3.289283366206448e-09</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0008464841279328558</v>
+        <v>0.8750385762726901</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.361932938856016e-08</v>
+        <v>3.289283366206448e-09</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0008240279487485532</v>
+        <v>0.9065502913311259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-2.297830374753452e-08</v>
+        <v>3.904667981591063e-09</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0009656094168979711</v>
+        <v>0.843152430577921</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.297830374753452e-08</v>
+        <v>3.904667981591063e-09</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000958017136177472</v>
+        <v>0.8741418862914443</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-2.233727810650888e-08</v>
+        <v>4.520052596975673e-09</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001084734705863086</v>
+        <v>0.8112662848831523</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.233727810650888e-08</v>
+        <v>4.520052596975673e-09</v>
       </c>
       <c r="F41" t="n">
-        <v>0.001085817466845797</v>
+        <v>0.8383137044548549</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-2.169625246548324e-08</v>
+        <v>5.135437212360288e-09</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001203859994828202</v>
+        <v>0.7793801391883832</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.169625246548324e-08</v>
+        <v>5.135437212360288e-09</v>
       </c>
       <c r="F42" t="n">
-        <v>0.001203859994828202</v>
+        <v>0.8003217290525287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-2.10552268244576e-08</v>
+        <v>5.750821827744904e-09</v>
       </c>
       <c r="D43" t="n">
-        <v>0.004638508006823489</v>
+        <v>0.7474939934936142</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.10552268244576e-08</v>
+        <v>5.750821827744904e-09</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001343063676290783</v>
+        <v>0.7614219433156388</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>-2.041420118343196e-08</v>
+        <v>6.36620644312952e-09</v>
       </c>
       <c r="D44" t="n">
-        <v>0.008073156018818778</v>
+        <v>0.7156078477988452</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.041420118343196e-08</v>
+        <v>6.36620644312952e-09</v>
       </c>
       <c r="F44" t="n">
-        <v>0.001672299075765347</v>
+        <v>0.7228703304753569</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-1.977317554240632e-08</v>
+        <v>6.981591058514136e-09</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01150780403081407</v>
+        <v>0.6837217021040762</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.977317554240632e-08</v>
+        <v>6.981591058514136e-09</v>
       </c>
       <c r="F45" t="n">
-        <v>0.002394924659875125</v>
+        <v>0.6859228737628557</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-1.913214990138068e-08</v>
+        <v>7.596975673898752e-09</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01494245204280935</v>
+        <v>0.6518355564093071</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.913214990138068e-08</v>
+        <v>7.596975673898752e-09</v>
       </c>
       <c r="F46" t="n">
-        <v>0.003714298895243349</v>
+        <v>0.6518355564093071</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-1.849112426035503e-08</v>
+        <v>8.212360289283367e-09</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01837710005480464</v>
+        <v>0.6327394451314969</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.849112426035503e-08</v>
+        <v>8.212360289283367e-09</v>
       </c>
       <c r="F47" t="n">
-        <v>0.00583378024849325</v>
+        <v>0.6215806497310407</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-1.785009861932939e-08</v>
+        <v>8.827744904667983e-09</v>
       </c>
       <c r="D48" t="n">
-        <v>0.02181174806679993</v>
+        <v>0.6136433338536869</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.785009861932939e-08</v>
+        <v>8.827744904667983e-09</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008956727186248062</v>
+        <v>0.5949955773850139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-1.720907297830375e-08</v>
+        <v>9.443129520052599e-09</v>
       </c>
       <c r="D49" t="n">
-        <v>0.02524639607879521</v>
+        <v>0.5945472225758767</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.720907297830375e-08</v>
+        <v>9.443129520052599e-09</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01328649817513101</v>
+        <v>0.5716340511133418</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-1.656804733727811e-08</v>
+        <v>1.005851413543721e-08</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02868104409079052</v>
+        <v>0.5754511112980665</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.656804733727811e-08</v>
+        <v>1.005851413543721e-08</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01902645168176538</v>
+        <v>0.5510497826581388</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-1.592702169625247e-08</v>
+        <v>1.067389875082183e-08</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0321156921027858</v>
+        <v>0.5563550000202564</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.592702169625247e-08</v>
+        <v>1.067389875082183e-08</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02637994617277428</v>
+        <v>0.5327964837615201</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1.528599605522683e-08</v>
+        <v>1.128928336620645e-08</v>
       </c>
       <c r="D52" t="n">
-        <v>0.03555034011478109</v>
+        <v>0.5372588887424462</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.528599605522683e-08</v>
+        <v>1.128928336620645e-08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.03555034011478109</v>
+        <v>0.5164278661656001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>-1.464497041420119e-08</v>
+        <v>1.190466798159106e-08</v>
       </c>
       <c r="D53" t="n">
-        <v>0.06446055283913779</v>
+        <v>0.518162777464636</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.464497041420119e-08</v>
+        <v>1.190466798159106e-08</v>
       </c>
       <c r="F53" t="n">
-        <v>0.04679372182977039</v>
+        <v>0.501497641612494</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-1.400394477317555e-08</v>
+        <v>1.252005259697568e-08</v>
       </c>
       <c r="D54" t="n">
-        <v>0.09337076556349479</v>
+        <v>0.4990666661868259</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.400394477317555e-08</v>
+        <v>1.252005259697568e-08</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06057709906117316</v>
+        <v>0.4875595218443164</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-1.336291913214991e-08</v>
+        <v>1.313543721236029e-08</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1222809782878515</v>
+        <v>0.4799705549090157</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.336291913214991e-08</v>
+        <v>1.313543721236029e-08</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07742020940778141</v>
+        <v>0.474167218603182</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-1.272189349112426e-08</v>
+        <v>1.375082182774491e-08</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1511911910122085</v>
+        <v>0.4608744436312056</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.272189349112426e-08</v>
+        <v>1.375082182774491e-08</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09784279046838777</v>
+        <v>0.4608744436312056</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-1.208086785009863e-08</v>
+        <v>1.436620644312953e-08</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1801014037365652</v>
+        <v>0.4473727106033835</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.208086785009863e-08</v>
+        <v>1.436620644312953e-08</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1223645798417841</v>
+        <v>0.4473255284518747</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-1.143984220907298e-08</v>
+        <v>1.498159105851414e-08</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2090116164609221</v>
+        <v>0.4338709775755614</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.143984220907298e-08</v>
+        <v>1.498159105851414e-08</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1515053151267632</v>
+        <v>0.433527283714167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-1.079881656804734e-08</v>
+        <v>1.559697567389876e-08</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2379218291852788</v>
+        <v>0.4203692445477393</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.079881656804734e-08</v>
+        <v>1.559697567389876e-08</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1857847339221168</v>
+        <v>0.4195771398484329</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-1.01577909270217e-08</v>
+        <v>1.621236028928337e-08</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2668320419096359</v>
+        <v>0.4068675115199172</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.01577909270217e-08</v>
+        <v>1.621236028928337e-08</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2257225738266377</v>
+        <v>0.4055725272850227</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-9.516765285996062e-09</v>
+        <v>1.682774490466799e-08</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2957422546339926</v>
+        <v>0.3933657784920951</v>
       </c>
       <c r="E61" t="n">
-        <v>-9.516765285996062e-09</v>
+        <v>1.682774490466799e-08</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2718385724391176</v>
+        <v>0.3916108764542869</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-8.875739644970418e-09</v>
+        <v>1.74431295200526e-08</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3246524673583495</v>
+        <v>0.379864045464273</v>
       </c>
       <c r="E62" t="n">
-        <v>-8.875739644970418e-09</v>
+        <v>1.74431295200526e-08</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3246524673583495</v>
+        <v>0.3777896177865757</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-8.23471400394478e-09</v>
+        <v>1.805851413543722e-08</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3838727561957171</v>
+        <v>0.3663623124364509</v>
       </c>
       <c r="E63" t="n">
-        <v>-8.23471400394478e-09</v>
+        <v>1.805851413543722e-08</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3842653335537005</v>
+        <v>0.3642061817122395</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-7.593688362919136e-09</v>
+        <v>1.867389875082184e-08</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4430930450330853</v>
+        <v>0.3528605794086288</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.593688362919136e-09</v>
+        <v>1.867389875082184e-08</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4491035954768428</v>
+        <v>0.3509579986616286</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-6.952662721893498e-09</v>
+        <v>1.928928336620645e-08</v>
       </c>
       <c r="D65" t="n">
-        <v>0.502313333870453</v>
+        <v>0.3393588463808067</v>
       </c>
       <c r="E65" t="n">
-        <v>-6.952662721893498e-09</v>
+        <v>1.928928336620645e-08</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5171750149500214</v>
+        <v>0.3381424990650935</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-6.311637080867854e-09</v>
+        <v>1.990466798159107e-08</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5615336227078211</v>
+        <v>0.3258571133529846</v>
       </c>
       <c r="E66" t="n">
-        <v>-6.311637080867854e-09</v>
+        <v>1.990466798159107e-08</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5864873537954844</v>
+        <v>0.3258571133529846</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-5.67061143984221e-09</v>
+        <v>2.052005259697568e-08</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6207539115451894</v>
+        <v>0.3163108349456937</v>
       </c>
       <c r="E67" t="n">
-        <v>-5.67061143984221e-09</v>
+        <v>2.052005259697568e-08</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6550483738354778</v>
+        <v>0.3141760720703797</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>-5.029585798816572e-09</v>
+        <v>2.11354372123603e-08</v>
       </c>
       <c r="D68" t="n">
-        <v>0.6799742003825571</v>
+        <v>0.3067645565384028</v>
       </c>
       <c r="E68" t="n">
-        <v>-5.029585798816572e-09</v>
+        <v>2.11354372123603e-08</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7208658368922475</v>
+        <v>0.3030808062212677</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-4.388560157790928e-09</v>
+        <v>2.175082182774492e-08</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7391944892199253</v>
+        <v>0.297218278131112</v>
       </c>
       <c r="E69" t="n">
-        <v>-4.388560157790928e-09</v>
+        <v>2.175082182774492e-08</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7819475047880411</v>
+        <v>0.2925295469243648</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-3.74753451676529e-09</v>
+        <v>2.236620644312953e-08</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7984147780572928</v>
+        <v>0.2876719997238211</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.74753451676529e-09</v>
+        <v>2.236620644312953e-08</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8363011393451045</v>
+        <v>0.2824805252983875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-3.106508875739646e-09</v>
+        <v>2.298159105851415e-08</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8576350668946611</v>
+        <v>0.2781257213165302</v>
       </c>
       <c r="E71" t="n">
-        <v>-3.106508875739646e-09</v>
+        <v>2.298159105851415e-08</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8819345023856852</v>
+        <v>0.272891972462052</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-2.465483234714009e-09</v>
+        <v>2.359697567389876e-08</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9168553557320287</v>
+        <v>0.2685794429092394</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.465483234714009e-09</v>
+        <v>2.359697567389876e-08</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9168553557320287</v>
+        <v>0.2637221195340749</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-1.824457593688364e-09</v>
+        <v>2.421236028928337e-08</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9052435604505066</v>
+        <v>0.2590331645019487</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.824457593688364e-09</v>
+        <v>2.421236028928337e-08</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9396336151523926</v>
+        <v>0.2549291976331725</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-1.183431952662727e-09</v>
+        <v>2.482774490466798e-08</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8936317651689847</v>
+        <v>0.2494868860946579</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.183431952662727e-09</v>
+        <v>2.482774490466798e-08</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9510878121990735</v>
+        <v>0.246471437878061</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-5.424063116370826e-10</v>
+        <v>2.54431295200526e-08</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8820199698874627</v>
+        <v>0.239940607687367</v>
       </c>
       <c r="E75" t="n">
-        <v>-5.424063116370826e-10</v>
+        <v>2.54431295200526e-08</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9525986323703789</v>
+        <v>0.2383070713874567</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>9.861932938855505e-11</v>
+        <v>2.605851413543721e-08</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8704081746059407</v>
+        <v>0.2303943292800761</v>
       </c>
       <c r="E76" t="n">
-        <v>9.861932938855505e-11</v>
+        <v>2.605851413543721e-08</v>
       </c>
       <c r="F76" t="n">
-        <v>0.945546761164616</v>
+        <v>0.2303943292800761</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>7.396449704141993e-10</v>
+        <v>2.667389875082183e-08</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8587963793244187</v>
+        <v>0.2236447193417283</v>
       </c>
       <c r="E77" t="n">
-        <v>7.396449704141993e-10</v>
+        <v>2.667389875082183e-08</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9313128840800919</v>
+        <v>0.222698423809131</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.380670611439837e-09</v>
+        <v>2.728928336620644e-08</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8471845840428966</v>
+        <v>0.2168951094033804</v>
       </c>
       <c r="E78" t="n">
-        <v>1.380670611439837e-09</v>
+        <v>2.728928336620644e-08</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9112776866151142</v>
+        <v>0.2152124917658149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>2.021696252465481e-09</v>
+        <v>2.790466798159106e-08</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8355727887613746</v>
+        <v>0.2101454994650326</v>
       </c>
       <c r="E79" t="n">
-        <v>2.021696252465481e-09</v>
+        <v>2.790466798159106e-08</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8868218542679894</v>
+        <v>0.2079366510758167</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>2.662721893491119e-09</v>
+        <v>2.852005259697568e-08</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8239609934798526</v>
+        <v>0.2033958895266847</v>
       </c>
       <c r="E80" t="n">
-        <v>2.662721893491119e-09</v>
+        <v>2.852005259697568e-08</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8593260725370258</v>
+        <v>0.2008710196648252</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>3.303747534516763e-09</v>
+        <v>2.913543721236029e-08</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8123491981983306</v>
+        <v>0.1966462795883368</v>
       </c>
       <c r="E81" t="n">
-        <v>3.303747534516763e-09</v>
+        <v>2.913543721236029e-08</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8301710269205296</v>
+        <v>0.1940157154585294</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>3.944773175542401e-09</v>
+        <v>2.975082182774491e-08</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8007374029168086</v>
+        <v>0.189896669649989</v>
       </c>
       <c r="E82" t="n">
-        <v>3.944773175542401e-09</v>
+        <v>2.975082182774491e-08</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8007374029168086</v>
+        <v>0.1873708563826182</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>4.585798816568045e-09</v>
+        <v>3.036620644312952e-08</v>
       </c>
       <c r="D83" t="n">
-        <v>0.7764671772021323</v>
+        <v>0.1831470597116411</v>
       </c>
       <c r="E83" t="n">
-        <v>4.585798816568045e-09</v>
+        <v>3.036620644312952e-08</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7721690910087301</v>
+        <v>0.1809365603627805</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>5.226824457593682e-09</v>
+        <v>3.098159105851414e-08</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7521969514874564</v>
+        <v>0.1763974497732932</v>
       </c>
       <c r="E84" t="n">
-        <v>5.226824457593682e-09</v>
+        <v>3.098159105851414e-08</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7446628016174026</v>
+        <v>0.1747129453247052</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>5.867850098619327e-09</v>
+        <v>3.159697567389875e-08</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7279267257727801</v>
+        <v>0.1696478398349454</v>
       </c>
       <c r="E85" t="n">
-        <v>5.867850098619327e-09</v>
+        <v>3.159697567389875e-08</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7181784501484944</v>
+        <v>0.1687001291940813</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>6.508875739644964e-09</v>
+        <v>3.221236028928337e-08</v>
       </c>
       <c r="D86" t="n">
-        <v>0.7036565000581041</v>
+        <v>0.1628982298965975</v>
       </c>
       <c r="E86" t="n">
-        <v>6.508875739644964e-09</v>
+        <v>3.221236028928337e-08</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6926759520076745</v>
+        <v>0.1628982298965975</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>7.149901380670608e-09</v>
+        <v>3.282774490466799e-08</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6793862743434278</v>
+        <v>0.1581259791433563</v>
       </c>
       <c r="E87" t="n">
-        <v>7.149901380670608e-09</v>
+        <v>3.282774490466799e-08</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6681152226006112</v>
+        <v>0.1573060354739111</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>7.790927021696246e-09</v>
+        <v>3.34431295200526e-08</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6551160486287518</v>
+        <v>0.1533537283901151</v>
       </c>
       <c r="E88" t="n">
-        <v>7.790927021696246e-09</v>
+        <v>3.34431295200526e-08</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6444561773329734</v>
+        <v>0.1519170144315516</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>8.43195266272189e-09</v>
+        <v>3.405851413543722e-08</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6308458229140755</v>
+        <v>0.1485814776368738</v>
       </c>
       <c r="E89" t="n">
-        <v>8.43195266272189e-09</v>
+        <v>3.405851413543722e-08</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6216587316104294</v>
+        <v>0.1467233053910169</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>9.072978303747528e-09</v>
+        <v>3.467389875082183e-08</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6065755971993996</v>
+        <v>0.1438092268836326</v>
       </c>
       <c r="E90" t="n">
-        <v>9.072978303747528e-09</v>
+        <v>3.467389875082183e-08</v>
       </c>
       <c r="F90" t="n">
-        <v>0.599682800838648</v>
+        <v>0.1417170469738047</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>9.714003944773172e-09</v>
+        <v>3.528928336620645e-08</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5823053714847233</v>
+        <v>0.1390369761303914</v>
       </c>
       <c r="E91" t="n">
-        <v>9.714003944773172e-09</v>
+        <v>3.528928336620645e-08</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5784883004232978</v>
+        <v>0.1368903778014131</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1.035502958579881e-08</v>
+        <v>3.590466798159107e-08</v>
       </c>
       <c r="D92" t="n">
-        <v>0.5580351457700473</v>
+        <v>0.1342647253771502</v>
       </c>
       <c r="E92" t="n">
-        <v>1.035502958579881e-08</v>
+        <v>3.590466798159107e-08</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5580351457700473</v>
+        <v>0.1322354364953397</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.099605522682445e-08</v>
+        <v>3.652005259697568e-08</v>
       </c>
       <c r="D93" t="n">
-        <v>0.5411211875919648</v>
+        <v>0.1294924746239089</v>
       </c>
       <c r="E93" t="n">
-        <v>1.099605522682445e-08</v>
+        <v>3.652005259697568e-08</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5382866888431541</v>
+        <v>0.1277443616770824</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1.163708086785009e-08</v>
+        <v>3.71354372123603e-08</v>
       </c>
       <c r="D94" t="n">
-        <v>0.5242072294138824</v>
+        <v>0.1247202238706677</v>
       </c>
       <c r="E94" t="n">
-        <v>1.163708086785009e-08</v>
+        <v>3.71354372123603e-08</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5192200278412328</v>
+        <v>0.123409291968139</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.227810650887574e-08</v>
+        <v>3.775082182774491e-08</v>
       </c>
       <c r="D95" t="n">
-        <v>0.5072932712358</v>
+        <v>0.1199479731174265</v>
       </c>
       <c r="E95" t="n">
-        <v>1.227810650887574e-08</v>
+        <v>3.775082182774491e-08</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5008156975214859</v>
+        <v>0.1192223659900074</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1.291913214990137e-08</v>
+        <v>3.836620644312953e-08</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4903793130577176</v>
+        <v>0.1151757223641853</v>
       </c>
       <c r="E96" t="n">
-        <v>1.291913214990137e-08</v>
+        <v>3.836620644312953e-08</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4830542326411174</v>
+        <v>0.1151757223641853</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.356015779092701e-08</v>
+        <v>3.898159105851414e-08</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4734653548796353</v>
+        <v>0.1118015455658463</v>
       </c>
       <c r="E97" t="n">
-        <v>1.356015779092701e-08</v>
+        <v>3.898159105851414e-08</v>
       </c>
       <c r="F97" t="n">
-        <v>0.46591616795733</v>
+        <v>0.1112622383543389</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1.420118343195266e-08</v>
+        <v>3.959697567389876e-08</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4565513967015526</v>
+        <v>0.1084273687675074</v>
       </c>
       <c r="E98" t="n">
-        <v>1.420118343195266e-08</v>
+        <v>3.959697567389876e-08</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4493820382273268</v>
+        <v>0.1074777457928074</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.48422090729783e-08</v>
+        <v>4.021236028928338e-08</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4396374385234703</v>
+        <v>0.1050531919691684</v>
       </c>
       <c r="E99" t="n">
-        <v>1.48422090729783e-08</v>
+        <v>4.021236028928338e-08</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4334323782083114</v>
+        <v>0.1038188151540984</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1.548323471400394e-08</v>
+        <v>4.082774490466799e-08</v>
       </c>
       <c r="D100" t="n">
-        <v>0.422723480345388</v>
+        <v>0.1016790151708295</v>
       </c>
       <c r="E100" t="n">
-        <v>1.548323471400394e-08</v>
+        <v>4.082774490466799e-08</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4180477226574869</v>
+        <v>0.1002820169127193</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.612426035502959e-08</v>
+        <v>4.144312952005261e-08</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4058095221673053</v>
+        <v>0.0983048383724905</v>
       </c>
       <c r="E101" t="n">
-        <v>1.612426035502959e-08</v>
+        <v>4.144312952005261e-08</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4032086063320561</v>
+        <v>0.09686392154317779</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1.676528599605523e-08</v>
+        <v>4.205851413543722e-08</v>
       </c>
       <c r="D102" t="n">
-        <v>0.388895563989223</v>
+        <v>0.09493066157415156</v>
       </c>
       <c r="E102" t="n">
-        <v>1.676528599605523e-08</v>
+        <v>4.205851413543722e-08</v>
       </c>
       <c r="F102" t="n">
-        <v>0.388895563989223</v>
+        <v>0.09356109951998122</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.740631163708086e-08</v>
+        <v>4.267389875082184e-08</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3771082001380114</v>
+        <v>0.0915564847758126</v>
       </c>
       <c r="E103" t="n">
-        <v>1.740631163708086e-08</v>
+        <v>4.267389875082184e-08</v>
       </c>
       <c r="F103" t="n">
-        <v>0.375089735455479</v>
+        <v>0.09037012131763722</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>1.80473372781065e-08</v>
+        <v>4.328928336620645e-08</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3653208362867997</v>
+        <v>0.08818230797747365</v>
       </c>
       <c r="E104" t="n">
-        <v>1.80473372781065e-08</v>
+        <v>4.328928336620645e-08</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3617746808344706</v>
+        <v>0.0872875574106533</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.868836291913215e-08</v>
+        <v>4.390466798159107e-08</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3535334724355879</v>
+        <v>0.08480813117913469</v>
       </c>
       <c r="E105" t="n">
-        <v>1.868836291913215e-08</v>
+        <v>4.390466798159107e-08</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3489345652991328</v>
+        <v>0.08430997827353696</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>1.932938856015779e-08</v>
+        <v>4.452005259697569e-08</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3417461085843763</v>
+        <v>0.08143395438079574</v>
       </c>
       <c r="E106" t="n">
-        <v>1.932938856015779e-08</v>
+        <v>4.452005259697569e-08</v>
       </c>
       <c r="F106" t="n">
-        <v>0.3365535540224012</v>
+        <v>0.08143395438079574</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.997041420118343e-08</v>
+        <v>4.51354372123603e-08</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3299587447331647</v>
+        <v>0.07904827314669119</v>
       </c>
       <c r="E107" t="n">
-        <v>1.997041420118343e-08</v>
+        <v>4.51354372123603e-08</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3246158121772108</v>
+        <v>0.07865612859069125</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>2.061143984220906e-08</v>
+        <v>4.575082182774492e-08</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3181713808819531</v>
+        <v>0.07666259191258662</v>
       </c>
       <c r="E108" t="n">
-        <v>2.061143984220906e-08</v>
+        <v>4.575082182774492e-08</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3131055049364967</v>
+        <v>0.0759734332965014</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2.125246548323472e-08</v>
+        <v>4.636620644312953e-08</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3063840170307412</v>
+        <v>0.07427691067848205</v>
       </c>
       <c r="E109" t="n">
-        <v>2.125246548323472e-08</v>
+        <v>4.636620644312953e-08</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3020067974731938</v>
+        <v>0.07338287327525818</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2.189349112426035e-08</v>
+        <v>4.698159105851415e-08</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2945966531795296</v>
+        <v>0.07189122944437748</v>
       </c>
       <c r="E110" t="n">
-        <v>2.189349112426035e-08</v>
+        <v>4.698159105851415e-08</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2913038549602379</v>
+        <v>0.07088145330399363</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>2.253451676528599e-08</v>
+        <v>4.759697567389877e-08</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2828092893283179</v>
+        <v>0.06950554821027291</v>
       </c>
       <c r="E111" t="n">
-        <v>2.253451676528599e-08</v>
+        <v>4.759697567389877e-08</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2809808425705635</v>
+        <v>0.06846617815973972</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>2.317554240631163e-08</v>
+        <v>4.821236028928338e-08</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2710219254771064</v>
+        <v>0.06711986697616834</v>
       </c>
       <c r="E112" t="n">
-        <v>2.317554240631163e-08</v>
+        <v>4.821236028928338e-08</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2710219254771064</v>
+        <v>0.06613405261952848</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>2.381656804733728e-08</v>
+        <v>4.8827744904668e-08</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2628072932131518</v>
+        <v>0.06473418574206379</v>
       </c>
       <c r="E113" t="n">
-        <v>2.381656804733728e-08</v>
+        <v>4.8827744904668e-08</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2614121701217584</v>
+        <v>0.06388208146039188</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>2.445759368836292e-08</v>
+        <v>4.944312952005261e-08</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2545926609491974</v>
+        <v>0.06234850450795922</v>
       </c>
       <c r="E114" t="n">
-        <v>2.445759368836292e-08</v>
+        <v>4.944312952005261e-08</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2521402480222421</v>
+        <v>0.06170726945936196</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>2.509861932938855e-08</v>
+        <v>5.005851413543723e-08</v>
       </c>
       <c r="D115" t="n">
-        <v>0.246378028685243</v>
+        <v>0.05996282327385465</v>
       </c>
       <c r="E115" t="n">
-        <v>2.509861932938855e-08</v>
+        <v>5.005851413543723e-08</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2431957319652366</v>
+        <v>0.0596066213934707</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>2.573964497041419e-08</v>
+        <v>5.067389875082183e-08</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2381633964212886</v>
+        <v>0.05757714203975013</v>
       </c>
       <c r="E116" t="n">
-        <v>2.573964497041419e-08</v>
+        <v>5.067389875082183e-08</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2345681947374211</v>
+        <v>0.05757714203975013</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>2.638067061143984e-08</v>
+        <v>5.128928336620645e-08</v>
       </c>
       <c r="D117" t="n">
-        <v>0.229948764157334</v>
+        <v>0.05589036766753571</v>
       </c>
       <c r="E117" t="n">
-        <v>2.638067061143984e-08</v>
+        <v>5.128928336620645e-08</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2262472091254749</v>
+        <v>0.05561600789493083</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>2.702169625246548e-08</v>
+        <v>5.190466798159106e-08</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2217341318933796</v>
+        <v>0.05420359329532128</v>
       </c>
       <c r="E118" t="n">
-        <v>2.702169625246548e-08</v>
+        <v>5.190466798159106e-08</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2182223479160776</v>
+        <v>0.05372108233453801</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>2.766272189349112e-08</v>
+        <v>5.252005259697568e-08</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2135194996294252</v>
+        <v>0.05251681892310686</v>
       </c>
       <c r="E119" t="n">
-        <v>2.766272189349112e-08</v>
+        <v>5.252005259697568e-08</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2104831838959083</v>
+        <v>0.05189040045379547</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>2.830374753451676e-08</v>
+        <v>5.313543721236029e-08</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2053048673654708</v>
+        <v>0.05083004455089243</v>
       </c>
       <c r="E120" t="n">
-        <v>2.830374753451676e-08</v>
+        <v>5.313543721236029e-08</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2030192898516464</v>
+        <v>0.05012199734792704</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>2.894477317554241e-08</v>
+        <v>5.375082182774491e-08</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1970902351015162</v>
+        <v>0.04914327017867801</v>
       </c>
       <c r="E121" t="n">
-        <v>2.894477317554241e-08</v>
+        <v>5.375082182774491e-08</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1958202385699711</v>
+        <v>0.04841390811215651</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>2.958579881656804e-08</v>
+        <v>5.436620644312953e-08</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1888756028375619</v>
+        <v>0.04745649580646359</v>
       </c>
       <c r="E122" t="n">
-        <v>2.958579881656804e-08</v>
+        <v>5.436620644312953e-08</v>
       </c>
       <c r="F122" t="n">
-        <v>0.1888756028375619</v>
+        <v>0.04676416784170771</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>3.022682445759368e-08</v>
+        <v>5.498159105851414e-08</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1831508127925796</v>
+        <v>0.04576972143424916</v>
       </c>
       <c r="E123" t="n">
-        <v>3.022682445759368e-08</v>
+        <v>5.498159105851414e-08</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1821754550296932</v>
+        <v>0.04517081163180443</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>3.086785009861932e-08</v>
+        <v>5.559697567389876e-08</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1774260227475973</v>
+        <v>0.04408294706203474</v>
       </c>
       <c r="E124" t="n">
-        <v>3.086785009861932e-08</v>
+        <v>5.559697567389876e-08</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1757118658760202</v>
+        <v>0.0436318745776705</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>3.150887573964497e-08</v>
+        <v>5.621236028928337e-08</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1717012327026148</v>
+        <v>0.04239617268982032</v>
       </c>
       <c r="E125" t="n">
-        <v>3.150887573964497e-08</v>
+        <v>5.621236028928337e-08</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1694774056947934</v>
+        <v>0.04214539177452972</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>3.214990138067061e-08</v>
+        <v>5.682774490466799e-08</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1659764426576326</v>
+        <v>0.04070939831760589</v>
       </c>
       <c r="E126" t="n">
-        <v>3.214990138067061e-08</v>
+        <v>5.682774490466799e-08</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1634646448042634</v>
+        <v>0.04070939831760589</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>3.279092702169624e-08</v>
+        <v>5.744312952005261e-08</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1602516526126503</v>
+        <v>0.0395167797304763</v>
       </c>
       <c r="E127" t="n">
-        <v>3.279092702169624e-08</v>
+        <v>5.744312952005261e-08</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1576661535226805</v>
+        <v>0.03932201841582961</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>3.343195266272188e-08</v>
+        <v>5.805851413543722e-08</v>
       </c>
       <c r="D128" t="n">
-        <v>0.154526862567668</v>
+        <v>0.0383241611433467</v>
       </c>
       <c r="E128" t="n">
-        <v>3.343195266272188e-08</v>
+        <v>5.805851413543722e-08</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1520745021682952</v>
+        <v>0.03798173273295855</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>3.407297830374753e-08</v>
+        <v>5.867389875082184e-08</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1488020725226855</v>
+        <v>0.03713154255621712</v>
       </c>
       <c r="E129" t="n">
-        <v>3.407297830374753e-08</v>
+        <v>5.867389875082184e-08</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1466822610593578</v>
+        <v>0.03668711104645713</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>3.471400394477317e-08</v>
+        <v>5.928928336620645e-08</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1430772824777032</v>
+        <v>0.03593892396908752</v>
       </c>
       <c r="E130" t="n">
-        <v>3.471400394477317e-08</v>
+        <v>5.928928336620645e-08</v>
       </c>
       <c r="F130" t="n">
-        <v>0.141482000514119</v>
+        <v>0.0354367231337898</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>3.535502958579881e-08</v>
+        <v>5.990466798159107e-08</v>
       </c>
       <c r="D131" t="n">
-        <v>0.137352492432721</v>
+        <v>0.03474630538195793</v>
       </c>
       <c r="E131" t="n">
-        <v>3.535502958579881e-08</v>
+        <v>5.990466798159107e-08</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1364662908508291</v>
+        <v>0.03422913877242099</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>3.599605522682446e-08</v>
+        <v>6.052005259697568e-08</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1316277023877386</v>
+        <v>0.03355368679482833</v>
       </c>
       <c r="E132" t="n">
-        <v>3.599605522682446e-08</v>
+        <v>6.052005259697568e-08</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1316277023877385</v>
+        <v>0.03306292773981512</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>3.66370808678501e-08</v>
+        <v>6.11354372123603e-08</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1276380872709504</v>
+        <v>0.03236106820769874</v>
       </c>
       <c r="E133" t="n">
-        <v>3.66370808678501e-08</v>
+        <v>6.11354372123603e-08</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1269591880405349</v>
+        <v>0.03193665981343666</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>3.727810650887573e-08</v>
+        <v>6.175082182774492e-08</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1236484721541622</v>
+        <v>0.03116844962056915</v>
       </c>
       <c r="E134" t="n">
-        <v>3.727810650887573e-08</v>
+        <v>6.175082182774492e-08</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1224552311146533</v>
+        <v>0.03084890477075001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>3.791913214990137e-08</v>
+        <v>6.236620644312953e-08</v>
       </c>
       <c r="D135" t="n">
-        <v>0.119658857037374</v>
+        <v>0.02997583103343956</v>
       </c>
       <c r="E135" t="n">
-        <v>3.791913214990137e-08</v>
+        <v>6.236620644312953e-08</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1181106975129659</v>
+        <v>0.02979823238921964</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>3.856015779092702e-08</v>
+        <v>6.298159105851415e-08</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1156692419205858</v>
+        <v>0.02878321244630996</v>
       </c>
       <c r="E136" t="n">
-        <v>3.856015779092702e-08</v>
+        <v>6.298159105851415e-08</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1139204531383448</v>
+        <v>0.02878321244630996</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>3.920118343195266e-08</v>
+        <v>6.359697567389876e-08</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1116796268037976</v>
+        <v>0.02793998224445451</v>
       </c>
       <c r="E137" t="n">
-        <v>3.920118343195266e-08</v>
+        <v>6.359697567389876e-08</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1098793638936624</v>
+        <v>0.02780248638172966</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>3.98422090729783e-08</v>
+        <v>6.421236028928338e-08</v>
       </c>
       <c r="D138" t="n">
-        <v>0.1076900116870094</v>
+        <v>0.02709675204259905</v>
       </c>
       <c r="E138" t="n">
-        <v>3.98422090729783e-08</v>
+        <v>6.421236028928338e-08</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1059822956817909</v>
+        <v>0.02685498228416429</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>4.048323471400394e-08</v>
+        <v>6.482774490466799e-08</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1037003965702212</v>
+        <v>0.02625352184074359</v>
       </c>
       <c r="E139" t="n">
-        <v>4.048323471400394e-08</v>
+        <v>6.482774490466799e-08</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1022241144056023</v>
+        <v>0.02593969990454367</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>4.112426035502959e-08</v>
+        <v>6.544312952005261e-08</v>
       </c>
       <c r="D140" t="n">
-        <v>0.09971078145343296</v>
+        <v>0.02541029163888813</v>
       </c>
       <c r="E140" t="n">
-        <v>4.112426035502959e-08</v>
+        <v>6.544312952005261e-08</v>
       </c>
       <c r="F140" t="n">
-        <v>0.09859968596796891</v>
+        <v>0.02505563899379758</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>4.176528599605522e-08</v>
+        <v>6.605851413543723e-08</v>
       </c>
       <c r="D141" t="n">
-        <v>0.09572116633664476</v>
+        <v>0.02456706143703268</v>
       </c>
       <c r="E141" t="n">
-        <v>4.176528599605522e-08</v>
+        <v>6.605851413543723e-08</v>
       </c>
       <c r="F141" t="n">
-        <v>0.09510387627176296</v>
+        <v>0.02420179930285585</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>4.240631163708086e-08</v>
+        <v>6.667389875082184e-08</v>
       </c>
       <c r="D142" t="n">
-        <v>0.09173155121985659</v>
+        <v>0.02372383123517722</v>
       </c>
       <c r="E142" t="n">
-        <v>4.240631163708086e-08</v>
+        <v>6.667389875082184e-08</v>
       </c>
       <c r="F142" t="n">
-        <v>0.09173155121985659</v>
+        <v>0.02337718058264825</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>4.30473372781065e-08</v>
+        <v>6.728928336620646e-08</v>
       </c>
       <c r="D143" t="n">
-        <v>0.0889511822185417</v>
+        <v>0.02288060103332176</v>
       </c>
       <c r="E143" t="n">
-        <v>4.30473372781065e-08</v>
+        <v>6.728928336620646e-08</v>
       </c>
       <c r="F143" t="n">
-        <v>0.08847783412155956</v>
+        <v>0.02258078258410461</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>4.368836291913215e-08</v>
+        <v>6.790466798159107e-08</v>
       </c>
       <c r="D144" t="n">
-        <v>0.08617081321722676</v>
+        <v>0.0220373708314663</v>
       </c>
       <c r="E144" t="n">
-        <v>4.368836291913215e-08</v>
+        <v>6.790466798159107e-08</v>
       </c>
       <c r="F144" t="n">
-        <v>0.08533887791193177</v>
+        <v>0.02181160505815471</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>4.432938856015779e-08</v>
+        <v>6.852005259697569e-08</v>
       </c>
       <c r="D145" t="n">
-        <v>0.08339044421591188</v>
+        <v>0.02119414062961084</v>
       </c>
       <c r="E145" t="n">
-        <v>4.432938856015779e-08</v>
+        <v>6.852005259697569e-08</v>
       </c>
       <c r="F145" t="n">
-        <v>0.08231109293247088</v>
+        <v>0.02106864775572838</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>4.497041420118343e-08</v>
+        <v>6.913543721236031e-08</v>
       </c>
       <c r="D146" t="n">
-        <v>0.08061007521459698</v>
+        <v>0.02035091042775538</v>
       </c>
       <c r="E146" t="n">
-        <v>4.497041420118343e-08</v>
+        <v>6.913543721236031e-08</v>
       </c>
       <c r="F146" t="n">
-        <v>0.07939088952467434</v>
+        <v>0.02035091042775538</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>4.561143984220906e-08</v>
+        <v>6.975082182774492e-08</v>
       </c>
       <c r="D147" t="n">
-        <v>0.07782970621328211</v>
+        <v>0.01975471212848811</v>
       </c>
       <c r="E147" t="n">
-        <v>4.561143984220906e-08</v>
+        <v>6.975082182774492e-08</v>
       </c>
       <c r="F147" t="n">
-        <v>0.07657467803003967</v>
+        <v>0.01965744117165312</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>4.625246548323471e-08</v>
+        <v>7.036620644312954e-08</v>
       </c>
       <c r="D148" t="n">
-        <v>0.07504933721196716</v>
+        <v>0.01915851382922084</v>
       </c>
       <c r="E148" t="n">
-        <v>4.625246548323471e-08</v>
+        <v>7.036620644312954e-08</v>
       </c>
       <c r="F148" t="n">
-        <v>0.07385886879006434</v>
+        <v>0.0189874814707892</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>4.689349112426035e-08</v>
+        <v>7.098159105851415e-08</v>
       </c>
       <c r="D149" t="n">
-        <v>0.07226896821065228</v>
+        <v>0.01856231552995357</v>
       </c>
       <c r="E149" t="n">
-        <v>4.689349112426035e-08</v>
+        <v>7.098159105851415e-08</v>
       </c>
       <c r="F149" t="n">
-        <v>0.07123987214624598</v>
+        <v>0.01834032115501884</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>4.753451676528599e-08</v>
+        <v>7.159697567389877e-08</v>
       </c>
       <c r="D150" t="n">
-        <v>0.06948859920933739</v>
+        <v>0.0179661172306863</v>
       </c>
       <c r="E150" t="n">
-        <v>4.753451676528599e-08</v>
+        <v>7.159697567389877e-08</v>
       </c>
       <c r="F150" t="n">
-        <v>0.06871409844008207</v>
+        <v>0.01771525005419724</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4.817554240631163e-08</v>
+        <v>7.221236028928338e-08</v>
       </c>
       <c r="D151" t="n">
-        <v>0.06670823020802251</v>
+        <v>0.01736991893141903</v>
       </c>
       <c r="E151" t="n">
-        <v>4.817554240631163e-08</v>
+        <v>7.221236028928338e-08</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0662779580130701</v>
+        <v>0.01711155799817958</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>4.881656804733728e-08</v>
+        <v>7.2827744904668e-08</v>
       </c>
       <c r="D152" t="n">
-        <v>0.06392786120670758</v>
+        <v>0.01677372063215175</v>
       </c>
       <c r="E152" t="n">
-        <v>4.881656804733728e-08</v>
+        <v>7.2827744904668e-08</v>
       </c>
       <c r="F152" t="n">
-        <v>0.06392786120670758</v>
+        <v>0.01652853481682109</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>4.945759368836292e-08</v>
+        <v>7.344312952005262e-08</v>
       </c>
       <c r="D153" t="n">
-        <v>0.06199021771048581</v>
+        <v>0.01617752233288448</v>
       </c>
       <c r="E153" t="n">
-        <v>4.945759368836292e-08</v>
+        <v>7.344312952005262e-08</v>
       </c>
       <c r="F153" t="n">
-        <v>0.06166040022132834</v>
+        <v>0.01596547033997695</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>5.009861932938855e-08</v>
+        <v>7.405851413543723e-08</v>
       </c>
       <c r="D154" t="n">
-        <v>0.06005257421426403</v>
+        <v>0.01558132403361721</v>
       </c>
       <c r="E154" t="n">
-        <v>5.009861932938855e-08</v>
+        <v>7.405851413543723e-08</v>
       </c>
       <c r="F154" t="n">
-        <v>0.05947289469261102</v>
+        <v>0.01542165439750237</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>5.073964497041419e-08</v>
+        <v>7.467389875082185e-08</v>
       </c>
       <c r="D155" t="n">
-        <v>0.05811493071804225</v>
+        <v>0.01498512573434994</v>
       </c>
       <c r="E155" t="n">
-        <v>5.073964497041419e-08</v>
+        <v>7.467389875082185e-08</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0573628461150705</v>
+        <v>0.01489637681925254</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>5.138067061143984e-08</v>
+        <v>7.528928336620646e-08</v>
       </c>
       <c r="D156" t="n">
-        <v>0.05617728722182043</v>
+        <v>0.01438892743508267</v>
       </c>
       <c r="E156" t="n">
-        <v>5.138067061143984e-08</v>
+        <v>7.528928336620646e-08</v>
       </c>
       <c r="F156" t="n">
-        <v>0.05532775598322167</v>
+        <v>0.01438892743508267</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>5.202169625246548e-08</v>
+        <v>7.590466798159108e-08</v>
       </c>
       <c r="D157" t="n">
-        <v>0.05423964372559865</v>
+        <v>0.01396739081167065</v>
       </c>
       <c r="E157" t="n">
-        <v>5.202169625246548e-08</v>
+        <v>7.590466798159108e-08</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0533651257915795</v>
+        <v>0.013898630889213</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>5.266272189349112e-08</v>
+        <v>7.65200525969757e-08</v>
       </c>
       <c r="D158" t="n">
-        <v>0.05230200022937687</v>
+        <v>0.01354585418825864</v>
       </c>
       <c r="E158" t="n">
-        <v>5.266272189349112e-08</v>
+        <v>7.65200525969757e-08</v>
       </c>
       <c r="F158" t="n">
-        <v>0.05147245703465887</v>
+        <v>0.0134249510833239</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>5.330374753451675e-08</v>
+        <v>7.71354372123603e-08</v>
       </c>
       <c r="D159" t="n">
-        <v>0.05036435673315509</v>
+        <v>0.01312431756484662</v>
       </c>
       <c r="E159" t="n">
-        <v>5.330374753451675e-08</v>
+        <v>7.71354372123603e-08</v>
       </c>
       <c r="F159" t="n">
-        <v>0.04964725120697468</v>
+        <v>0.01296738673346081</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5.39447731755424e-08</v>
+        <v>7.775082182774493e-08</v>
       </c>
       <c r="D160" t="n">
-        <v>0.04842671323693327</v>
+        <v>0.0127027809414346</v>
       </c>
       <c r="E160" t="n">
-        <v>5.39447731755424e-08</v>
+        <v>7.775082182774493e-08</v>
       </c>
       <c r="F160" t="n">
-        <v>0.04788700980304178</v>
+        <v>0.01252543655566912</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>5.458579881656804e-08</v>
+        <v>7.836620644312953e-08</v>
       </c>
       <c r="D161" t="n">
-        <v>0.04648906974071149</v>
+        <v>0.01228124431802259</v>
       </c>
       <c r="E161" t="n">
-        <v>5.458579881656804e-08</v>
+        <v>7.836620644312953e-08</v>
       </c>
       <c r="F161" t="n">
-        <v>0.04618923431737517</v>
+        <v>0.01209859926599429</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>5.522682445759368e-08</v>
+        <v>7.898159105851416e-08</v>
       </c>
       <c r="D162" t="n">
-        <v>0.04455142624448971</v>
+        <v>0.01185970769461056</v>
       </c>
       <c r="E162" t="n">
-        <v>5.522682445759368e-08</v>
+        <v>7.898159105851416e-08</v>
       </c>
       <c r="F162" t="n">
-        <v>0.04455142624448971</v>
+        <v>0.01168637358048171</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>5.586785009861933e-08</v>
+        <v>7.959697567389876e-08</v>
       </c>
       <c r="D163" t="n">
-        <v>0.04320107946797368</v>
+        <v>0.01143817107119855</v>
       </c>
       <c r="E163" t="n">
-        <v>5.586785009861933e-08</v>
+        <v>7.959697567389876e-08</v>
       </c>
       <c r="F163" t="n">
-        <v>0.04297121315536773</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="n">
-        <v>5.650887573964497e-08</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.04185073269145769</v>
-      </c>
-      <c r="E164" t="n">
-        <v>5.650887573964497e-08</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.04144672692686144</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="n">
-        <v>5.714990138067061e-08</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0.04050038591494169</v>
-      </c>
-      <c r="E165" t="n">
-        <v>5.714990138067061e-08</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0.03997622551229046</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="n">
-        <v>5.779092702169624e-08</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.03915003913842569</v>
-      </c>
-      <c r="E166" t="n">
-        <v>5.779092702169624e-08</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.03855796686497438</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="n">
-        <v>5.843195266272189e-08</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.03779969236190966</v>
-      </c>
-      <c r="E167" t="n">
-        <v>5.843195266272189e-08</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.03719020893823282</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="n">
-        <v>5.907297830374753e-08</v>
-      </c>
-      <c r="D168" t="n">
-        <v>0.03644934558539367</v>
-      </c>
-      <c r="E168" t="n">
-        <v>5.907297830374753e-08</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.03587120968538542</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="n">
-        <v>5.971400394477318e-08</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.03509899880887766</v>
-      </c>
-      <c r="E169" t="n">
-        <v>5.971400394477318e-08</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.03459922705975178</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="n">
-        <v>6.035502958579881e-08</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0.03374865203236166</v>
-      </c>
-      <c r="E170" t="n">
-        <v>6.035502958579881e-08</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.03337251901465153</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr"/>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="n">
-        <v>6.099605522682445e-08</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0.03239830525584567</v>
-      </c>
-      <c r="E171" t="n">
-        <v>6.099605522682445e-08</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.03218934350340429</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr"/>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="n">
-        <v>6.163708086785009e-08</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.03104795847932967</v>
-      </c>
-      <c r="E172" t="n">
-        <v>6.163708086785009e-08</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.03104795847932967</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr"/>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="n">
-        <v>6.227810650887573e-08</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.03010689970334602</v>
-      </c>
-      <c r="E173" t="n">
-        <v>6.227810650887573e-08</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.02994670993170339</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="n">
-        <v>6.291913214990136e-08</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0.02916584092736237</v>
-      </c>
-      <c r="E174" t="n">
-        <v>6.291913214990136e-08</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.02888429599362555</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr"/>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="n">
-        <v>6.356015779092703e-08</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.02822478215137867</v>
-      </c>
-      <c r="E175" t="n">
-        <v>6.356015779092703e-08</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.02785950283415236</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="n">
-        <v>6.420118343195267e-08</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0.02728372337539502</v>
-      </c>
-      <c r="E176" t="n">
-        <v>6.420118343195267e-08</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.02687111662234009</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="n">
-        <v>6.48422090729783e-08</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0.02634266459941137</v>
-      </c>
-      <c r="E177" t="n">
-        <v>6.48422090729783e-08</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0.02591792352724492</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="n">
-        <v>6.548323471400394e-08</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0.02540160582342772</v>
-      </c>
-      <c r="E178" t="n">
-        <v>6.548323471400394e-08</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0.02499870971792307</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr"/>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="n">
-        <v>6.612426035502958e-08</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0.02446054704744407</v>
-      </c>
-      <c r="E179" t="n">
-        <v>6.612426035502958e-08</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.02411226136343074</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="n">
-        <v>6.676528599605522e-08</v>
-      </c>
-      <c r="D180" t="n">
-        <v>0.02351948827146042</v>
-      </c>
-      <c r="E180" t="n">
-        <v>6.676528599605522e-08</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.02325736463282416</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="n">
-        <v>6.740631163708085e-08</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0.02257842949547677</v>
-      </c>
-      <c r="E181" t="n">
-        <v>6.740631163708085e-08</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.02243280569515956</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="n">
-        <v>6.804733727810649e-08</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.02163737071949312</v>
-      </c>
-      <c r="E182" t="n">
-        <v>6.804733727810649e-08</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.02163737071949312</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="n">
-        <v>6.868836291913216e-08</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0.02098154538983907</v>
-      </c>
-      <c r="E183" t="n">
-        <v>6.868836291913216e-08</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.0208699071962389</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="n">
-        <v>6.932938856015779e-08</v>
-      </c>
-      <c r="D184" t="n">
-        <v>0.02032572006018505</v>
-      </c>
-      <c r="E184" t="n">
-        <v>6.932938856015779e-08</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.02012950790124247</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="n">
-        <v>6.997041420118343e-08</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0.01966989473053103</v>
-      </c>
-      <c r="E185" t="n">
-        <v>6.997041420118343e-08</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.01941532693170714</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr"/>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="n">
-        <v>7.061143984220907e-08</v>
-      </c>
-      <c r="D186" t="n">
-        <v>0.01901406940087701</v>
-      </c>
-      <c r="E186" t="n">
-        <v>7.061143984220907e-08</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.01872651838483628</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="n">
-        <v>7.125246548323471e-08</v>
-      </c>
-      <c r="D187" t="n">
-        <v>0.018358244071223</v>
-      </c>
-      <c r="E187" t="n">
-        <v>7.125246548323471e-08</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.01806223635783324</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="n">
-        <v>7.189349112426034e-08</v>
-      </c>
-      <c r="D188" t="n">
-        <v>0.01770241874156897</v>
-      </c>
-      <c r="E188" t="n">
-        <v>7.189349112426034e-08</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.01742163494790138</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="n">
-        <v>7.253451676528598e-08</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.01704659341191496</v>
-      </c>
-      <c r="E189" t="n">
-        <v>7.253451676528598e-08</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.01680386825224406</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="n">
-        <v>7.317554240631162e-08</v>
-      </c>
-      <c r="D190" t="n">
-        <v>0.01639076808226093</v>
-      </c>
-      <c r="E190" t="n">
-        <v>7.317554240631162e-08</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.01620809036806463</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="n">
-        <v>7.381656804733726e-08</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0.01573494275260692</v>
-      </c>
-      <c r="E191" t="n">
-        <v>7.381656804733726e-08</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0.01563345539256646</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="n">
-        <v>7.445759368836289e-08</v>
-      </c>
-      <c r="D192" t="n">
-        <v>0.0150791174229529</v>
-      </c>
-      <c r="E192" t="n">
-        <v>7.445759368836289e-08</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.0150791174229529</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="n">
-        <v>7.509861932938856e-08</v>
-      </c>
-      <c r="D193" t="n">
-        <v>0.01462207172719787</v>
-      </c>
-      <c r="E193" t="n">
-        <v>7.509861932938856e-08</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.01454427324245747</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="n">
-        <v>7.57396449704142e-08</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0.01416502603144286</v>
-      </c>
-      <c r="E194" t="n">
-        <v>7.57396449704142e-08</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.01402829037843456</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="n">
-        <v>7.638067061143983e-08</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.01370798033568786</v>
-      </c>
-      <c r="E195" t="n">
-        <v>7.638067061143983e-08</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.01353057904426864</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="n">
-        <v>7.702169625246547e-08</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0.01325093463993285</v>
-      </c>
-      <c r="E196" t="n">
-        <v>7.702169625246547e-08</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.01305054945334425</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="n">
-        <v>7.766272189349111e-08</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.01279388894417784</v>
-      </c>
-      <c r="E197" t="n">
-        <v>7.766272189349111e-08</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.0125876118190459</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="n">
-        <v>7.830374753451675e-08</v>
-      </c>
-      <c r="D198" t="n">
-        <v>0.01233684324842284</v>
-      </c>
-      <c r="E198" t="n">
-        <v>7.830374753451675e-08</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.0121411763547581</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="n">
-        <v>7.894477317554238e-08</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0.01187979755266783</v>
-      </c>
-      <c r="E199" t="n">
-        <v>7.894477317554238e-08</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.01171065327386537</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="n">
-        <v>7.958579881656805e-08</v>
-      </c>
-      <c r="D200" t="n">
-        <v>0.0114227518569128</v>
-      </c>
-      <c r="E200" t="n">
-        <v>7.958579881656805e-08</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0.01129545278975222</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="n">
-        <v>8.022682445759369e-08</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.0109657061611578</v>
-      </c>
-      <c r="E201" t="n">
-        <v>8.022682445759369e-08</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.01089498511580319</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="n">
-        <v>8.086785009861932e-08</v>
-      </c>
-      <c r="D202" t="n">
-        <v>0.01050866046540279</v>
-      </c>
-      <c r="E202" t="n">
-        <v>8.086785009861932e-08</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.01050866046540279</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="n">
-        <v>8.150887573964496e-08</v>
-      </c>
-      <c r="D203" t="n">
-        <v>0.01019014460673905</v>
-      </c>
-      <c r="E203" t="n">
-        <v>8.150887573964496e-08</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.01013591902661313</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="n">
-        <v>8.21499013806706e-08</v>
-      </c>
-      <c r="D204" t="n">
-        <v>0.009871628748075317</v>
-      </c>
-      <c r="E204" t="n">
-        <v>8.21499013806706e-08</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.009776320886206724</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="n">
-        <v>8.279092702169624e-08</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0.00955311288941158</v>
-      </c>
-      <c r="E205" t="n">
-        <v>8.279092702169624e-08</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0.009429456105633675</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="n">
-        <v>8.343195266272187e-08</v>
-      </c>
-      <c r="D206" t="n">
-        <v>0.009234597030747844</v>
-      </c>
-      <c r="E206" t="n">
-        <v>8.343195266272187e-08</v>
-      </c>
-      <c r="F206" t="n">
-        <v>0.00909491474634409</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="n">
-        <v>8.407297830374751e-08</v>
-      </c>
-      <c r="D207" t="n">
-        <v>0.008916081172084107</v>
-      </c>
-      <c r="E207" t="n">
-        <v>8.407297830374751e-08</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.008772286869788081</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="n">
-        <v>8.471400394477318e-08</v>
-      </c>
-      <c r="D208" t="n">
-        <v>0.008597565313420357</v>
-      </c>
-      <c r="E208" t="n">
-        <v>8.471400394477318e-08</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.008461162537415742</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="n">
-        <v>8.535502958579881e-08</v>
-      </c>
-      <c r="D209" t="n">
-        <v>0.008279049454756621</v>
-      </c>
-      <c r="E209" t="n">
-        <v>8.535502958579881e-08</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.008161131810677206</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr"/>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="n">
-        <v>8.599605522682445e-08</v>
-      </c>
-      <c r="D210" t="n">
-        <v>0.007960533596092884</v>
-      </c>
-      <c r="E210" t="n">
-        <v>8.599605522682445e-08</v>
-      </c>
-      <c r="F210" t="n">
-        <v>0.007871784751022567</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr"/>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="n">
-        <v>8.663708086785009e-08</v>
-      </c>
-      <c r="D211" t="n">
-        <v>0.007642017737429147</v>
-      </c>
-      <c r="E211" t="n">
-        <v>8.663708086785009e-08</v>
-      </c>
-      <c r="F211" t="n">
-        <v>0.007592711419901934</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr"/>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="n">
-        <v>8.727810650887573e-08</v>
-      </c>
-      <c r="D212" t="n">
-        <v>0.007323501878765411</v>
-      </c>
-      <c r="E212" t="n">
-        <v>8.727810650887573e-08</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0.007323501878765411</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="n">
-        <v>8.791913214990136e-08</v>
-      </c>
-      <c r="D213" t="n">
-        <v>0.007101527679768294</v>
-      </c>
-      <c r="E213" t="n">
-        <v>8.791913214990136e-08</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.007063766220516353</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr"/>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="n">
-        <v>8.8560157790927e-08</v>
-      </c>
-      <c r="D214" t="n">
-        <v>0.006879553480771177</v>
-      </c>
-      <c r="E214" t="n">
-        <v>8.8560157790927e-08</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.00681319466387109</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr"/>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="n">
-        <v>8.920118343195264e-08</v>
-      </c>
-      <c r="D215" t="n">
-        <v>0.00665757928177406</v>
-      </c>
-      <c r="E215" t="n">
-        <v>8.920118343195264e-08</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.00657149745899919</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr"/>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="n">
-        <v>8.98422090729783e-08</v>
-      </c>
-      <c r="D216" t="n">
-        <v>0.006435605082776934</v>
-      </c>
-      <c r="E216" t="n">
-        <v>8.98422090729783e-08</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.006338384856070219</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr"/>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="n">
-        <v>9.048323471400394e-08</v>
-      </c>
-      <c r="D217" t="n">
-        <v>0.006213630883779817</v>
-      </c>
-      <c r="E217" t="n">
-        <v>9.048323471400394e-08</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.00611356710525377</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr"/>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="n">
-        <v>9.112426035502958e-08</v>
-      </c>
-      <c r="D218" t="n">
-        <v>0.005991656684782701</v>
-      </c>
-      <c r="E218" t="n">
-        <v>9.112426035502958e-08</v>
-      </c>
-      <c r="F218" t="n">
-        <v>0.005896754456719405</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr"/>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="n">
-        <v>9.176528599605522e-08</v>
-      </c>
-      <c r="D219" t="n">
-        <v>0.005769682485785584</v>
-      </c>
-      <c r="E219" t="n">
-        <v>9.176528599605522e-08</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.005687657160636696</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr"/>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="n">
-        <v>9.240631163708085e-08</v>
-      </c>
-      <c r="D220" t="n">
-        <v>0.005547708286788466</v>
-      </c>
-      <c r="E220" t="n">
-        <v>9.240631163708085e-08</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0.005485985467175216</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr"/>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="n">
-        <v>9.304733727810649e-08</v>
-      </c>
-      <c r="D221" t="n">
-        <v>0.005325734087791349</v>
-      </c>
-      <c r="E221" t="n">
-        <v>9.304733727810649e-08</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0.005291449626504537</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr"/>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="n">
-        <v>9.368836291913213e-08</v>
-      </c>
-      <c r="D222" t="n">
-        <v>0.005103759888794233</v>
-      </c>
-      <c r="E222" t="n">
-        <v>9.368836291913213e-08</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.005103759888794233</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="n">
-        <v>9.432938856015777e-08</v>
-      </c>
-      <c r="D223" t="n">
-        <v>0.004949065723087308</v>
-      </c>
-      <c r="E223" t="n">
-        <v>9.432938856015777e-08</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.004922643669233783</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr"/>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="n">
-        <v>9.497041420118343e-08</v>
-      </c>
-      <c r="D224" t="n">
-        <v>0.004794371557380377</v>
-      </c>
-      <c r="E224" t="n">
-        <v>9.497041420118343e-08</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0.004747897043092288</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="n">
-        <v>9.561143984220907e-08</v>
-      </c>
-      <c r="D225" t="n">
-        <v>0.004639677391673451</v>
-      </c>
-      <c r="E225" t="n">
-        <v>9.561143984220907e-08</v>
-      </c>
-      <c r="F225" t="n">
-        <v>0.004579333250658781</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr"/>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="n">
-        <v>9.625246548323471e-08</v>
-      </c>
-      <c r="D226" t="n">
-        <v>0.004484983225966526</v>
-      </c>
-      <c r="E226" t="n">
-        <v>9.625246548323471e-08</v>
-      </c>
-      <c r="F226" t="n">
-        <v>0.004416765532222268</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="n">
-        <v>9.689349112426034e-08</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.0043302890602596</v>
-      </c>
-      <c r="E227" t="n">
-        <v>9.689349112426034e-08</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.004260007128071766</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr"/>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="n">
-        <v>9.753451676528598e-08</v>
-      </c>
-      <c r="D228" t="n">
-        <v>0.004175594894552675</v>
-      </c>
-      <c r="E228" t="n">
-        <v>9.753451676528598e-08</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.00410887127849629</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="n">
-        <v>9.817554240631162e-08</v>
-      </c>
-      <c r="D229" t="n">
-        <v>0.00402090072884575</v>
-      </c>
-      <c r="E229" t="n">
-        <v>9.817554240631162e-08</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.003963171223784858</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="n">
-        <v>9.881656804733726e-08</v>
-      </c>
-      <c r="D230" t="n">
-        <v>0.003866206563138825</v>
-      </c>
-      <c r="E230" t="n">
-        <v>9.881656804733726e-08</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0.003822720204226483</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="n">
-        <v>9.945759368836292e-08</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.003711512397431894</v>
-      </c>
-      <c r="E231" t="n">
-        <v>9.945759368836292e-08</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0.003687331460110179</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr"/>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="n">
-        <v>1.000986193293886e-07</v>
-      </c>
-      <c r="D232" t="n">
-        <v>0.003556818231724971</v>
-      </c>
-      <c r="E232" t="n">
-        <v>1.000986193293886e-07</v>
-      </c>
-      <c r="F232" t="n">
-        <v>0.00355681823172497</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="n">
-        <v>1.007396449704142e-07</v>
-      </c>
-      <c r="D233" t="n">
-        <v>0.00344901162621911</v>
-      </c>
-      <c r="E233" t="n">
-        <v>1.007396449704142e-07</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0.003430993759359867</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr"/>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="n">
-        <v>1.013806706114398e-07</v>
-      </c>
-      <c r="D234" t="n">
-        <v>0.00334120502071325</v>
-      </c>
-      <c r="E234" t="n">
-        <v>1.013806706114398e-07</v>
-      </c>
-      <c r="F234" t="n">
-        <v>0.003309671283303887</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="n">
-        <v>1.020216962524655e-07</v>
-      </c>
-      <c r="D235" t="n">
-        <v>0.003233398415207389</v>
-      </c>
-      <c r="E235" t="n">
-        <v>1.020216962524655e-07</v>
-      </c>
-      <c r="F235" t="n">
-        <v>0.003192664043846045</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="n">
-        <v>1.026627218934911e-07</v>
-      </c>
-      <c r="D236" t="n">
-        <v>0.003125591809701529</v>
-      </c>
-      <c r="E236" t="n">
-        <v>1.026627218934911e-07</v>
-      </c>
-      <c r="F236" t="n">
-        <v>0.003079785281275357</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="n">
-        <v>1.033037475345167e-07</v>
-      </c>
-      <c r="D237" t="n">
-        <v>0.003017785204195668</v>
-      </c>
-      <c r="E237" t="n">
-        <v>1.033037475345167e-07</v>
-      </c>
-      <c r="F237" t="n">
-        <v>0.00297084823588084</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="n">
-        <v>1.039447731755424e-07</v>
-      </c>
-      <c r="D238" t="n">
-        <v>0.002909978598689807</v>
-      </c>
-      <c r="E238" t="n">
-        <v>1.039447731755424e-07</v>
-      </c>
-      <c r="F238" t="n">
-        <v>0.002865666147951509</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="n">
-        <v>1.04585798816568e-07</v>
-      </c>
-      <c r="D239" t="n">
-        <v>0.002802171993183942</v>
-      </c>
-      <c r="E239" t="n">
-        <v>1.04585798816568e-07</v>
-      </c>
-      <c r="F239" t="n">
-        <v>0.002764052257776376</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr"/>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="n">
-        <v>1.052268244575937e-07</v>
-      </c>
-      <c r="D240" t="n">
-        <v>0.002694365387678082</v>
-      </c>
-      <c r="E240" t="n">
-        <v>1.052268244575937e-07</v>
-      </c>
-      <c r="F240" t="n">
-        <v>0.002665819805644465</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr"/>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="n">
-        <v>1.058678500986193e-07</v>
-      </c>
-      <c r="D241" t="n">
-        <v>0.002586558782172221</v>
-      </c>
-      <c r="E241" t="n">
-        <v>1.058678500986193e-07</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0.002570782031844787</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="n">
-        <v>1.06508875739645e-07</v>
-      </c>
-      <c r="D242" t="n">
-        <v>0.002478752176666358</v>
-      </c>
-      <c r="E242" t="n">
-        <v>1.06508875739645e-07</v>
-      </c>
-      <c r="F242" t="n">
-        <v>0.002478752176666359</v>
+        <v>0.01128825821517683</v>
       </c>
     </row>
   </sheetData>

--- a/python_imp/samples_export.xlsx
+++ b/python_imp/samples_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,2658 +462,2558 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.03555034011478109</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.947994740302433e-08</v>
+        <v>-1.977317554240632e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009778957441417161</v>
+        <v>0.01150780403081407</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.947994740302433e-08</v>
+        <v>-1.977317554240632e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005085960215905115</v>
+        <v>0.002394924659875125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.3246524673583495</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.886456278763971e-08</v>
+        <v>-1.913214990138068e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01133085547530101</v>
+        <v>0.01494245204280935</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.886456278763971e-08</v>
+        <v>-1.913214990138068e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00700509110280086</v>
+        <v>0.003714298895243349</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.9168553557320287</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.82491781722551e-08</v>
+        <v>-1.849112426035503e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01288275350918486</v>
+        <v>0.01837710005480464</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.82491781722551e-08</v>
+        <v>-1.849112426035503e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009419777377621223</v>
+        <v>0.00583378024849325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.443129520052593e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9706970133569975</v>
+        <v>0.8007374029168086</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.763379355687048e-08</v>
+        <v>-1.785009861932939e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01443465154306871</v>
+        <v>0.02181174806679993</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.763379355687048e-08</v>
+        <v>-1.785009861932939e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0123927024118454</v>
+        <v>0.008956727186248062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.5580351457700473</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-1.720907297830375e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.02524639607879521</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.701840894148587e-08</v>
+        <v>-1.720907297830375e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01598654957695256</v>
+        <v>0.01328649817513101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.388895563989223</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.640302432610125e-08</v>
+        <v>-1.656804733727811e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0329202506642956</v>
+        <v>0.02868104409079052</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.640302432610125e-08</v>
+        <v>-1.656804733727811e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02034945972472026</v>
+        <v>0.01902645168176538</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.2710219254771064</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.578763971071664e-08</v>
+        <v>-1.592702169625247e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04985395175163863</v>
+        <v>0.0321156921027858</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.578763971071664e-08</v>
+        <v>-1.592702169625247e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02597140362811955</v>
+        <v>0.02637994617277428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.1888756028375619</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.517225509533202e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06678765283898166</v>
+        <v>0.03555034011478109</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.517225509533202e-08</v>
+        <v>-1.528599605522683e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03342780954041986</v>
+        <v>0.03555034011478109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>3.599605522682445e-08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1316277023877387</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.45568704799474e-08</v>
+        <v>-1.464497041420119e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08372135392632468</v>
+        <v>0.06446055283913779</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.45568704799474e-08</v>
+        <v>-1.464497041420119e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04329410571489062</v>
+        <v>0.04679372182977039</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.09173155121985659</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.394148586456279e-08</v>
+        <v>-1.400394477317555e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1006550550136677</v>
+        <v>0.09337076556349479</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.394148586456279e-08</v>
+        <v>-1.400394477317555e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05614572040480127</v>
+        <v>0.06057709906117316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.452005259697567e-08</v>
+        <v>4.881656804733726e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0814339543807958</v>
+        <v>0.06392786120670763</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.332610124917817e-08</v>
+        <v>-1.336291913214991e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1175887561010107</v>
+        <v>0.1222809782878515</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.332610124917817e-08</v>
+        <v>-1.336291913214991e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07255808186342123</v>
+        <v>0.07742020940778141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.04455142624448971</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.271071663379356e-08</v>
+        <v>-1.272189349112426e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1345224571883538</v>
+        <v>0.1511911910122085</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.271071663379356e-08</v>
+        <v>-1.272189349112426e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09310661834401994</v>
+        <v>0.09784279046838777</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="B14" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.03104795847932967</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.209533201840894e-08</v>
+        <v>-1.208086785009863e-08</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1514561582756968</v>
+        <v>0.1801014037365652</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.209533201840894e-08</v>
+        <v>-1.208086785009863e-08</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1183667580998668</v>
+        <v>0.1223645798417841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.02163737071949312</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.147994740302433e-08</v>
+        <v>-1.143984220907298e-08</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1683898593630398</v>
+        <v>0.2090116164609221</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.147994740302433e-08</v>
+        <v>-1.143984220907298e-08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1489139293842313</v>
+        <v>0.1515053151267632</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.0150791174229529</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-1.079881656804734e-08</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.2379218291852788</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.086456278763971e-08</v>
+        <v>-1.079881656804734e-08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1853235604503829</v>
+        <v>0.1857847339221168</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>7.528928336620645e-08</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.01438892743508268</v>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-1.024917817225509e-08</v>
+        <v>-1.01577909270217e-08</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2396318221284143</v>
+        <v>0.2668320419096359</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.024917817225509e-08</v>
+        <v>-1.01577909270217e-08</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2279010363539921</v>
+        <v>0.2257225738266377</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-9.633793556870478e-09</v>
+        <v>-9.516765285996062e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2939400838064458</v>
+        <v>0.2957422546339926</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.633793556870478e-09</v>
+        <v>-9.516765285996062e-09</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2758715693603346</v>
+        <v>0.2718385724391176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-9.018408941485862e-09</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3482483454844773</v>
+        <v>0.3246524673583495</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.018408941485862e-09</v>
+        <v>-8.875739644970418e-09</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3281903285370875</v>
+        <v>0.3246524673583495</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-8.403024326101253e-09</v>
+        <v>-8.23471400394478e-09</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4025566071625081</v>
+        <v>0.3838727561957171</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.403024326101253e-09</v>
+        <v>-8.23471400394478e-09</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3838124829519267</v>
+        <v>0.3842653335537005</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-7.787639710716637e-09</v>
+        <v>-7.593688362919136e-09</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4568648688405396</v>
+        <v>0.4430930450330853</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.787639710716637e-09</v>
+        <v>-7.593688362919136e-09</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4416932016725303</v>
+        <v>0.4491035954768428</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-7.172255095332021e-09</v>
+        <v>-6.952662721893498e-09</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5111731305185711</v>
+        <v>0.502313333870453</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.172255095332021e-09</v>
+        <v>-6.952662721893498e-09</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5007876537665746</v>
+        <v>0.5171750149500214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>-6.556870479947405e-09</v>
+        <v>-6.311637080867854e-09</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5654813921966024</v>
+        <v>0.5615336227078211</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.556870479947405e-09</v>
+        <v>-6.311637080867854e-09</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5600510083017367</v>
+        <v>0.5864873537954844</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-5.94148586456279e-09</v>
+        <v>-5.67061143984221e-09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6197896538746339</v>
+        <v>0.6207539115451894</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.94148586456279e-09</v>
+        <v>-5.67061143984221e-09</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6184384343456931</v>
+        <v>0.6550483738354778</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-5.326101249178174e-09</v>
+        <v>-5.029585798816572e-09</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6740979155526654</v>
+        <v>0.6799742003825571</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.326101249178174e-09</v>
+        <v>-5.029585798816572e-09</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6749051009661208</v>
+        <v>0.7208658368922475</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-4.388560157790928e-09</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.7391944892199253</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.710716633793558e-09</v>
+        <v>-4.388560157790928e-09</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7284061772306969</v>
+        <v>0.7819475047880411</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-4.095332018408942e-09</v>
+        <v>-3.74753451676529e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>0.752635260843327</v>
+        <v>0.7984147780572928</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.095332018408942e-09</v>
+        <v>-3.74753451676529e-09</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7779970825552612</v>
+        <v>0.8363011393451045</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-3.479947403024326e-09</v>
+        <v>-3.106508875739646e-09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7768643444559571</v>
+        <v>0.8576350668946611</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.479947403024326e-09</v>
+        <v>-3.106508875739646e-09</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8231342377483085</v>
+        <v>0.8819345023856852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-2.864562787639711e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8010934280685872</v>
+        <v>0.9168553557320287</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.864562787639711e-09</v>
+        <v>-2.465483234714009e-09</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8633743139664963</v>
+        <v>0.9168553557320287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-2.249178172255095e-09</v>
+        <v>-1.824457593688364e-09</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8253225116812173</v>
+        <v>0.9052435604505066</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.249178172255095e-09</v>
+        <v>-1.824457593688364e-09</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8982739823664824</v>
+        <v>0.9396336151523926</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-1.633793556870479e-09</v>
+        <v>-1.183431952662727e-09</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8495515952938474</v>
+        <v>0.8936317651689847</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.633793556870479e-09</v>
+        <v>-1.183431952662727e-09</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9273899141049244</v>
+        <v>0.9510878121990735</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-1.018408941485863e-09</v>
+        <v>-5.424063116370826e-10</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8737806789064775</v>
+        <v>0.8820199698874627</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.018408941485863e-09</v>
+        <v>-5.424063116370826e-10</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9502787803384803</v>
+        <v>0.9525986323703789</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-4.030243261012473e-10</v>
+        <v>9.861932938855505e-11</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8980097625191075</v>
+        <v>0.8704081746059407</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.030243261012473e-10</v>
+        <v>9.861932938855505e-11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9664972522238078</v>
+        <v>0.945546761164616</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>2.123602892833685e-10</v>
+        <v>7.396449704141993e-10</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9222388461317377</v>
+        <v>0.8587963793244187</v>
       </c>
       <c r="E34" t="n">
-        <v>2.123602892833685e-10</v>
+        <v>7.396449704141993e-10</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9756020009175648</v>
+        <v>0.9313128840800919</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>8.277449046679843e-10</v>
+        <v>1.380670611439837e-09</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9464679297443677</v>
+        <v>0.8471845840428966</v>
       </c>
       <c r="E35" t="n">
-        <v>8.277449046679843e-10</v>
+        <v>1.380670611439837e-09</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9771496975764087</v>
+        <v>0.9112776866151142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.4431295200526e-09</v>
+        <v>2.021696252465481e-09</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9706970133569972</v>
+        <v>0.8355727887613746</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4431295200526e-09</v>
+        <v>2.021696252465481e-09</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9706970133569974</v>
+        <v>0.8868218542679894</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2.058514135437216e-09</v>
+        <v>2.662721893491119e-09</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9388108676622282</v>
+        <v>0.8239609934798526</v>
       </c>
       <c r="E37" t="n">
-        <v>2.058514135437216e-09</v>
+        <v>2.662721893491119e-09</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9560838380950746</v>
+        <v>0.8593260725370258</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>2.673898750821832e-09</v>
+        <v>3.303747534516763e-09</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9069247219674591</v>
+        <v>0.8123491981983306</v>
       </c>
       <c r="E38" t="n">
-        <v>2.673898750821832e-09</v>
+        <v>3.303747534516763e-09</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9342829363427267</v>
+        <v>0.8301710269205296</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>3.289283366206448e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8750385762726901</v>
+        <v>0.8007374029168086</v>
       </c>
       <c r="E39" t="n">
-        <v>3.289283366206448e-09</v>
+        <v>3.944773175542401e-09</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9065502913311259</v>
+        <v>0.8007374029168086</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>3.904667981591063e-09</v>
+        <v>4.585798816568045e-09</v>
       </c>
       <c r="D40" t="n">
-        <v>0.843152430577921</v>
+        <v>0.7764671772021323</v>
       </c>
       <c r="E40" t="n">
-        <v>3.904667981591063e-09</v>
+        <v>4.585798816568045e-09</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8741418862914443</v>
+        <v>0.7721690910087301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>4.520052596975673e-09</v>
+        <v>5.226824457593682e-09</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8112662848831523</v>
+        <v>0.7521969514874564</v>
       </c>
       <c r="E41" t="n">
-        <v>4.520052596975673e-09</v>
+        <v>5.226824457593682e-09</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8383137044548549</v>
+        <v>0.7446628016174026</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>5.135437212360288e-09</v>
+        <v>5.867850098619327e-09</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7793801391883832</v>
+        <v>0.7279267257727801</v>
       </c>
       <c r="E42" t="n">
-        <v>5.135437212360288e-09</v>
+        <v>5.867850098619327e-09</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8003217290525287</v>
+        <v>0.7181784501484944</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>5.750821827744904e-09</v>
+        <v>6.508875739644964e-09</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7474939934936142</v>
+        <v>0.7036565000581041</v>
       </c>
       <c r="E43" t="n">
-        <v>5.750821827744904e-09</v>
+        <v>6.508875739644964e-09</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7614219433156388</v>
+        <v>0.6926759520076745</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>6.36620644312952e-09</v>
+        <v>7.149901380670608e-09</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7156078477988452</v>
+        <v>0.6793862743434278</v>
       </c>
       <c r="E44" t="n">
-        <v>6.36620644312952e-09</v>
+        <v>7.149901380670608e-09</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7228703304753569</v>
+        <v>0.6681152226006112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>6.981591058514136e-09</v>
+        <v>7.790927021696246e-09</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6837217021040762</v>
+        <v>0.6551160486287518</v>
       </c>
       <c r="E45" t="n">
-        <v>6.981591058514136e-09</v>
+        <v>7.790927021696246e-09</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6859228737628557</v>
+        <v>0.6444561773329734</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>8.43195266272189e-09</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.6308458229140755</v>
       </c>
       <c r="E46" t="n">
-        <v>7.596975673898752e-09</v>
+        <v>8.43195266272189e-09</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6518355564093071</v>
+        <v>0.6216587316104294</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>8.212360289283367e-09</v>
+        <v>9.072978303747528e-09</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6327394451314969</v>
+        <v>0.6065755971993996</v>
       </c>
       <c r="E47" t="n">
-        <v>8.212360289283367e-09</v>
+        <v>9.072978303747528e-09</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6215806497310407</v>
+        <v>0.599682800838648</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>8.827744904667983e-09</v>
+        <v>9.714003944773172e-09</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6136433338536869</v>
+        <v>0.5823053714847233</v>
       </c>
       <c r="E48" t="n">
-        <v>8.827744904667983e-09</v>
+        <v>9.714003944773172e-09</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5949955773850139</v>
+        <v>0.5784883004232978</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>9.443129520052599e-09</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5945472225758767</v>
+        <v>0.5580351457700473</v>
       </c>
       <c r="E49" t="n">
-        <v>9.443129520052599e-09</v>
+        <v>1.035502958579881e-08</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5716340511133418</v>
+        <v>0.5580351457700473</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.005851413543721e-08</v>
+        <v>1.099605522682445e-08</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5754511112980665</v>
+        <v>0.5411211875919648</v>
       </c>
       <c r="E50" t="n">
-        <v>1.005851413543721e-08</v>
+        <v>1.099605522682445e-08</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5510497826581388</v>
+        <v>0.5382866888431541</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1.067389875082183e-08</v>
+        <v>1.163708086785009e-08</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5563550000202564</v>
+        <v>0.5242072294138824</v>
       </c>
       <c r="E51" t="n">
-        <v>1.067389875082183e-08</v>
+        <v>1.163708086785009e-08</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5327964837615201</v>
+        <v>0.5192200278412328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.128928336620645e-08</v>
+        <v>1.227810650887574e-08</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5372588887424462</v>
+        <v>0.5072932712358</v>
       </c>
       <c r="E52" t="n">
-        <v>1.128928336620645e-08</v>
+        <v>1.227810650887574e-08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5164278661656001</v>
+        <v>0.5008156975214859</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1.190466798159106e-08</v>
+        <v>1.291913214990137e-08</v>
       </c>
       <c r="D53" t="n">
-        <v>0.518162777464636</v>
+        <v>0.4903793130577176</v>
       </c>
       <c r="E53" t="n">
-        <v>1.190466798159106e-08</v>
+        <v>1.291913214990137e-08</v>
       </c>
       <c r="F53" t="n">
-        <v>0.501497641612494</v>
+        <v>0.4830542326411174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.252005259697568e-08</v>
+        <v>1.356015779092701e-08</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4990666661868259</v>
+        <v>0.4734653548796353</v>
       </c>
       <c r="E54" t="n">
-        <v>1.252005259697568e-08</v>
+        <v>1.356015779092701e-08</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4875595218443164</v>
+        <v>0.46591616795733</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1.313543721236029e-08</v>
+        <v>1.420118343195266e-08</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4799705549090157</v>
+        <v>0.4565513967015526</v>
       </c>
       <c r="E55" t="n">
-        <v>1.313543721236029e-08</v>
+        <v>1.420118343195266e-08</v>
       </c>
       <c r="F55" t="n">
-        <v>0.474167218603182</v>
+        <v>0.4493820382273268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.48422090729783e-08</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.4396374385234703</v>
       </c>
       <c r="E56" t="n">
-        <v>1.375082182774491e-08</v>
+        <v>1.48422090729783e-08</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4608744436312056</v>
+        <v>0.4334323782083114</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>1.436620644312953e-08</v>
+        <v>1.548323471400394e-08</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4473727106033835</v>
+        <v>0.422723480345388</v>
       </c>
       <c r="E57" t="n">
-        <v>1.436620644312953e-08</v>
+        <v>1.548323471400394e-08</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4473255284518747</v>
+        <v>0.4180477226574869</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.498159105851414e-08</v>
+        <v>1.612426035502959e-08</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4338709775755614</v>
+        <v>0.4058095221673053</v>
       </c>
       <c r="E58" t="n">
-        <v>1.498159105851414e-08</v>
+        <v>1.612426035502959e-08</v>
       </c>
       <c r="F58" t="n">
-        <v>0.433527283714167</v>
+        <v>0.4032086063320561</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1.559697567389876e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4203692445477393</v>
+        <v>0.388895563989223</v>
       </c>
       <c r="E59" t="n">
-        <v>1.559697567389876e-08</v>
+        <v>1.676528599605523e-08</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4195771398484329</v>
+        <v>0.388895563989223</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.621236028928337e-08</v>
+        <v>1.740631163708086e-08</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4068675115199172</v>
+        <v>0.3771082001380114</v>
       </c>
       <c r="E60" t="n">
-        <v>1.621236028928337e-08</v>
+        <v>1.740631163708086e-08</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4055725272850227</v>
+        <v>0.375089735455479</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1.682774490466799e-08</v>
+        <v>1.80473372781065e-08</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3933657784920951</v>
+        <v>0.3653208362867997</v>
       </c>
       <c r="E61" t="n">
-        <v>1.682774490466799e-08</v>
+        <v>1.80473372781065e-08</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3916108764542869</v>
+        <v>0.3617746808344706</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.74431295200526e-08</v>
+        <v>1.868836291913215e-08</v>
       </c>
       <c r="D62" t="n">
-        <v>0.379864045464273</v>
+        <v>0.3535334724355879</v>
       </c>
       <c r="E62" t="n">
-        <v>1.74431295200526e-08</v>
+        <v>1.868836291913215e-08</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3777896177865757</v>
+        <v>0.3489345652991328</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1.805851413543722e-08</v>
+        <v>1.932938856015779e-08</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3663623124364509</v>
+        <v>0.3417461085843763</v>
       </c>
       <c r="E63" t="n">
-        <v>1.805851413543722e-08</v>
+        <v>1.932938856015779e-08</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3642061817122395</v>
+        <v>0.3365535540224012</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.867389875082184e-08</v>
+        <v>1.997041420118343e-08</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3528605794086288</v>
+        <v>0.3299587447331647</v>
       </c>
       <c r="E64" t="n">
-        <v>1.867389875082184e-08</v>
+        <v>1.997041420118343e-08</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3509579986616286</v>
+        <v>0.3246158121772108</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>1.928928336620645e-08</v>
+        <v>2.061143984220906e-08</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3393588463808067</v>
+        <v>0.3181713808819531</v>
       </c>
       <c r="E65" t="n">
-        <v>1.928928336620645e-08</v>
+        <v>2.061143984220906e-08</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3381424990650935</v>
+        <v>0.3131055049364967</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>2.125246548323472e-08</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.3063840170307412</v>
       </c>
       <c r="E66" t="n">
-        <v>1.990466798159107e-08</v>
+        <v>2.125246548323472e-08</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3258571133529846</v>
+        <v>0.3020067974731938</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2.052005259697568e-08</v>
+        <v>2.189349112426035e-08</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3163108349456937</v>
+        <v>0.2945966531795296</v>
       </c>
       <c r="E67" t="n">
-        <v>2.052005259697568e-08</v>
+        <v>2.189349112426035e-08</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3141760720703797</v>
+        <v>0.2913038549602379</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2.11354372123603e-08</v>
+        <v>2.253451676528599e-08</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3067645565384028</v>
+        <v>0.2828092893283179</v>
       </c>
       <c r="E68" t="n">
-        <v>2.11354372123603e-08</v>
+        <v>2.253451676528599e-08</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3030808062212677</v>
+        <v>0.2809808425705635</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>2.175082182774492e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="D69" t="n">
-        <v>0.297218278131112</v>
+        <v>0.2710219254771064</v>
       </c>
       <c r="E69" t="n">
-        <v>2.175082182774492e-08</v>
+        <v>2.317554240631163e-08</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2925295469243648</v>
+        <v>0.2710219254771064</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>2.236620644312953e-08</v>
+        <v>2.381656804733728e-08</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2876719997238211</v>
+        <v>0.2628072932131518</v>
       </c>
       <c r="E70" t="n">
-        <v>2.236620644312953e-08</v>
+        <v>2.381656804733728e-08</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2824805252983875</v>
+        <v>0.2614121701217584</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>2.298159105851415e-08</v>
+        <v>2.445759368836292e-08</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2781257213165302</v>
+        <v>0.2545926609491974</v>
       </c>
       <c r="E71" t="n">
-        <v>2.298159105851415e-08</v>
+        <v>2.445759368836292e-08</v>
       </c>
       <c r="F71" t="n">
-        <v>0.272891972462052</v>
+        <v>0.2521402480222421</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>2.359697567389876e-08</v>
+        <v>2.509861932938855e-08</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2685794429092394</v>
+        <v>0.246378028685243</v>
       </c>
       <c r="E72" t="n">
-        <v>2.359697567389876e-08</v>
+        <v>2.509861932938855e-08</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2637221195340749</v>
+        <v>0.2431957319652366</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>2.421236028928337e-08</v>
+        <v>2.573964497041419e-08</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2590331645019487</v>
+        <v>0.2381633964212886</v>
       </c>
       <c r="E73" t="n">
-        <v>2.421236028928337e-08</v>
+        <v>2.573964497041419e-08</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2549291976331725</v>
+        <v>0.2345681947374211</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>2.482774490466798e-08</v>
+        <v>2.638067061143984e-08</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2494868860946579</v>
+        <v>0.229948764157334</v>
       </c>
       <c r="E74" t="n">
-        <v>2.482774490466798e-08</v>
+        <v>2.638067061143984e-08</v>
       </c>
       <c r="F74" t="n">
-        <v>0.246471437878061</v>
+        <v>0.2262472091254749</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>2.54431295200526e-08</v>
+        <v>2.702169625246548e-08</v>
       </c>
       <c r="D75" t="n">
-        <v>0.239940607687367</v>
+        <v>0.2217341318933796</v>
       </c>
       <c r="E75" t="n">
-        <v>2.54431295200526e-08</v>
+        <v>2.702169625246548e-08</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2383070713874567</v>
+        <v>0.2182223479160776</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.766272189349112e-08</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.2135194996294252</v>
       </c>
       <c r="E76" t="n">
-        <v>2.605851413543721e-08</v>
+        <v>2.766272189349112e-08</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2303943292800761</v>
+        <v>0.2104831838959083</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>2.667389875082183e-08</v>
+        <v>2.830374753451676e-08</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2236447193417283</v>
+        <v>0.2053048673654708</v>
       </c>
       <c r="E77" t="n">
-        <v>2.667389875082183e-08</v>
+        <v>2.830374753451676e-08</v>
       </c>
       <c r="F77" t="n">
-        <v>0.222698423809131</v>
+        <v>0.2030192898516464</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>2.728928336620644e-08</v>
+        <v>2.894477317554241e-08</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2168951094033804</v>
+        <v>0.1970902351015162</v>
       </c>
       <c r="E78" t="n">
-        <v>2.728928336620644e-08</v>
+        <v>2.894477317554241e-08</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2152124917658149</v>
+        <v>0.1958202385699711</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>2.790466798159106e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2101454994650326</v>
+        <v>0.1888756028375619</v>
       </c>
       <c r="E79" t="n">
-        <v>2.790466798159106e-08</v>
+        <v>2.958579881656804e-08</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2079366510758167</v>
+        <v>0.1888756028375619</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>2.852005259697568e-08</v>
+        <v>3.022682445759368e-08</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2033958895266847</v>
+        <v>0.1831508127925796</v>
       </c>
       <c r="E80" t="n">
-        <v>2.852005259697568e-08</v>
+        <v>3.022682445759368e-08</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2008710196648252</v>
+        <v>0.1821754550296932</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>2.913543721236029e-08</v>
+        <v>3.086785009861932e-08</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1966462795883368</v>
+        <v>0.1774260227475973</v>
       </c>
       <c r="E81" t="n">
-        <v>2.913543721236029e-08</v>
+        <v>3.086785009861932e-08</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1940157154585294</v>
+        <v>0.1757118658760202</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>2.975082182774491e-08</v>
+        <v>3.150887573964497e-08</v>
       </c>
       <c r="D82" t="n">
-        <v>0.189896669649989</v>
+        <v>0.1717012327026148</v>
       </c>
       <c r="E82" t="n">
-        <v>2.975082182774491e-08</v>
+        <v>3.150887573964497e-08</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1873708563826182</v>
+        <v>0.1694774056947934</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>3.036620644312952e-08</v>
+        <v>3.214990138067061e-08</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1831470597116411</v>
+        <v>0.1659764426576326</v>
       </c>
       <c r="E83" t="n">
-        <v>3.036620644312952e-08</v>
+        <v>3.214990138067061e-08</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1809365603627805</v>
+        <v>0.1634646448042634</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>3.098159105851414e-08</v>
+        <v>3.279092702169624e-08</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1763974497732932</v>
+        <v>0.1602516526126503</v>
       </c>
       <c r="E84" t="n">
-        <v>3.098159105851414e-08</v>
+        <v>3.279092702169624e-08</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1747129453247052</v>
+        <v>0.1576661535226805</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>3.159697567389875e-08</v>
+        <v>3.343195266272188e-08</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1696478398349454</v>
+        <v>0.154526862567668</v>
       </c>
       <c r="E85" t="n">
-        <v>3.159697567389875e-08</v>
+        <v>3.343195266272188e-08</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1687001291940813</v>
+        <v>0.1520745021682952</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>3.407297830374753e-08</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1488020725226855</v>
       </c>
       <c r="E86" t="n">
-        <v>3.221236028928337e-08</v>
+        <v>3.407297830374753e-08</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1628982298965975</v>
+        <v>0.1466822610593578</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>3.282774490466799e-08</v>
+        <v>3.471400394477317e-08</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1581259791433563</v>
+        <v>0.1430772824777032</v>
       </c>
       <c r="E87" t="n">
-        <v>3.282774490466799e-08</v>
+        <v>3.471400394477317e-08</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1573060354739111</v>
+        <v>0.141482000514119</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>3.34431295200526e-08</v>
+        <v>3.535502958579881e-08</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1533537283901151</v>
+        <v>0.137352492432721</v>
       </c>
       <c r="E88" t="n">
-        <v>3.34431295200526e-08</v>
+        <v>3.535502958579881e-08</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1519170144315516</v>
+        <v>0.1364662908508291</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>3.405851413543722e-08</v>
+        <v>3.599605522682446e-08</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1485814776368738</v>
+        <v>0.1316277023877386</v>
       </c>
       <c r="E89" t="n">
-        <v>3.405851413543722e-08</v>
+        <v>3.599605522682446e-08</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1467233053910169</v>
+        <v>0.1316277023877385</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>3.467389875082183e-08</v>
+        <v>3.66370808678501e-08</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1438092268836326</v>
+        <v>0.1276380872709504</v>
       </c>
       <c r="E90" t="n">
-        <v>3.467389875082183e-08</v>
+        <v>3.66370808678501e-08</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1417170469738047</v>
+        <v>0.1269591880405349</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>3.528928336620645e-08</v>
+        <v>3.727810650887573e-08</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1390369761303914</v>
+        <v>0.1236484721541622</v>
       </c>
       <c r="E91" t="n">
-        <v>3.528928336620645e-08</v>
+        <v>3.727810650887573e-08</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1368903778014131</v>
+        <v>0.1224552311146533</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>3.590466798159107e-08</v>
+        <v>3.791913214990137e-08</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1342647253771502</v>
+        <v>0.119658857037374</v>
       </c>
       <c r="E92" t="n">
-        <v>3.590466798159107e-08</v>
+        <v>3.791913214990137e-08</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1322354364953397</v>
+        <v>0.1181106975129659</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>3.652005259697568e-08</v>
+        <v>3.856015779092702e-08</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1294924746239089</v>
+        <v>0.1156692419205858</v>
       </c>
       <c r="E93" t="n">
-        <v>3.652005259697568e-08</v>
+        <v>3.856015779092702e-08</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1277443616770824</v>
+        <v>0.1139204531383448</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>3.71354372123603e-08</v>
+        <v>3.920118343195266e-08</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1247202238706677</v>
+        <v>0.1116796268037976</v>
       </c>
       <c r="E94" t="n">
-        <v>3.71354372123603e-08</v>
+        <v>3.920118343195266e-08</v>
       </c>
       <c r="F94" t="n">
-        <v>0.123409291968139</v>
+        <v>0.1098793638936624</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3.775082182774491e-08</v>
+        <v>3.98422090729783e-08</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1199479731174265</v>
+        <v>0.1076900116870094</v>
       </c>
       <c r="E95" t="n">
-        <v>3.775082182774491e-08</v>
+        <v>3.98422090729783e-08</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1192223659900074</v>
+        <v>0.1059822956817909</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>4.048323471400394e-08</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.1037003965702212</v>
       </c>
       <c r="E96" t="n">
-        <v>3.836620644312953e-08</v>
+        <v>4.048323471400394e-08</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1151757223641853</v>
+        <v>0.1022241144056023</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>3.898159105851414e-08</v>
+        <v>4.112426035502959e-08</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1118015455658463</v>
+        <v>0.09971078145343296</v>
       </c>
       <c r="E97" t="n">
-        <v>3.898159105851414e-08</v>
+        <v>4.112426035502959e-08</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1112622383543389</v>
+        <v>0.09859968596796891</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>3.959697567389876e-08</v>
+        <v>4.176528599605522e-08</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1084273687675074</v>
+        <v>0.09572116633664476</v>
       </c>
       <c r="E98" t="n">
-        <v>3.959697567389876e-08</v>
+        <v>4.176528599605522e-08</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1074777457928074</v>
+        <v>0.09510387627176296</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>4.021236028928338e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1050531919691684</v>
+        <v>0.09173155121985659</v>
       </c>
       <c r="E99" t="n">
-        <v>4.021236028928338e-08</v>
+        <v>4.240631163708086e-08</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1038188151540984</v>
+        <v>0.09173155121985659</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>4.082774490466799e-08</v>
+        <v>4.30473372781065e-08</v>
       </c>
       <c r="D100" t="n">
-        <v>0.1016790151708295</v>
+        <v>0.0889511822185417</v>
       </c>
       <c r="E100" t="n">
-        <v>4.082774490466799e-08</v>
+        <v>4.30473372781065e-08</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1002820169127193</v>
+        <v>0.08847783412155956</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>4.144312952005261e-08</v>
+        <v>4.368836291913215e-08</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0983048383724905</v>
+        <v>0.08617081321722676</v>
       </c>
       <c r="E101" t="n">
-        <v>4.144312952005261e-08</v>
+        <v>4.368836291913215e-08</v>
       </c>
       <c r="F101" t="n">
-        <v>0.09686392154317779</v>
+        <v>0.08533887791193177</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>4.205851413543722e-08</v>
+        <v>4.432938856015779e-08</v>
       </c>
       <c r="D102" t="n">
-        <v>0.09493066157415156</v>
+        <v>0.08339044421591188</v>
       </c>
       <c r="E102" t="n">
-        <v>4.205851413543722e-08</v>
+        <v>4.432938856015779e-08</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09356109951998122</v>
+        <v>0.08231109293247088</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>4.267389875082184e-08</v>
+        <v>4.497041420118343e-08</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0915564847758126</v>
+        <v>0.08061007521459698</v>
       </c>
       <c r="E103" t="n">
-        <v>4.267389875082184e-08</v>
+        <v>4.497041420118343e-08</v>
       </c>
       <c r="F103" t="n">
-        <v>0.09037012131763722</v>
+        <v>0.07939088952467434</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>4.328928336620645e-08</v>
+        <v>4.561143984220906e-08</v>
       </c>
       <c r="D104" t="n">
-        <v>0.08818230797747365</v>
+        <v>0.07782970621328211</v>
       </c>
       <c r="E104" t="n">
-        <v>4.328928336620645e-08</v>
+        <v>4.561143984220906e-08</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0872875574106533</v>
+        <v>0.07657467803003967</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>4.390466798159107e-08</v>
+        <v>4.625246548323471e-08</v>
       </c>
       <c r="D105" t="n">
-        <v>0.08480813117913469</v>
+        <v>0.07504933721196716</v>
       </c>
       <c r="E105" t="n">
-        <v>4.390466798159107e-08</v>
+        <v>4.625246548323471e-08</v>
       </c>
       <c r="F105" t="n">
-        <v>0.08430997827353696</v>
+        <v>0.07385886879006434</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>4.452005259697569e-08</v>
+        <v>4.689349112426035e-08</v>
       </c>
       <c r="D106" t="n">
-        <v>0.08143395438079574</v>
+        <v>0.07226896821065228</v>
       </c>
       <c r="E106" t="n">
-        <v>4.452005259697569e-08</v>
+        <v>4.689349112426035e-08</v>
       </c>
       <c r="F106" t="n">
-        <v>0.08143395438079574</v>
+        <v>0.07123987214624598</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>4.51354372123603e-08</v>
+        <v>4.753451676528599e-08</v>
       </c>
       <c r="D107" t="n">
-        <v>0.07904827314669119</v>
+        <v>0.06948859920933739</v>
       </c>
       <c r="E107" t="n">
-        <v>4.51354372123603e-08</v>
+        <v>4.753451676528599e-08</v>
       </c>
       <c r="F107" t="n">
-        <v>0.07865612859069125</v>
+        <v>0.06871409844008207</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>4.575082182774492e-08</v>
+        <v>4.817554240631163e-08</v>
       </c>
       <c r="D108" t="n">
-        <v>0.07666259191258662</v>
+        <v>0.06670823020802251</v>
       </c>
       <c r="E108" t="n">
-        <v>4.575082182774492e-08</v>
+        <v>4.817554240631163e-08</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0759734332965014</v>
+        <v>0.0662779580130701</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>4.636620644312953e-08</v>
+        <v>4.881656804733728e-08</v>
       </c>
       <c r="D109" t="n">
-        <v>0.07427691067848205</v>
+        <v>0.06392786120670758</v>
       </c>
       <c r="E109" t="n">
-        <v>4.636620644312953e-08</v>
+        <v>4.881656804733728e-08</v>
       </c>
       <c r="F109" t="n">
-        <v>0.07338287327525818</v>
+        <v>0.06392786120670758</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>4.698159105851415e-08</v>
+        <v>4.945759368836292e-08</v>
       </c>
       <c r="D110" t="n">
-        <v>0.07189122944437748</v>
+        <v>0.06199021771048581</v>
       </c>
       <c r="E110" t="n">
-        <v>4.698159105851415e-08</v>
+        <v>4.945759368836292e-08</v>
       </c>
       <c r="F110" t="n">
-        <v>0.07088145330399363</v>
+        <v>0.06166040022132834</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>4.759697567389877e-08</v>
+        <v>5.009861932938855e-08</v>
       </c>
       <c r="D111" t="n">
-        <v>0.06950554821027291</v>
+        <v>0.06005257421426403</v>
       </c>
       <c r="E111" t="n">
-        <v>4.759697567389877e-08</v>
+        <v>5.009861932938855e-08</v>
       </c>
       <c r="F111" t="n">
-        <v>0.06846617815973972</v>
+        <v>0.05947289469261102</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>4.821236028928338e-08</v>
+        <v>5.073964497041419e-08</v>
       </c>
       <c r="D112" t="n">
-        <v>0.06711986697616834</v>
+        <v>0.05811493071804225</v>
       </c>
       <c r="E112" t="n">
-        <v>4.821236028928338e-08</v>
+        <v>5.073964497041419e-08</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06613405261952848</v>
+        <v>0.0573628461150705</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>4.8827744904668e-08</v>
+        <v>5.138067061143984e-08</v>
       </c>
       <c r="D113" t="n">
-        <v>0.06473418574206379</v>
+        <v>0.05617728722182043</v>
       </c>
       <c r="E113" t="n">
-        <v>4.8827744904668e-08</v>
+        <v>5.138067061143984e-08</v>
       </c>
       <c r="F113" t="n">
-        <v>0.06388208146039188</v>
+        <v>0.05532775598322167</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>4.944312952005261e-08</v>
+        <v>5.202169625246548e-08</v>
       </c>
       <c r="D114" t="n">
-        <v>0.06234850450795922</v>
+        <v>0.05423964372559865</v>
       </c>
       <c r="E114" t="n">
-        <v>4.944312952005261e-08</v>
+        <v>5.202169625246548e-08</v>
       </c>
       <c r="F114" t="n">
-        <v>0.06170726945936196</v>
+        <v>0.0533651257915795</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>5.005851413543723e-08</v>
+        <v>5.266272189349112e-08</v>
       </c>
       <c r="D115" t="n">
-        <v>0.05996282327385465</v>
+        <v>0.05230200022937687</v>
       </c>
       <c r="E115" t="n">
-        <v>5.005851413543723e-08</v>
+        <v>5.266272189349112e-08</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0596066213934707</v>
+        <v>0.05147245703465887</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>5.330374753451675e-08</v>
       </c>
       <c r="D116" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.05036435673315509</v>
       </c>
       <c r="E116" t="n">
-        <v>5.067389875082183e-08</v>
+        <v>5.330374753451675e-08</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05757714203975013</v>
+        <v>0.04964725120697468</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>5.128928336620645e-08</v>
+        <v>5.39447731755424e-08</v>
       </c>
       <c r="D117" t="n">
-        <v>0.05589036766753571</v>
+        <v>0.04842671323693327</v>
       </c>
       <c r="E117" t="n">
-        <v>5.128928336620645e-08</v>
+        <v>5.39447731755424e-08</v>
       </c>
       <c r="F117" t="n">
-        <v>0.05561600789493083</v>
+        <v>0.04788700980304178</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>5.190466798159106e-08</v>
+        <v>5.458579881656804e-08</v>
       </c>
       <c r="D118" t="n">
-        <v>0.05420359329532128</v>
+        <v>0.04648906974071149</v>
       </c>
       <c r="E118" t="n">
-        <v>5.190466798159106e-08</v>
+        <v>5.458579881656804e-08</v>
       </c>
       <c r="F118" t="n">
-        <v>0.05372108233453801</v>
+        <v>0.04618923431737517</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>5.252005259697568e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="D119" t="n">
-        <v>0.05251681892310686</v>
+        <v>0.04455142624448971</v>
       </c>
       <c r="E119" t="n">
-        <v>5.252005259697568e-08</v>
+        <v>5.522682445759368e-08</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05189040045379547</v>
+        <v>0.04455142624448971</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>5.313543721236029e-08</v>
+        <v>5.586785009861933e-08</v>
       </c>
       <c r="D120" t="n">
-        <v>0.05083004455089243</v>
+        <v>0.04320107946797368</v>
       </c>
       <c r="E120" t="n">
-        <v>5.313543721236029e-08</v>
+        <v>5.586785009861933e-08</v>
       </c>
       <c r="F120" t="n">
-        <v>0.05012199734792704</v>
+        <v>0.04297121315536773</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>5.375082182774491e-08</v>
+        <v>5.650887573964497e-08</v>
       </c>
       <c r="D121" t="n">
-        <v>0.04914327017867801</v>
+        <v>0.04185073269145769</v>
       </c>
       <c r="E121" t="n">
-        <v>5.375082182774491e-08</v>
+        <v>5.650887573964497e-08</v>
       </c>
       <c r="F121" t="n">
-        <v>0.04841390811215651</v>
+        <v>0.04144672692686144</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>5.436620644312953e-08</v>
+        <v>5.714990138067061e-08</v>
       </c>
       <c r="D122" t="n">
-        <v>0.04745649580646359</v>
+        <v>0.04050038591494169</v>
       </c>
       <c r="E122" t="n">
-        <v>5.436620644312953e-08</v>
+        <v>5.714990138067061e-08</v>
       </c>
       <c r="F122" t="n">
-        <v>0.04676416784170771</v>
+        <v>0.03997622551229046</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>5.498159105851414e-08</v>
+        <v>5.779092702169624e-08</v>
       </c>
       <c r="D123" t="n">
-        <v>0.04576972143424916</v>
+        <v>0.03915003913842569</v>
       </c>
       <c r="E123" t="n">
-        <v>5.498159105851414e-08</v>
+        <v>5.779092702169624e-08</v>
       </c>
       <c r="F123" t="n">
-        <v>0.04517081163180443</v>
+        <v>0.03855796686497438</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>5.559697567389876e-08</v>
+        <v>5.843195266272189e-08</v>
       </c>
       <c r="D124" t="n">
-        <v>0.04408294706203474</v>
+        <v>0.03779969236190966</v>
       </c>
       <c r="E124" t="n">
-        <v>5.559697567389876e-08</v>
+        <v>5.843195266272189e-08</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0436318745776705</v>
+        <v>0.03719020893823282</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>5.621236028928337e-08</v>
+        <v>5.907297830374753e-08</v>
       </c>
       <c r="D125" t="n">
-        <v>0.04239617268982032</v>
+        <v>0.03644934558539367</v>
       </c>
       <c r="E125" t="n">
-        <v>5.621236028928337e-08</v>
+        <v>5.907297830374753e-08</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04214539177452972</v>
+        <v>0.03587120968538542</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>5.971400394477318e-08</v>
       </c>
       <c r="D126" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.03509899880887766</v>
       </c>
       <c r="E126" t="n">
-        <v>5.682774490466799e-08</v>
+        <v>5.971400394477318e-08</v>
       </c>
       <c r="F126" t="n">
-        <v>0.04070939831760589</v>
+        <v>0.03459922705975178</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>5.744312952005261e-08</v>
+        <v>6.035502958579881e-08</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0395167797304763</v>
+        <v>0.03374865203236166</v>
       </c>
       <c r="E127" t="n">
-        <v>5.744312952005261e-08</v>
+        <v>6.035502958579881e-08</v>
       </c>
       <c r="F127" t="n">
-        <v>0.03932201841582961</v>
+        <v>0.03337251901465153</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>5.805851413543722e-08</v>
+        <v>6.099605522682445e-08</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0383241611433467</v>
+        <v>0.03239830525584567</v>
       </c>
       <c r="E128" t="n">
-        <v>5.805851413543722e-08</v>
+        <v>6.099605522682445e-08</v>
       </c>
       <c r="F128" t="n">
-        <v>0.03798173273295855</v>
+        <v>0.03218934350340429</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>5.867389875082184e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="D129" t="n">
-        <v>0.03713154255621712</v>
+        <v>0.03104795847932967</v>
       </c>
       <c r="E129" t="n">
-        <v>5.867389875082184e-08</v>
+        <v>6.163708086785009e-08</v>
       </c>
       <c r="F129" t="n">
-        <v>0.03668711104645713</v>
+        <v>0.03104795847932967</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>5.928928336620645e-08</v>
+        <v>6.227810650887573e-08</v>
       </c>
       <c r="D130" t="n">
-        <v>0.03593892396908752</v>
+        <v>0.03010689970334602</v>
       </c>
       <c r="E130" t="n">
-        <v>5.928928336620645e-08</v>
+        <v>6.227810650887573e-08</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0354367231337898</v>
+        <v>0.02994670993170339</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>5.990466798159107e-08</v>
+        <v>6.291913214990136e-08</v>
       </c>
       <c r="D131" t="n">
-        <v>0.03474630538195793</v>
+        <v>0.02916584092736237</v>
       </c>
       <c r="E131" t="n">
-        <v>5.990466798159107e-08</v>
+        <v>6.291913214990136e-08</v>
       </c>
       <c r="F131" t="n">
-        <v>0.03422913877242099</v>
+        <v>0.02888429599362555</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>6.052005259697568e-08</v>
+        <v>6.356015779092703e-08</v>
       </c>
       <c r="D132" t="n">
-        <v>0.03355368679482833</v>
+        <v>0.02822478215137867</v>
       </c>
       <c r="E132" t="n">
-        <v>6.052005259697568e-08</v>
+        <v>6.356015779092703e-08</v>
       </c>
       <c r="F132" t="n">
-        <v>0.03306292773981512</v>
+        <v>0.02785950283415236</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>6.11354372123603e-08</v>
+        <v>6.420118343195267e-08</v>
       </c>
       <c r="D133" t="n">
-        <v>0.03236106820769874</v>
+        <v>0.02728372337539502</v>
       </c>
       <c r="E133" t="n">
-        <v>6.11354372123603e-08</v>
+        <v>6.420118343195267e-08</v>
       </c>
       <c r="F133" t="n">
-        <v>0.03193665981343666</v>
+        <v>0.02687111662234009</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>6.175082182774492e-08</v>
+        <v>6.48422090729783e-08</v>
       </c>
       <c r="D134" t="n">
-        <v>0.03116844962056915</v>
+        <v>0.02634266459941137</v>
       </c>
       <c r="E134" t="n">
-        <v>6.175082182774492e-08</v>
+        <v>6.48422090729783e-08</v>
       </c>
       <c r="F134" t="n">
-        <v>0.03084890477075001</v>
+        <v>0.02591792352724492</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>6.236620644312953e-08</v>
+        <v>6.548323471400394e-08</v>
       </c>
       <c r="D135" t="n">
-        <v>0.02997583103343956</v>
+        <v>0.02540160582342772</v>
       </c>
       <c r="E135" t="n">
-        <v>6.236620644312953e-08</v>
+        <v>6.548323471400394e-08</v>
       </c>
       <c r="F135" t="n">
-        <v>0.02979823238921964</v>
+        <v>0.02499870971792307</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.612426035502958e-08</v>
       </c>
       <c r="D136" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.02446054704744407</v>
       </c>
       <c r="E136" t="n">
-        <v>6.298159105851415e-08</v>
+        <v>6.612426035502958e-08</v>
       </c>
       <c r="F136" t="n">
-        <v>0.02878321244630996</v>
+        <v>0.02411226136343074</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>6.359697567389876e-08</v>
+        <v>6.676528599605522e-08</v>
       </c>
       <c r="D137" t="n">
-        <v>0.02793998224445451</v>
+        <v>0.02351948827146042</v>
       </c>
       <c r="E137" t="n">
-        <v>6.359697567389876e-08</v>
+        <v>6.676528599605522e-08</v>
       </c>
       <c r="F137" t="n">
-        <v>0.02780248638172966</v>
+        <v>0.02325736463282416</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>6.421236028928338e-08</v>
+        <v>6.740631163708085e-08</v>
       </c>
       <c r="D138" t="n">
-        <v>0.02709675204259905</v>
+        <v>0.02257842949547677</v>
       </c>
       <c r="E138" t="n">
-        <v>6.421236028928338e-08</v>
+        <v>6.740631163708085e-08</v>
       </c>
       <c r="F138" t="n">
-        <v>0.02685498228416429</v>
+        <v>0.02243280569515956</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>6.482774490466799e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="D139" t="n">
-        <v>0.02625352184074359</v>
+        <v>0.02163737071949312</v>
       </c>
       <c r="E139" t="n">
-        <v>6.482774490466799e-08</v>
+        <v>6.804733727810649e-08</v>
       </c>
       <c r="F139" t="n">
-        <v>0.02593969990454367</v>
+        <v>0.02163737071949312</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>6.544312952005261e-08</v>
+        <v>6.868836291913216e-08</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02541029163888813</v>
+        <v>0.02098154538983907</v>
       </c>
       <c r="E140" t="n">
-        <v>6.544312952005261e-08</v>
+        <v>6.868836291913216e-08</v>
       </c>
       <c r="F140" t="n">
-        <v>0.02505563899379758</v>
+        <v>0.0208699071962389</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>6.605851413543723e-08</v>
+        <v>6.932938856015779e-08</v>
       </c>
       <c r="D141" t="n">
-        <v>0.02456706143703268</v>
+        <v>0.02032572006018505</v>
       </c>
       <c r="E141" t="n">
-        <v>6.605851413543723e-08</v>
+        <v>6.932938856015779e-08</v>
       </c>
       <c r="F141" t="n">
-        <v>0.02420179930285585</v>
+        <v>0.02012950790124247</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>6.667389875082184e-08</v>
+        <v>6.997041420118343e-08</v>
       </c>
       <c r="D142" t="n">
-        <v>0.02372383123517722</v>
+        <v>0.01966989473053103</v>
       </c>
       <c r="E142" t="n">
-        <v>6.667389875082184e-08</v>
+        <v>6.997041420118343e-08</v>
       </c>
       <c r="F142" t="n">
-        <v>0.02337718058264825</v>
+        <v>0.01941532693170714</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>6.728928336620646e-08</v>
+        <v>7.061143984220907e-08</v>
       </c>
       <c r="D143" t="n">
-        <v>0.02288060103332176</v>
+        <v>0.01901406940087701</v>
       </c>
       <c r="E143" t="n">
-        <v>6.728928336620646e-08</v>
+        <v>7.061143984220907e-08</v>
       </c>
       <c r="F143" t="n">
-        <v>0.02258078258410461</v>
+        <v>0.01872651838483628</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>6.790466798159107e-08</v>
+        <v>7.125246548323471e-08</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0220373708314663</v>
+        <v>0.018358244071223</v>
       </c>
       <c r="E144" t="n">
-        <v>6.790466798159107e-08</v>
+        <v>7.125246548323471e-08</v>
       </c>
       <c r="F144" t="n">
-        <v>0.02181160505815471</v>
+        <v>0.01806223635783324</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>6.852005259697569e-08</v>
+        <v>7.189349112426034e-08</v>
       </c>
       <c r="D145" t="n">
-        <v>0.02119414062961084</v>
+        <v>0.01770241874156897</v>
       </c>
       <c r="E145" t="n">
-        <v>6.852005259697569e-08</v>
+        <v>7.189349112426034e-08</v>
       </c>
       <c r="F145" t="n">
-        <v>0.02106864775572838</v>
+        <v>0.01742163494790138</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>7.253451676528598e-08</v>
       </c>
       <c r="D146" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.01704659341191496</v>
       </c>
       <c r="E146" t="n">
-        <v>6.913543721236031e-08</v>
+        <v>7.253451676528598e-08</v>
       </c>
       <c r="F146" t="n">
-        <v>0.02035091042775538</v>
+        <v>0.01680386825224406</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>6.975082182774492e-08</v>
+        <v>7.317554240631162e-08</v>
       </c>
       <c r="D147" t="n">
-        <v>0.01975471212848811</v>
+        <v>0.01639076808226093</v>
       </c>
       <c r="E147" t="n">
-        <v>6.975082182774492e-08</v>
+        <v>7.317554240631162e-08</v>
       </c>
       <c r="F147" t="n">
-        <v>0.01965744117165312</v>
+        <v>0.01620809036806463</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>7.036620644312954e-08</v>
+        <v>7.381656804733726e-08</v>
       </c>
       <c r="D148" t="n">
-        <v>0.01915851382922084</v>
+        <v>0.01573494275260692</v>
       </c>
       <c r="E148" t="n">
-        <v>7.036620644312954e-08</v>
+        <v>7.381656804733726e-08</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0189874814707892</v>
+        <v>0.01563345539256646</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>7.098159105851415e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="D149" t="n">
-        <v>0.01856231552995357</v>
+        <v>0.0150791174229529</v>
       </c>
       <c r="E149" t="n">
-        <v>7.098159105851415e-08</v>
+        <v>7.445759368836289e-08</v>
       </c>
       <c r="F149" t="n">
-        <v>0.01834032115501884</v>
+        <v>0.0150791174229529</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>7.159697567389877e-08</v>
+        <v>7.509861932938856e-08</v>
       </c>
       <c r="D150" t="n">
-        <v>0.0179661172306863</v>
+        <v>0.01462207172719787</v>
       </c>
       <c r="E150" t="n">
-        <v>7.159697567389877e-08</v>
+        <v>7.509861932938856e-08</v>
       </c>
       <c r="F150" t="n">
-        <v>0.01771525005419724</v>
+        <v>0.01454427324245747</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>7.221236028928338e-08</v>
+        <v>7.57396449704142e-08</v>
       </c>
       <c r="D151" t="n">
-        <v>0.01736991893141903</v>
+        <v>0.01416502603144286</v>
       </c>
       <c r="E151" t="n">
-        <v>7.221236028928338e-08</v>
+        <v>7.57396449704142e-08</v>
       </c>
       <c r="F151" t="n">
-        <v>0.01711155799817958</v>
+        <v>0.01402829037843456</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7.2827744904668e-08</v>
+        <v>7.638067061143983e-08</v>
       </c>
       <c r="D152" t="n">
-        <v>0.01677372063215175</v>
+        <v>0.01370798033568786</v>
       </c>
       <c r="E152" t="n">
-        <v>7.2827744904668e-08</v>
+        <v>7.638067061143983e-08</v>
       </c>
       <c r="F152" t="n">
-        <v>0.01652853481682109</v>
+        <v>0.01353057904426864</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>7.344312952005262e-08</v>
+        <v>7.702169625246547e-08</v>
       </c>
       <c r="D153" t="n">
-        <v>0.01617752233288448</v>
+        <v>0.01325093463993285</v>
       </c>
       <c r="E153" t="n">
-        <v>7.344312952005262e-08</v>
+        <v>7.702169625246547e-08</v>
       </c>
       <c r="F153" t="n">
-        <v>0.01596547033997695</v>
+        <v>0.01305054945334425</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>7.405851413543723e-08</v>
+        <v>7.766272189349111e-08</v>
       </c>
       <c r="D154" t="n">
-        <v>0.01558132403361721</v>
+        <v>0.01279388894417784</v>
       </c>
       <c r="E154" t="n">
-        <v>7.405851413543723e-08</v>
+        <v>7.766272189349111e-08</v>
       </c>
       <c r="F154" t="n">
-        <v>0.01542165439750237</v>
+        <v>0.0125876118190459</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>7.467389875082185e-08</v>
+        <v>7.830374753451675e-08</v>
       </c>
       <c r="D155" t="n">
-        <v>0.01498512573434994</v>
+        <v>0.01233684324842284</v>
       </c>
       <c r="E155" t="n">
-        <v>7.467389875082185e-08</v>
+        <v>7.830374753451675e-08</v>
       </c>
       <c r="F155" t="n">
-        <v>0.01489637681925254</v>
+        <v>0.0121411763547581</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>7.528928336620646e-08</v>
+        <v>7.894477317554238e-08</v>
       </c>
       <c r="D156" t="n">
-        <v>0.01438892743508267</v>
+        <v>0.01187979755266783</v>
       </c>
       <c r="E156" t="n">
-        <v>7.528928336620646e-08</v>
+        <v>7.894477317554238e-08</v>
       </c>
       <c r="F156" t="n">
-        <v>0.01438892743508267</v>
+        <v>0.01171065327386537</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>7.590466798159108e-08</v>
+        <v>7.958579881656805e-08</v>
       </c>
       <c r="D157" t="n">
-        <v>0.01396739081167065</v>
+        <v>0.0114227518569128</v>
       </c>
       <c r="E157" t="n">
-        <v>7.590466798159108e-08</v>
+        <v>7.958579881656805e-08</v>
       </c>
       <c r="F157" t="n">
-        <v>0.013898630889213</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="n">
-        <v>7.65200525969757e-08</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.01354585418825864</v>
-      </c>
-      <c r="E158" t="n">
-        <v>7.65200525969757e-08</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.0134249510833239</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="n">
-        <v>7.71354372123603e-08</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.01312431756484662</v>
-      </c>
-      <c r="E159" t="n">
-        <v>7.71354372123603e-08</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.01296738673346081</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="n">
-        <v>7.775082182774493e-08</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.0127027809414346</v>
-      </c>
-      <c r="E160" t="n">
-        <v>7.775082182774493e-08</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.01252543655566912</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="n">
-        <v>7.836620644312953e-08</v>
-      </c>
-      <c r="D161" t="n">
-        <v>0.01228124431802259</v>
-      </c>
-      <c r="E161" t="n">
-        <v>7.836620644312953e-08</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.01209859926599429</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="n">
-        <v>7.898159105851416e-08</v>
-      </c>
-      <c r="D162" t="n">
-        <v>0.01185970769461056</v>
-      </c>
-      <c r="E162" t="n">
-        <v>7.898159105851416e-08</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.01168637358048171</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="n">
-        <v>7.959697567389876e-08</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0.01143817107119855</v>
-      </c>
-      <c r="E163" t="n">
-        <v>7.959697567389876e-08</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.01128825821517683</v>
+        <v>0.01129545278975222</v>
       </c>
     </row>
   </sheetData>
